--- a/input/requirements/Condition.xlsx
+++ b/input/requirements/Condition.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahenket/Development/GitHub/Nictiz/GBB-IG/input/requirements/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edelman_nict1\IGs\GBB-IG\input\requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED832230-90A2-B141-8A59-508F66A307AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E15BA777-63BA-4A20-8B94-138FB720C249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-140" yWindow="-26660" windowWidth="43920" windowHeight="26260" activeTab="1" xr2:uid="{71855D19-E937-4D4D-85D2-5BCEBB780255}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{71855D19-E937-4D4D-85D2-5BCEBB780255}"/>
   </bookViews>
   <sheets>
     <sheet name="Uitleg" sheetId="5" r:id="rId1"/>
@@ -50,9 +50,9 @@
   <commentList>
     <comment ref="C5" authorId="0" shapeId="0" xr:uid="{CD16CA43-E215-4DCF-A4C0-2D380EB1C0BC}">
       <text>
-        <t xml:space="preserve">[Opmerkingenthread]
-U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
-Opmerking:
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     Uit Scope en Usage van Condition FHIR R4 v4.0.1 </t>
       </text>
     </comment>
@@ -73,9 +73,9 @@
   <commentList>
     <comment ref="K20" authorId="0" shapeId="0" xr:uid="{B3533A99-0CB6-4646-9417-20A66FEFD573}">
       <text>
-        <t>[Opmerkingenthread]
-U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
-Opmerking:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     1. Actief
 2. Inactief
 Kortere waardelijst</t>
@@ -83,41 +83,41 @@
     </comment>
     <comment ref="K26" authorId="1" shapeId="0" xr:uid="{20B2A504-5F6F-4996-9921-E2104F9548D8}">
       <text>
-        <t>[Opmerkingenthread]
-U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
-Opmerking:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     Wel in metadata!</t>
       </text>
     </comment>
     <comment ref="E29" authorId="2" shapeId="0" xr:uid="{DC3A08E9-01DD-48D1-B7F5-357810DE5428}">
       <text>
-        <t>[Opmerkingenthread]
-U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
-Opmerking:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     Onduidelijk welke waardelijst gehandeerd moet worden</t>
       </text>
     </comment>
     <comment ref="B31" authorId="3" shapeId="0" xr:uid="{035A58F6-6A6B-4788-883F-2110C3BA07ED}">
       <text>
-        <t>[Opmerkingenthread]
-U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
-Opmerking:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     ter discussie</t>
       </text>
     </comment>
     <comment ref="C31" authorId="4" shapeId="0" xr:uid="{00D6E7CD-1959-4C9A-8BC1-A1E323A0102F}">
       <text>
-        <t>[Opmerkingenthread]
-U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
-Opmerking:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     ter discussie</t>
       </text>
     </comment>
     <comment ref="C39" authorId="5" shapeId="0" xr:uid="{065B39A6-9843-49BF-88E8-0C2BF95F8D00}">
       <text>
-        <t>[Opmerkingenthread]
-U kunt deze opmerkingenthread lezen in uw versie van Excel. Eventuele wijzigingen aan de thread gaan echter verloren als het bestand wordt geopend in een nieuwere versie van Excel. Meer informatie: https://go.microsoft.com/fwlink/?linkid=870924
-Opmerking:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     ter discussie</t>
       </text>
     </comment>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="391">
   <si>
     <t>Veld</t>
   </si>
@@ -1565,6 +1565,15 @@
 - nadereSpecificatieProbleemNaam heeft in ZIBFHIR-145 een mapping gekregen op FHIR, maar is duidelijker in openEHR gemodelleerd als "variant" (echter variant is specifieker, dan LIMS/ZIB wil duiden )
 -specialistcontact: in openEHR is het onduidelijk, mogelijk other participants mits je aan kan geven dat het een voorkeurscontactpersoon is. in FHIR ook niet ideaal, namelijk note.text of via careteam.reason</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">* Logisch informatie model EHDSCondition versie 1.0.0
+* Verplichte elementen uit FHIR R4 Condition 
+* Verplichte elementen uit openEHR Problem / Diagnosis versie 1.7.4 
+* Zib Probleem uit publicatie 2017 
+* Zib Probleem uit publicatie 2020 
+* Informatiestandaard BgZ-MSZ versie 2.0.2 
+* Usecase Spoedsamenvatting van informatiestandaard Acute Zorg versie 2.2.0 </t>
   </si>
 </sst>
 </file>
@@ -1891,7 +1900,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="21">
     <dxf>
@@ -1985,46 +1994,6 @@
       </border>
     </dxf>
     <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2090,6 +2059,46 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment wrapText="1"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2811,7 +2820,7 @@
   <autoFilter ref="A2:C13" xr:uid="{7AAA9086-205B-4EC4-8920-A2DD04D02676}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{BDCFF82A-D4BE-440B-90DF-AA26F6831D5C}" name="Veld"/>
-    <tableColumn id="2" xr3:uid="{77503B9E-152C-4B39-87F4-D4FBBF1B3BDA}" name="Uitleg" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{77503B9E-152C-4B39-87F4-D4FBBF1B3BDA}" name="Uitleg" dataDxfId="20"/>
     <tableColumn id="5" xr3:uid="{B530BE2A-715C-42B8-BFE1-95637D35484B}" name="Beschrijving"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2819,36 +2828,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1B14A882-8085-4978-86D3-1A5B42023C72}" name="Tabel3" displayName="Tabel3" ref="A1:E17" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1B14A882-8085-4978-86D3-1A5B42023C72}" name="Tabel3" displayName="Tabel3" ref="A1:E17" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <autoFilter ref="A1:E17" xr:uid="{1B14A882-8085-4978-86D3-1A5B42023C72}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{2D5F85E5-856C-4A15-8C5D-D8D344B8F13C}" name="Type bron" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{062A7D5A-6D4F-45DD-9A5C-7A2D82A1266A}" name="Naam bron" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{24E64AAE-4BAD-402C-98B7-B46BE371B39E}" name="Toelichting" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{98DE6918-807C-41E0-ACBA-1E2221CF05FC}" name="Informatiebehoefte verwerkt in sheet 'informatiebeheofte'" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{8CFF4D4C-ABDD-49BC-8B49-237193168687}" name="Link naar bron informatie" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{2D5F85E5-856C-4A15-8C5D-D8D344B8F13C}" name="Type bron" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{062A7D5A-6D4F-45DD-9A5C-7A2D82A1266A}" name="Naam bron" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{24E64AAE-4BAD-402C-98B7-B46BE371B39E}" name="Toelichting" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{98DE6918-807C-41E0-ACBA-1E2221CF05FC}" name="Informatiebehoefte verwerkt in sheet 'informatiebeheofte'" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{8CFF4D4C-ABDD-49BC-8B49-237193168687}" name="Link naar bron informatie" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}" name="Tabel6" displayName="Tabel6" ref="A2:N59" totalsRowShown="0" headerRowDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}" name="Tabel6" displayName="Tabel6" ref="A2:N59" totalsRowShown="0" headerRowDxfId="12">
   <autoFilter ref="A2:N59" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{51E2B1E8-BF1C-4C85-9A83-8C69A4006993}" name="Nummer" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{021C00E0-4FF4-4652-B8E3-674B1F145954}" name="Naam" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{51E2B1E8-BF1C-4C85-9A83-8C69A4006993}" name="Nummer" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{021C00E0-4FF4-4652-B8E3-674B1F145954}" name="Naam" dataDxfId="10"/>
     <tableColumn id="12" xr3:uid="{721FE94A-B8C9-44E1-A03C-56E48CDCE2A3}" name="data-element"/>
-    <tableColumn id="3" xr3:uid="{12776FCA-6A89-4E9E-907F-2E30F0D43DA3}" name="Omschrijving" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{9E28C4DB-2A8B-484B-80F1-321440976652}" name="Variabiliteit" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{12776FCA-6A89-4E9E-907F-2E30F0D43DA3}" name="Omschrijving" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{9E28C4DB-2A8B-484B-80F1-321440976652}" name="Variabiliteit" dataDxfId="8"/>
     <tableColumn id="5" xr3:uid="{6FA3E114-7382-4230-B15E-A8DB28B8CE4B}" name="Aanwezigheid"/>
     <tableColumn id="6" xr3:uid="{E8FFDBDF-8B88-4089-89D0-252402D12764}" name="Verleden/heden/toekomst"/>
     <tableColumn id="7" xr3:uid="{BB9C62AB-9839-431A-90A2-B6A6D70DF1FB}" name="Herkomst"/>
     <tableColumn id="8" xr3:uid="{6BE87E7D-EFAE-42FD-9334-11E5EBAC9DC3}" name="Komt het in FHIR R4 voor?"/>
     <tableColumn id="9" xr3:uid="{C6EE00AA-2B37-4BE3-B349-AF61C6E68575}" name="Komt het in openEHR voor?"/>
     <tableColumn id="10" xr3:uid="{943D4BF3-315C-41FB-99E4-8DB8C54604A4}" name="Komt voor in ZIBProbleem-v4.4? (2020)"/>
-    <tableColumn id="14" xr3:uid="{8B1A7EB4-D690-4A36-9698-ACA592C2A715}" name="Komt voor in ZIBProbleem? (2017)" dataDxfId="15"/>
-    <tableColumn id="13" xr3:uid="{51A57E0A-A216-45BB-973D-E0D8C72BEEEC}" name="Komt voor in ZIBProbleem? (2024)" dataDxfId="14"/>
+    <tableColumn id="14" xr3:uid="{8B1A7EB4-D690-4A36-9698-ACA592C2A715}" name="Komt voor in ZIBProbleem? (2017)" dataDxfId="7"/>
+    <tableColumn id="13" xr3:uid="{51A57E0A-A216-45BB-973D-E0D8C72BEEEC}" name="Komt voor in ZIBProbleem? (2024)" dataDxfId="6"/>
     <tableColumn id="11" xr3:uid="{E7EDB106-7E3F-4122-A864-3B3AE59C9D87}" name="Opmerking"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -3230,15 +3239,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F1013F7-63B2-4F83-92B0-1C8153859891}">
   <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="218.5" customWidth="1"/>
+    <col min="1" max="1" width="218.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18">
         <f>(510*132.5) + (160*132.5)</f>
         <v>88775</v>
@@ -3247,7 +3256,7 @@
         <v>5832</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19">
         <f>(542*132.5)</f>
         <v>71815</v>
@@ -3265,17 +3274,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CC1E3B3-D087-4A2B-920B-9BA971FAD64B}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
-    <col min="2" max="2" width="46.6640625" customWidth="1"/>
-    <col min="3" max="3" width="59.6640625" customWidth="1"/>
+    <col min="2" max="2" width="46.7109375" customWidth="1"/>
+    <col min="3" max="3" width="59.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
     </row>
-    <row r="2" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -3286,7 +3295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -3297,7 +3306,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="96" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="105" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -3308,7 +3317,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="304" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="330" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -3319,7 +3328,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -3330,7 +3339,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -3341,7 +3350,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -3352,7 +3361,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="96" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="105" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -3363,18 +3372,18 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="135" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>23</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+      <c r="C10" s="4" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -3385,7 +3394,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="256" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="315" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -3394,7 +3403,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -3416,16 +3425,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8AA88E1-0CFC-4A69-A682-35DA329C9688}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" customWidth="1"/>
-    <col min="2" max="2" width="51.33203125" customWidth="1"/>
-    <col min="3" max="3" width="67.33203125" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
+    <col min="2" max="2" width="51.28515625" customWidth="1"/>
+    <col min="3" max="3" width="67.28515625" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="58.1640625" customWidth="1"/>
+    <col min="5" max="5" width="58.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>31</v>
       </c>
@@ -3442,7 +3451,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>36</v>
       </c>
@@ -3459,7 +3468,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>36</v>
       </c>
@@ -3476,7 +3485,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>36</v>
       </c>
@@ -3493,7 +3502,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>46</v>
       </c>
@@ -3508,7 +3517,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>46</v>
       </c>
@@ -3523,7 +3532,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>46</v>
       </c>
@@ -3538,7 +3547,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>55</v>
       </c>
@@ -3555,7 +3564,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>55</v>
       </c>
@@ -3572,7 +3581,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>55</v>
       </c>
@@ -3581,49 +3590,49 @@
       <c r="D10" s="3"/>
       <c r="E10" s="6"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="6"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="6"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="4"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="4"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="4"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
       <c r="E16" s="4"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -3650,25 +3659,25 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7034CDAF-2A08-4BE8-92C3-F4E7A6F24E1B}">
   <dimension ref="A1:O65"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.5" customWidth="1"/>
-    <col min="2" max="2" width="29.33203125" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" customWidth="1"/>
-    <col min="4" max="4" width="87.5" style="3" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="2" max="2" width="29.28515625" customWidth="1"/>
+    <col min="3" max="3" width="32.7109375" customWidth="1"/>
+    <col min="4" max="4" width="87.42578125" style="3" customWidth="1"/>
     <col min="5" max="5" width="78" style="3" customWidth="1"/>
-    <col min="6" max="6" width="18.6640625" customWidth="1"/>
-    <col min="7" max="7" width="11.5" customWidth="1"/>
-    <col min="8" max="8" width="32.5" customWidth="1"/>
-    <col min="9" max="9" width="28.1640625" customWidth="1"/>
-    <col min="10" max="10" width="51.33203125" customWidth="1"/>
-    <col min="11" max="11" width="38.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="38.5" customWidth="1"/>
-    <col min="14" max="14" width="33.33203125" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" customWidth="1"/>
+    <col min="8" max="8" width="32.42578125" customWidth="1"/>
+    <col min="9" max="9" width="28.140625" customWidth="1"/>
+    <col min="10" max="10" width="51.28515625" customWidth="1"/>
+    <col min="11" max="11" width="38.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="38.42578125" customWidth="1"/>
+    <col min="14" max="14" width="33.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>62</v>
       </c>
@@ -3712,7 +3721,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="182.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" ht="182.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
         <v>80</v>
       </c>
@@ -3743,7 +3752,7 @@
       <c r="N3" s="19"/>
       <c r="O3" s="9"/>
     </row>
-    <row r="4" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
         <v>85</v>
       </c>
@@ -3770,7 +3779,7 @@
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
     </row>
-    <row r="5" spans="1:15" ht="48" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
         <v>91</v>
       </c>
@@ -3798,7 +3807,7 @@
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
     </row>
-    <row r="6" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
         <v>96</v>
       </c>
@@ -3826,7 +3835,7 @@
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
     </row>
-    <row r="7" spans="1:15" ht="80" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" ht="105" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>99</v>
       </c>
@@ -3854,7 +3863,7 @@
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
     </row>
-    <row r="8" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>103</v>
       </c>
@@ -3875,7 +3884,7 @@
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
     </row>
-    <row r="9" spans="1:15" ht="48" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>106</v>
       </c>
@@ -3907,7 +3916,7 @@
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
     </row>
-    <row r="10" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>114</v>
       </c>
@@ -3934,7 +3943,7 @@
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
     </row>
-    <row r="11" spans="1:15" ht="64" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" ht="75" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>119</v>
       </c>
@@ -3967,7 +3976,7 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
     </row>
-    <row r="12" spans="1:15" ht="96" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" ht="105" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>127</v>
       </c>
@@ -4003,7 +4012,7 @@
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
     </row>
-    <row r="13" spans="1:15" ht="180.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" ht="180.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>135</v>
       </c>
@@ -4039,7 +4048,7 @@
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
     </row>
-    <row r="14" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
         <v>142</v>
       </c>
@@ -4073,7 +4082,7 @@
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
     </row>
-    <row r="15" spans="1:15" ht="135" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" ht="135" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>147</v>
       </c>
@@ -4107,7 +4116,7 @@
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
     </row>
-    <row r="16" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
         <v>154</v>
       </c>
@@ -4125,7 +4134,7 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
     </row>
-    <row r="17" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
         <v>156</v>
       </c>
@@ -4159,7 +4168,7 @@
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
     </row>
-    <row r="18" spans="1:14" ht="70.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
         <v>163</v>
       </c>
@@ -4187,7 +4196,7 @@
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
     </row>
-    <row r="19" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
         <v>168</v>
       </c>
@@ -4208,7 +4217,7 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
     </row>
-    <row r="20" spans="1:14" ht="101.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:14" ht="101.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>171</v>
       </c>
@@ -4246,7 +4255,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="108" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14" ht="108" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>179</v>
       </c>
@@ -4277,7 +4286,7 @@
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
     </row>
-    <row r="22" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>183</v>
       </c>
@@ -4295,7 +4304,7 @@
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
     </row>
-    <row r="23" spans="1:14" ht="64" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
         <v>185</v>
       </c>
@@ -4335,7 +4344,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="80" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" ht="75" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>195</v>
       </c>
@@ -4363,7 +4372,7 @@
       <c r="M24" s="3"/>
       <c r="N24" s="5"/>
     </row>
-    <row r="25" spans="1:14" ht="149.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:14" ht="149.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
         <v>199</v>
       </c>
@@ -4391,7 +4400,7 @@
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
     </row>
-    <row r="26" spans="1:14" ht="48" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="19" t="s">
         <v>204</v>
       </c>
@@ -4425,7 +4434,7 @@
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
     </row>
-    <row r="27" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="19" t="s">
         <v>210</v>
       </c>
@@ -4449,7 +4458,7 @@
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
     </row>
-    <row r="28" spans="1:14" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:14" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="19" t="s">
         <v>215</v>
       </c>
@@ -4473,7 +4482,7 @@
       <c r="I28" s="3"/>
       <c r="N28" s="3"/>
     </row>
-    <row r="29" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
         <v>219</v>
       </c>
@@ -4501,7 +4510,7 @@
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
     </row>
-    <row r="30" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
         <v>223</v>
       </c>
@@ -4529,7 +4538,7 @@
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
     </row>
-    <row r="31" spans="1:14" ht="219" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:14" ht="219" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
         <v>228</v>
       </c>
@@ -4557,7 +4566,7 @@
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
     </row>
-    <row r="32" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>233</v>
       </c>
@@ -4586,7 +4595,7 @@
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
     </row>
-    <row r="33" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
         <v>240</v>
       </c>
@@ -4609,7 +4618,7 @@
       </c>
       <c r="N33" s="3"/>
     </row>
-    <row r="34" spans="1:14" ht="162" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14" ht="162" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="19" t="s">
         <v>243</v>
       </c>
@@ -4637,7 +4646,7 @@
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
     </row>
-    <row r="35" spans="1:14" ht="121.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" ht="121.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
         <v>248</v>
       </c>
@@ -4665,7 +4674,7 @@
       <c r="M35" s="3"/>
       <c r="N35" s="3"/>
     </row>
-    <row r="36" spans="1:14" ht="32" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>253</v>
       </c>
@@ -4692,7 +4701,7 @@
       <c r="M36" s="3"/>
       <c r="N36" s="3"/>
     </row>
-    <row r="37" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
         <v>259</v>
       </c>
@@ -4720,7 +4729,7 @@
       <c r="M37" s="3"/>
       <c r="N37" s="3"/>
     </row>
-    <row r="38" spans="1:14" ht="66.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
         <v>263</v>
       </c>
@@ -4748,7 +4757,7 @@
       <c r="M38" s="3"/>
       <c r="N38" s="3"/>
     </row>
-    <row r="39" spans="1:14" ht="178.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14" ht="178.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
         <v>267</v>
       </c>
@@ -4776,7 +4785,7 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
     </row>
-    <row r="40" spans="1:14" ht="135" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" ht="135" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
         <v>271</v>
       </c>
@@ -4808,7 +4817,7 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
     </row>
-    <row r="41" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="s">
         <v>276</v>
       </c>
@@ -4836,7 +4845,7 @@
       <c r="M41" s="3"/>
       <c r="N41" s="3"/>
     </row>
-    <row r="42" spans="1:14" ht="98.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
         <v>280</v>
       </c>
@@ -4864,7 +4873,7 @@
       <c r="M42" s="3"/>
       <c r="N42" s="3"/>
     </row>
-    <row r="43" spans="1:14" ht="32" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="19" t="s">
         <v>285</v>
       </c>
@@ -4896,7 +4905,7 @@
       <c r="M43" s="3"/>
       <c r="N43" s="3"/>
     </row>
-    <row r="44" spans="1:14" ht="48" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A44" s="9"/>
       <c r="B44" s="3"/>
       <c r="C44" s="10"/>
@@ -4913,7 +4922,7 @@
       <c r="M44" s="3"/>
       <c r="N44" s="3"/>
     </row>
-    <row r="45" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="19" t="s">
         <v>292</v>
       </c>
@@ -4947,7 +4956,7 @@
       <c r="M45" s="3"/>
       <c r="N45" s="3"/>
     </row>
-    <row r="46" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>299</v>
       </c>
@@ -4966,7 +4975,7 @@
       <c r="M46" s="3"/>
       <c r="N46" s="3"/>
     </row>
-    <row r="47" spans="1:14" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:14" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
         <v>301</v>
       </c>
@@ -4994,7 +5003,7 @@
       <c r="M47" s="3"/>
       <c r="N47" s="3"/>
     </row>
-    <row r="48" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="19" t="s">
         <v>305</v>
       </c>
@@ -5026,7 +5035,7 @@
       <c r="M48" s="3"/>
       <c r="N48" s="3"/>
     </row>
-    <row r="49" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="19" t="s">
         <v>311</v>
       </c>
@@ -5051,7 +5060,7 @@
       <c r="M49" s="3"/>
       <c r="N49" s="3"/>
     </row>
-    <row r="50" spans="1:14" ht="32" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="19" t="s">
         <v>314</v>
       </c>
@@ -5076,7 +5085,7 @@
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
     </row>
-    <row r="51" spans="1:14" ht="32" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="19" t="s">
         <v>317</v>
       </c>
@@ -5110,7 +5119,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="52" spans="1:14" ht="32" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="9"/>
       <c r="B52" s="3"/>
       <c r="C52" s="10"/>
@@ -5127,7 +5136,7 @@
       <c r="M52" s="3"/>
       <c r="N52" s="4"/>
     </row>
-    <row r="53" spans="1:14" ht="32" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="9" t="s">
         <v>325</v>
       </c>
@@ -5145,7 +5154,7 @@
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
     </row>
-    <row r="54" spans="1:14" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:14" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="19" t="s">
         <v>327</v>
       </c>
@@ -5179,7 +5188,7 @@
       <c r="M54" s="25"/>
       <c r="N54" s="3"/>
     </row>
-    <row r="55" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="9" t="s">
         <v>334</v>
       </c>
@@ -5207,7 +5216,7 @@
       <c r="M55" s="17"/>
       <c r="N55" s="3"/>
     </row>
-    <row r="56" spans="1:14" ht="32" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A56" s="19" t="s">
         <v>338</v>
       </c>
@@ -5239,7 +5248,7 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
     </row>
-    <row r="57" spans="1:14" ht="32" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="19" t="s">
         <v>344</v>
       </c>
@@ -5271,7 +5280,7 @@
       <c r="M57" s="3"/>
       <c r="N57" s="3"/>
     </row>
-    <row r="58" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="19" t="s">
         <v>351</v>
       </c>
@@ -5303,7 +5312,7 @@
       <c r="M58" s="3"/>
       <c r="N58" s="3"/>
     </row>
-    <row r="59" spans="1:14" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:14" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="9" t="s">
         <v>355</v>
       </c>
@@ -5326,15 +5335,15 @@
         <v>361</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B63" s="28"/>
       <c r="C63" s="28"/>
     </row>
-    <row r="64" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B64" s="29"/>
       <c r="C64" s="30"/>
     </row>
-    <row r="65" spans="2:3" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B65" s="28"/>
       <c r="C65" s="28"/>
     </row>
@@ -5358,17 +5367,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{273AFAA3-99F7-4E93-9580-DCAE2B14D938}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.1640625" customWidth="1"/>
-    <col min="2" max="2" width="18.5" customWidth="1"/>
-    <col min="4" max="4" width="15.1640625" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" customWidth="1"/>
-    <col min="6" max="6" width="16.5" customWidth="1"/>
-    <col min="7" max="7" width="41.5" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" customWidth="1"/>
+    <col min="7" max="7" width="41.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="195.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="195.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>362</v>
       </c>
@@ -5391,7 +5400,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>364</v>
       </c>
@@ -5423,10 +5432,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2489EBC-5098-4697-9724-F190D24E1C3D}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" ht="111" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" ht="111" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>367</v>
       </c>
@@ -5440,13 +5449,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0062C35-A590-498D-8635-16DE3DC0B82A}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.5" customWidth="1"/>
+    <col min="1" max="1" width="36.42578125" customWidth="1"/>
     <col min="2" max="2" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>100</v>
       </c>
@@ -5454,7 +5463,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="32" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>368</v>
       </c>
@@ -5462,7 +5471,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>370</v>
       </c>
@@ -5478,15 +5487,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9E8E4E8-143C-4C64-99FB-1306F2338EFB}">
   <dimension ref="A2:J9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="27.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="27.5" style="3" customWidth="1"/>
-    <col min="4" max="4" width="60.1640625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="47.6640625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="27.42578125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="60.140625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="47.7109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B2" s="15" t="s">
         <v>371</v>
       </c>
@@ -5494,7 +5503,7 @@
       <c r="D2" s="12"/>
       <c r="E2" s="12"/>
     </row>
-    <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B3" s="16" t="s">
         <v>372</v>
       </c>
@@ -5508,7 +5517,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="156" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="156" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="14" t="s">
         <v>375</v>
       </c>
@@ -5520,7 +5529,7 @@
       </c>
       <c r="E4" s="14"/>
     </row>
-    <row r="5" spans="1:10" ht="182.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="182.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
         <v>378</v>
       </c>
@@ -5532,7 +5541,7 @@
       </c>
       <c r="E5" s="14"/>
     </row>
-    <row r="6" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="19"/>
       <c r="B6" s="3" t="s">
         <v>339</v>
@@ -5549,7 +5558,7 @@
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B7" s="14" t="s">
         <v>382</v>
       </c>
@@ -5561,7 +5570,7 @@
       </c>
       <c r="E7" s="14"/>
     </row>
-    <row r="8" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B8" s="14" t="s">
         <v>384</v>
       </c>
@@ -5573,7 +5582,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="80" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="B9" s="14"/>
       <c r="C9" s="14" t="s">
         <v>387</v>
@@ -5592,6 +5601,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="bb18a1b9-ddba-4244-9634-64732d0cb267">
@@ -5600,15 +5618,6 @@
     <TaxCatchAll xmlns="06294a2e-6f87-4144-83b8-94a4d04d144a" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5819,6 +5828,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{148267B0-4CF5-48A7-B543-CDE45AF0A8FC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E3A9028-3436-4B29-A420-9ED5B8A085B1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -5831,14 +5848,6 @@
     <ds:schemaRef ds:uri="06294a2e-6f87-4144-83b8-94a4d04d144a"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{148267B0-4CF5-48A7-B543-CDE45AF0A8FC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/input/requirements/Condition.xlsx
+++ b/input/requirements/Condition.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30613"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edelman_nict1\IGs\GBB-IG\input\requirements\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nictiznl.sharepoint.com/sites/Zib-transitiecommunity/Gedeelde documenten/Architectuur/Werkgroepen ZIBS 2.0 Implementatie/Bouwblokken/Condition/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E15BA777-63BA-4A20-8B94-138FB720C249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{89866ED0-A22E-4686-A559-9500B72E2D08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{71855D19-E937-4D4D-85D2-5BCEBB780255}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="3" activeTab="3" xr2:uid="{71855D19-E937-4D4D-85D2-5BCEBB780255}"/>
   </bookViews>
   <sheets>
     <sheet name="Uitleg" sheetId="5" r:id="rId1"/>
@@ -63,33 +63,22 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={B3533A99-0CB6-4646-9417-20A66FEFD573}</author>
-    <author>tc={20B2A504-5F6F-4996-9921-E2104F9548D8}</author>
+    <author>tc={FC56F738-FB65-495B-9B48-E0F47216F010}</author>
     <author>tc={DC3A08E9-01DD-48D1-B7F5-357810DE5428}</author>
     <author>tc={035A58F6-6A6B-4788-883F-2110C3BA07ED}</author>
     <author>tc={00D6E7CD-1959-4C9A-8BC1-A1E323A0102F}</author>
     <author>tc={065B39A6-9843-49BF-88E8-0C2BF95F8D00}</author>
   </authors>
   <commentList>
-    <comment ref="K20" authorId="0" shapeId="0" xr:uid="{B3533A99-0CB6-4646-9417-20A66FEFD573}">
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{FC56F738-FB65-495B-9B48-E0F47216F010}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    1. Actief
-2. Inactief
-Kortere waardelijst</t>
+    AllergyInt heeft een andere naam conventie voor ‘Nummer’. Controleren welke juist is.</t>
       </text>
     </comment>
-    <comment ref="K26" authorId="1" shapeId="0" xr:uid="{20B2A504-5F6F-4996-9921-E2104F9548D8}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Wel in metadata!</t>
-      </text>
-    </comment>
-    <comment ref="E29" authorId="2" shapeId="0" xr:uid="{DC3A08E9-01DD-48D1-B7F5-357810DE5428}">
+    <comment ref="E29" authorId="1" shapeId="0" xr:uid="{DC3A08E9-01DD-48D1-B7F5-357810DE5428}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -97,7 +86,7 @@
     Onduidelijk welke waardelijst gehandeerd moet worden</t>
       </text>
     </comment>
-    <comment ref="B31" authorId="3" shapeId="0" xr:uid="{035A58F6-6A6B-4788-883F-2110C3BA07ED}">
+    <comment ref="B31" authorId="2" shapeId="0" xr:uid="{035A58F6-6A6B-4788-883F-2110C3BA07ED}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -105,7 +94,7 @@
     ter discussie</t>
       </text>
     </comment>
-    <comment ref="C31" authorId="4" shapeId="0" xr:uid="{00D6E7CD-1959-4C9A-8BC1-A1E323A0102F}">
+    <comment ref="C31" authorId="3" shapeId="0" xr:uid="{00D6E7CD-1959-4C9A-8BC1-A1E323A0102F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -113,7 +102,7 @@
     ter discussie</t>
       </text>
     </comment>
-    <comment ref="C39" authorId="5" shapeId="0" xr:uid="{065B39A6-9843-49BF-88E8-0C2BF95F8D00}">
+    <comment ref="C40" authorId="4" shapeId="0" xr:uid="{065B39A6-9843-49BF-88E8-0C2BF95F8D00}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -125,13 +114,34 @@
 </comments>
 </file>
 
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={75AC27D5-B4F8-442C-9CA0-BF0C6D98019C}</author>
+  </authors>
+  <commentList>
+    <comment ref="D4" authorId="0" shapeId="0" xr:uid="{75AC27D5-B4F8-442C-9CA0-BF0C6D98019C}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    geen voorsortering geweest op de zib 2020. Wij wilden coded, dat is text. Dus zelf toegevoegd aan BgZ-MSZ</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="512">
   <si>
     <t>Veld</t>
   </si>
   <si>
     <t>Beschrijving</t>
+  </si>
+  <si>
+    <t>a.d.h.v. keuze FHIR als basismodel</t>
   </si>
   <si>
     <t>Conceptbeschrijving</t>
@@ -163,7 +173,8 @@
 Spoedsamenvatting 2.2.0, bij het opstellen van de episodes en problemen 
 BgZ-MSZ: bij klachten en diagnoses
 eOverdracht: problemen
-Eerstelijnszorg: problemen</t>
+Eerstelijnszorg: problemen/episode
+Medicatieproces: om te duiden waarom bepaalde medicatie wordt voorschreven / toegediend</t>
   </si>
   <si>
     <t>Representatie</t>
@@ -181,7 +192,7 @@
     <t>[Alle bekende synoniemen voor het concept.]</t>
   </si>
   <si>
-    <t>episode, diagnose, aandoening, probleem, klacht(als het geen onderdeel is van de aandoening), functionele beperking, complicatie, symptoom(als het geen onderdeel is van de aandoening)</t>
+    <t>episode, diagnose, aandoening, probleem, klacht(als het geen onderdeel is van de aandoening), functionele beperking, complicatie, symptoom(als het geen onderdeel is van de aandoening, dus alleen als zelfstandig klinisch relevant probleem en niet voor losse of kortdurende symptomen. )</t>
   </si>
   <si>
     <t>Juist gebruik</t>
@@ -199,7 +210,7 @@
     <t>[Beschrijf hier waar het concept niet voor bedoeld is, en geef waar mogelijk aan welk concept er wel geschikt voor is.]</t>
   </si>
   <si>
-    <t>Het concept is niet bedoeld voor losse metingen, bevindingen of kortdurende symptomen; gebruik hiervoor Observation. Het is ook niet bedoeld om de uitgevoerde ingreep zelf vast te leggen; gebruik daarvoor Procedure. Voor allergieën en intoleranties die klinische beslisondersteuning moeten activeren, is AllergyIntolerance het aangewezen concept. Een blijvende toestand na een ingreep kan wel als conditie worden vastgelegd.</t>
+    <t>Het concept is niet bedoeld voor losse metingen, bevindingen of kortdurende symptomen of als de symptomen bijdragen  tot het komen van een diagnose/gezondheidstoestand; gebruik hiervoor Observation. Het is ook niet bedoeld om de uitgevoerde ingreep zelf vast te leggen; gebruik daarvoor Procedure. Voor allergieën en intoleranties die klinische beslisondersteuning moeten activeren, is AllergyIntolerance het aangewezen concept. Een blijvende toestand na een ingreep kan wel als conditie worden vastgelegd.</t>
   </si>
   <si>
     <t>Referenties</t>
@@ -221,6 +232,42 @@
   </si>
   <si>
     <t>Keuze Basismodel</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">FHIR Condition Maturity Level: 3 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&amp;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> openEHR Problem/Diagnosis;latest revision / latest published  53 [1.7.4] 
+Na analyse blijkt FHIR beste keus, want: 
+- categorie: bij openEHR zijn de keuzes voor categorie niet overeenkomend met de categorieen van de LIM -&gt; maar hoeft niet persé een deal-breaker te zijn
+- diagnosisAssertionStatus waardelijst komt niet precies overeen bij openEHR(mist differential en netered-in-error), wel volledige mapping met FHIR
+- stage komt niet precies overeen in openEHR, namelijk via extensie / uitbreiding van archetype Specific Details (cluster?), wel in FHIR
+- nadereSpecificatieProbleemNaam heeft in ZIBFHIR-145 een mapping gekregen op FHIR, maar is duidelijker in openEHR gemodelleerd als "variant" (echter variant is specifieker, dan LIMS/ZIB wil duiden )
+- specialistcontact: in openEHR is het onduidelijk, mogelijk other participants mits je aan kan geven dat het een voorkeurscontactpersoon is. in FHIR ook niet ideaal, namelijk note.text of via careteam.reason</t>
+    </r>
   </si>
   <si>
     <t>Concept-sheet is opgemaakt met spelregel: https://nictiz.atlassian.net/browse/DAGIM-72</t>
@@ -263,13 +310,16 @@
     <t>Volgens DAGIM-19 is het nodig dat alle verplichte elementen van de FHIR resource opgenomen worden als informatiebehoefte.</t>
   </si>
   <si>
+    <t>Ja, alleen verplichte elementen</t>
+  </si>
+  <si>
     <t xml:space="preserve">openEHR archetype Problem/Diagnosis </t>
   </si>
   <si>
-    <t>Volgens DAGIM-21 l is het nodig dat alle verplichte elementen van de openEHR archetype opgenomen worden als informatiebehoefte.</t>
-  </si>
-  <si>
-    <t>Clinical Knowledge Manager</t>
+    <t>Volgens DAGIM-21 l is het nodig dat alle verplichte elementen van de openEHR archetype opgenomen worden als informatiebehoefte. latest published  53 [1.7.4]</t>
+  </si>
+  <si>
+    <t>Clinical Knowledge Manager (openEHR Problem/Diagnosis 1.7.4)</t>
   </si>
   <si>
     <t>Zib</t>
@@ -281,7 +331,11 @@
     <t>Geen baseline. Onduidelijk of deze meegenomen moet worden. Is het nodig om AandoeningOfGesteldheid en Symptoom uit 2024 ook mee te nemen?</t>
   </si>
   <si>
-    <t>Diagnose-v2.0(2024NL) - Zorginformatiebouwstenen</t>
+    <t>ja, deels</t>
+  </si>
+  <si>
+    <t>Diagnose-v2.0(2024NL) - Zorginformatiebouwstenen 
+https://www.zibs.nl/wiki/RegistratieGegevens-v1.1.2(2024NL)</t>
   </si>
   <si>
     <t>Zib Probleem v4.4 2020</t>
@@ -290,13 +344,20 @@
     <t>Baseline</t>
   </si>
   <si>
+    <t>ja</t>
+  </si>
+  <si>
     <t>Probleem-v4.4(2020NL) - Zorginformatiebouwstenen</t>
   </si>
   <si>
     <t>Zib Probleem V4.1 2017</t>
   </si>
   <si>
-    <t>Probleem-v4.1(2017NL) - Zorginformatiebouwstenen</t>
+    <t>ja, behoudens data-element probleemtype</t>
+  </si>
+  <si>
+    <t>Probleem-v4.1(2017NL) - Zorginformatiebouwstenen
+https://www.zibs.nl/images/2/2a/Architectuurdocument_Registratie_aan_de_bron_-_Volume_1_v1.1.pdf</t>
   </si>
   <si>
     <t>Informatiestandaard</t>
@@ -305,7 +366,36 @@
     <t>Informatiestandaard BgZ-MSZ 2.0.2</t>
   </si>
   <si>
-    <t>Volgens de DoD Q3 moet dit opgenomen worden in deze iteratie van de GBB. De informatiebehoefte is identiek aan zib 2017 op één element na. Bij dit element staat de informatiestandaard als herkomst beschreven.</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Volgens de DoD Q3 moet dit opgenomen worden in deze iteratie van de GBB. De informatiebehoefte is identiek aan zib 2017 op één element na. Bij dit element</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE97132"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>staat de informatiestandaard als herkomst beschreven.</t>
+    </r>
+  </si>
+  <si>
+    <t>Ja, behoudens data-element NadereSpecificatieProbleemNaam</t>
   </si>
   <si>
     <t>Dataset (voor transactie) 2.16.840.1.113883.2.4.3.11.60.42.4.42 - Sturen</t>
@@ -318,7 +408,80 @@
   </si>
   <si>
     <t>https://referentiemodel.nhg.org/
-https://www.nhg.org/wp-content/uploads/2023/02/Richtlijn-Gegevensuitwisseling-acute-zorg-versie-4-2022.pdf</t>
+https://www.nhg.org/wp-content/uploads/2023/02/Richtlijn-Gegevensuitwisseling-acute-zorg-versie-4-2022.pdf
+KEZO Overdracht Concern, 2.16.840.1.113883.2.4.3.11.60.66.10.212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeugdgezondheidszorg </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Volgens de DoD Q3 wordt deze informatiestandaard </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">niet </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>in deze iteratie van de GBB meegenomen</t>
+    </r>
+  </si>
+  <si>
+    <t>nee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vaccinatie-Immunisatie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MedMij (Zelfmetingen, eAfspraak, PDF/A, Dossierwijzigingsverzoek) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uitkomstgerichte Zorg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huisartsenzorg (eerstelijnszorg) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geboortezorg </t>
+  </si>
+  <si>
+    <t xml:space="preserve">eOverdracht  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BgLz,  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BgGGZ </t>
+  </si>
+  <si>
+    <t>Beeldbeschikbaarheid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Labuitwisseling  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MedicatieProces </t>
+  </si>
+  <si>
+    <t>zie ook scopebepaling: https://nictiznl.sharepoint.com/:w:/r/sites/Zib-transitiecommunity/_layouts/15/Doc.aspx?sourcedoc=%7B638068DB-18FC-40E3-99DD-94FDB108BAB0%7D&amp;file=scopebepaling-condition.docx&amp;action=default&amp;mobileredirect=true</t>
   </si>
   <si>
     <t>Nummer</t>
@@ -351,18 +514,21 @@
     <t>Komt het in openEHR voor?</t>
   </si>
   <si>
-    <t>Komt voor in ZIBProbleem-v4.4? (2020)</t>
-  </si>
-  <si>
-    <t>Komt voor in ZIBProbleem? (2017)</t>
-  </si>
-  <si>
-    <t>Komt voor in ZIBProbleem? (2024)</t>
-  </si>
-  <si>
     <t>Opmerking</t>
   </si>
   <si>
+    <t>Kolom1</t>
+  </si>
+  <si>
+    <t>Kolom2</t>
+  </si>
+  <si>
+    <t>[Nummer van de informatie-requirement start bij 1, sub behoeftes kunnen worden gemodelleerd met X.X of X.X.X]</t>
+  </si>
+  <si>
+    <t>[Naam waaraan de informatie-requirement te herkennen is]</t>
+  </si>
+  <si>
     <t>[Geef hier een tekstuele omschrijving van de behoefte die ingevuld wordt met de informatie-requirement]</t>
   </si>
   <si>
@@ -372,6 +538,9 @@
     <t>[Geef aan in welke situaties het element waarmee de informatie-requirement gedekt wordt er zou moeten zijn, en evt. wanneer het afwezig kan zijn]</t>
   </si>
   <si>
+    <t>[Geef aan of de informatie relevant is voor gebruik van het model voor zaken in het verleden, in het heden, en/of de toekomst. Vaak is slechts een van deze situaties in scope van het bouwblok, maar niet altijd]</t>
+  </si>
+  <si>
     <t>[Geef aan waar de behoefte vandaan komt, bv. een specifieke informatiestandaard of bepaalde zorgrichtlijn]</t>
   </si>
   <si>
@@ -381,16 +550,15 @@
     <t>Patient</t>
   </si>
   <si>
+    <t>Zorgverlener heeft de patient nodig om de gezondheidstoestand aan te koppelen.</t>
+  </si>
+  <si>
     <t>Ja (subject)</t>
   </si>
   <si>
     <t>Ja (Reference model: subject of care) 1:1</t>
   </si>
   <si>
-    <t>Nee, Kenmerken die relevant zijn voor een eenduidige definitie van het concept vormen de dataelementen van de zib. Een zib moet alle mogelijke eigenschappen van dat concept vatten voor zover relevant in gebruik van informatiesystemen binnen het zorg- en gezondheidsdomein
-Kenmerken die wel relevant zijn voor een compleet begrip, maar ook los van het concept herbruikbaar zijn worden als aparte zib middels een relaties vormgegeven</t>
-  </si>
-  <si>
     <t>CON-1.1</t>
   </si>
   <si>
@@ -400,50 +568,53 @@
     <t>De patiënt waarover de gezondheidstoestand gaat</t>
   </si>
   <si>
+    <t>Verwijzing naar EHDSPatient</t>
+  </si>
+  <si>
+    <t>1..1</t>
+  </si>
+  <si>
+    <t>EHDS LIM EHDSCondition 1.0.0</t>
+  </si>
+  <si>
+    <t>CON-1.2</t>
+  </si>
+  <si>
+    <t>Subject of care</t>
+  </si>
+  <si>
+    <t>De persoon waarnaar in deze evaluatie wordt verwezen, is doorgaans de persoon op wie het medisch dossier betrekking heeft, oftewel de patiënt. In bepaalde omstandigheden kan het echter ook om anderen gaan, bijvoorbeeld een orgaandonor, een foetus of een familielid.</t>
+  </si>
+  <si>
+    <t>Vewijzing naar Subject of Care</t>
+  </si>
+  <si>
+    <t>openEHR Problem/Diagnosis 1.7.4</t>
+  </si>
+  <si>
+    <t>CON-1.3</t>
+  </si>
+  <si>
+    <t>Geeft aan aan welke patiënt of groep het dossier in kader van gezondheidstoestand is gekoppeld.</t>
+  </si>
+  <si>
+    <t>Verwijziging naar Patient of Groep</t>
+  </si>
+  <si>
+    <t>CON-1.4</t>
+  </si>
+  <si>
+    <t>Onderwerp</t>
+  </si>
+  <si>
+    <t>NL-behoefte vanuit zib-2017:Degene op wie de informatie betrekking heeft. Vaak zal dit de patiënt zijn, maar vooral bij kleine kinderen kan het informatie over de ouder of verzorger zijn. Vooral bij de verpleegkundige overdrachten speelt b.v. bekwaamheid en betrokkenheid van mantelzorgers een rol.
+NL-behoefte voor iemand anders dan patient komt te vervallen in zib- 2020:  impliciet is dit altijd de patiënt. In de sporadische gevallen dat de patiënt niet het onderwerp is, is dit in de betreffende zibs al expliciet gemodelleerd, zoals bijvoorbeeld in FamilieAnamnese.</t>
+  </si>
+  <si>
     <t>Verwijzing naar Patient</t>
   </si>
   <si>
-    <t>1..1</t>
-  </si>
-  <si>
-    <t>EHDS LIM EHDSCondition 1.0.0</t>
-  </si>
-  <si>
-    <t>CON-1.2</t>
-  </si>
-  <si>
-    <t>Subject of care</t>
-  </si>
-  <si>
-    <t>De persoon waarnaar in deze evaluatie wordt verwezen, is doorgaans de persoon op wie het medisch dossier betrekking heeft, oftewel de patiënt. In bepaalde omstandigheden kan het echter ook om anderen gaan, bijvoorbeeld een orgaandonor, een foetus of een familielid.</t>
-  </si>
-  <si>
-    <t>Vewijzing naar Subject of Care</t>
-  </si>
-  <si>
-    <t>openEHR Problem/Diagnosis 1.7.4</t>
-  </si>
-  <si>
-    <t>CON-1.3</t>
-  </si>
-  <si>
-    <t>Geeft aan aan welke patiënt of groep het dossier in kader van gezondheidstoestand is gekoppeld.</t>
-  </si>
-  <si>
-    <t>Verwijziging naar Patient of Groep</t>
-  </si>
-  <si>
-    <t>CON-1.4</t>
-  </si>
-  <si>
-    <t>Onderwerp</t>
-  </si>
-  <si>
-    <t>NL-behoefte vanuit zib-2017:Degene op wie de informatie betrekking heeft. Vaak zal dit de patiënt zijn, maar vooral bij kleine kinderen kan het informatie over de ouder of verzorger zijn. Vooral bij de verpleegkundige overdrachten speelt b.v. bekwaamheid en betrokkenheid van mantelzorgers een rol.
-NL-behoefte komt te vervallen in zib- 2020:  impliciet is dit altijd de patiënt. In de sporadische gevallen dat de patiënt niet het onderwerp is, is dit in de betreffende zibs al expliciet gemodelleerd, zoals bijvoorbeeld in FamilieAnamnese.</t>
-  </si>
-  <si>
-    <t>ZIB 2017  (https://www.zibs.nl/images/2/2a/Architectuurdocument_Registratie_aan_de_bron_-_Volume_1_v1.1.pdf) 
+    <t>ZIB 2017
 Spoedsamenvatting 2.2.0</t>
   </si>
   <si>
@@ -465,6 +636,9 @@
     <t>Business identifier van het object</t>
   </si>
   <si>
+    <t>Identifier</t>
+  </si>
+  <si>
     <t>0..*</t>
   </si>
   <si>
@@ -474,12 +648,6 @@
     <t>Ja (architype.id) maar komt niet voor in de archetypen, maar komt naar voren bij het opslaan (originating_system_item_ids : DV_IDENTIFIER). is 0..*</t>
   </si>
   <si>
-    <t>Nee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nee </t>
-  </si>
-  <si>
     <t>CON-2.2</t>
   </si>
   <si>
@@ -501,9 +669,7 @@
     <t>Auteur</t>
   </si>
   <si>
-    <t>De auteur van de informatie over de gezondheidstoestand.
-NL-behoefte voor auteur, informatiebron en vastlegger komt uit 'registratie aan de bron' voor zib2017.
-NL-behoefte komt te vervallen in zib2020</t>
+    <t>De auteur van de informatie over de gezondheidstoestand.</t>
   </si>
   <si>
     <t>0..* Choice of types</t>
@@ -541,12 +707,6 @@
     <t>Ja (RM:other_participations)</t>
   </si>
   <si>
-    <t>Auteur: niet voor elke zib klinisch relevant, en bovendien niet voor elke zib duidelijk wat hiermee bedoeld wordt, met name in relatie tot bron van de informatie en de vastlegger in het dossier.</t>
-  </si>
-  <si>
-    <t>JA, auteur als basiselement</t>
-  </si>
-  <si>
     <t>CON-3.1</t>
   </si>
   <si>
@@ -559,22 +719,21 @@
     <t xml:space="preserve">
 De zorgverlener die de informatie over de conditie invoert/registreert
 NL-behoefte: Waarom/meerwaarde vanuit de spoedsamenvatting; om verschil te maken tussen wie registreert en wie is verantwoordelijke dossierhouder; Er kunnen verschillende zorgverleners werken bij dezelfde organisatie -&gt; niet bekend of dit een informatiebehoefte is uit het zorgveld of uit HL7standaard V3 CDA (custiodian en author) 
-</t>
+NL-behoefte voor auteur, informatiebron en vastlegger komt uit 'registratie aan de bron' voor zib2017.
+NL-behoefte komt te vervallen in zib2020</t>
   </si>
   <si>
     <t>Verwijziging naar EHDSHealthProfessional</t>
   </si>
   <si>
-    <t>EHDS LIM EHDSCondition 1.0.0, Zib 2017 (https://www.zibs.nl/images/2/2a/Architectuurdocument_Registratie_aan_de_bron_-_Volume_1_v1.1.pdf) 
+    <t>EHDS LIM EHDSCondition 1.0.0
+Zib 2017 
 Spoedsamenvatting 2.2.0</t>
   </si>
   <si>
     <t>Ja (recorder = Practitioner of PractitionerRole)</t>
   </si>
   <si>
-    <t>ja</t>
-  </si>
-  <si>
     <t>CON-3.2</t>
   </si>
   <si>
@@ -584,12 +743,15 @@
     <t>authorEHDSOrganisation</t>
   </si>
   <si>
-    <t xml:space="preserve">De organisatie waaruit de informatie over de conditie afkomstig is.
+    <t>De organisatie waaruit de informatie over de conditie afkomstig is.
 NL-behoefte: waarom/meerwaarde vanuit de spoedsamenvatting: om verschil te maken tussen wie registreert en wie is verantwoordelijke dossierhouder; als in er kunnen verschillende zorgverleners werken bij dezelfde organisatie.-&gt; niet bekend of dit een informatiebehoefte is uit het zorgveld of uit  HL7standaard V3 CDA (custiodian en author) 
-Bij het sturen van verwijzingen, rapportages, logistieke berichten en ambulanceberichten ligt het initiatief voor gegevensuitwisseling bij de brondossierhouder (bron: https://www.nhg.org/wp-content/uploads/2023/02/Richtlijn-Gegevensuitwisseling-acute-zorg-versie-4-2022.pdf ). </t>
+NL-behoefte spoedsamenvatting: Bij het sturen van verwijzingen, rapportages, logistieke berichten en ambulanceberichten ligt het initiatief voor gegevensuitwisseling bij de brondossierhouder</t>
   </si>
   <si>
     <t>Verwijziging naar EHDSOrganization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0..* </t>
   </si>
   <si>
     <t>EHDS LIM EHDSCondition 1.0.0
@@ -612,6 +774,9 @@
   </si>
   <si>
     <t>Verwijziging naar EHDSDevice</t>
+  </si>
+  <si>
+    <t>Nee</t>
   </si>
   <si>
     <t>CON-3.4</t>
@@ -657,10 +822,7 @@
     <t>Verwijzing naar patient, zorgverlener, contactpersoon</t>
   </si>
   <si>
-    <t>Zib 2017 (https://www.zibs.nl/images/2/2a/Architectuurdocument_Registratie_aan_de_bron_-_Volume_1_v1.1.pdf)</t>
-  </si>
-  <si>
-    <t>nee</t>
+    <t>Zib 2017</t>
   </si>
   <si>
     <t>CON-4</t>
@@ -669,6 +831,9 @@
     <t>Datum en evt. tijd van registreren</t>
   </si>
   <si>
+    <t>Datum en eventueel tijdstip van registreren</t>
+  </si>
+  <si>
     <t>CON-4.1</t>
   </si>
   <si>
@@ -696,13 +861,10 @@
     <t xml:space="preserve">zorgepisode.startdatum </t>
   </si>
   <si>
-    <t>HIS-behoefte: Dit komt overeen met de tijd dat de concern in het patiëntendossier terecht is gekomen. HIS-referentiemodel geeft aan : startdatum episode: DatumTijd=systeemdatum. Datum van het eerste contact van de patiënt met de medisch medewerker over de gezondheidskwestie van de episode. De startdatum betreft de registratie van het eerste item in de episode; cardinaliteit 1</t>
+    <t xml:space="preserve">HIS-behoefte: Dit komt overeen met de tijd dat de concern in het patiëntendossier terecht is gekomen. HIS-referentiemodel geeft aan : startdatum episode: DatumTijd=systeemdatum. Datum van het eerste contact van de patiënt met de medisch medewerker over de gezondheidskwestie van de episode. De startdatum betreft de registratie van het eerste item in de episode; </t>
   </si>
   <si>
     <t>IVL_TS</t>
-  </si>
-  <si>
-    <t>Spoedsamenvatting 2.2.0 (bron: KEZO Overdracht Concern, 2.16.840.1.113883.2.4.3.11.60.66.10.212)</t>
   </si>
   <si>
     <t>CON-5</t>
@@ -741,7 +903,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Aptos Narrow"/>
       </rPr>
-      <t>unknown?</t>
+      <t>unknown(?)</t>
     </r>
     <r>
       <rPr>
@@ -749,62 +911,11 @@
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
       </rPr>
-      <t xml:space="preserve">) </t>
+      <t>)</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
-      </rPr>
-      <t>PAT-301</t>
-    </r>
   </si>
   <si>
     <t>Ja (clinicalStatus)</t>
-  </si>
-  <si>
-    <t>Ja  0..1 (status) Problem/Diagnosis qualifier: Active/inactive met current/pass, mogelijk ook gecombineerd met level of control: Controlled Indeterminate Not controlled. En 'Remission status' Vraag aan Wouter: is dit allemaal te mappen op FHIR-uitwisseling?</t>
-  </si>
-  <si>
-    <t>Ja, ProbleemStatus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://nictiz.atlassian.net/browse/PAT-301 </t>
-  </si>
-  <si>
-    <t>CON-5.2</t>
-  </si>
-  <si>
-    <t>HIS-behoefte: vanuit episode. De status is actief of open, danwel gesloten. bijbehorende problemen worden niet gesloten, maar episode wel. Indien een probleem evolueert, bijvoorbeeld van hoesten naar longontsteking, dan verandert de episodenaam.
-Zib 2017: De probleemstatus beschrijft de toestand van het probleem: Actuele problemen zijn problemen waar de patiënt symptomen van ondervindt of waar bewijsmateriaal voor is.
-Problemen met status 'Niet actueel' verwijzen naar problemen waar de patiënt geen last meer van heeft of waar geen aanwijzingen meer voor zijn.</t>
-  </si>
-  <si>
-    <t>spoedsamenvatting: open, gesloten, gesloten met attentiewaarde (= active/remission/resolved; episodes uit het verleden die niet meer actueel zijn, maar die de huisarts toch in beeld wil houden., bijvoorbeeld hartinfact in verleden.)
-ZIB 2017-ZIB2020: actueel, niet actueel
-ZIB2024: aandoeningOfGesteldheid:Asymptomatisch, Verbeterd, Verslechterd, Onveranderd, Progressief, Opvlammend, Niet meer aanwezig</t>
-  </si>
-  <si>
-    <t>Spoedsamenvatting 2.2.0; Zib 2017; zib 2020</t>
-  </si>
-  <si>
-    <t>CON-6</t>
-  </si>
-  <si>
-    <t>Bron</t>
-  </si>
-  <si>
-    <t>CON-6.1</t>
-  </si>
-  <si>
-    <t>Source</t>
-  </si>
-  <si>
-    <t>De bron van de informatie over de conditie, bijvoorbeeld de patiënt zelf of zijn/haar naaste. Gebruikt in gevallen waarin de patiënt de informatie zelf heeft opgesteld of de auteur door de patiënt verstrekte informatie heeft aangeleverd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gecodeerde concept </t>
   </si>
   <si>
     <r>
@@ -814,7 +925,7 @@
         <rFont val="Aptos Narrow"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Ja (asserter</t>
+      <t xml:space="preserve">Ja  0..1 (status) Problem/Diagnosis qualifier: Active/inactive met current/pass, mogelijk ook gecombineerd met level of control: Controlled Indeterminate Not controlled. En 'Remission status' </t>
     </r>
     <r>
       <rPr>
@@ -823,61 +934,71 @@
         <rFont val="Aptos Narrow"/>
         <scheme val="minor"/>
       </rPr>
-      <t>?</t>
+      <t>Vraag aan Wouter: is dit allemaal te mappen op FHIR-uitwisseling?</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PAT-306</t>
-    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">https://nictiz.atlassian.net/browse/PAT-301 </t>
+  </si>
+  <si>
+    <t>Vraag aan Wouter/Yasmin vanuit EU-core profiel is deze https://hl7.org/fhir/R4/valueset-condition-clinical.html , maar er is ook deze: https://build.fhir.org/ig/HL7/UTG/en/CodeSystem-condition-clinical.html en de id in artdecor is gelijk aan deze. maar de oid aan de eerste. de laatste heeft unknown erbij, welke moet het zijn?</t>
+  </si>
+  <si>
+    <t>CON-5.2</t>
+  </si>
+  <si>
+    <t>HIS-behoefte: vanuit episode. De status is actief of open, danwel gesloten. bijbehorende problemen worden niet gesloten, maar episode wel. Indien een probleem evolueert, bijvoorbeeld van hoesten naar longontsteking, dan verandert de episodenaam.
+Zib 2017: De probleemstatus beschrijft de toestand van het probleem: Actuele problemen zijn problemen waar de patiënt symptomen van ondervindt of waar bewijsmateriaal voor is.
+Problemen met status 'Niet actueel' verwijzen naar problemen waar de patiënt geen last meer van heeft of waar geen aanwijzingen meer voor zijn.</t>
+  </si>
+  <si>
+    <t>spoedsamenvatting: open, gesloten, gesloten met attentiewaarde (= inactive/remission/resolved; episodes uit het verleden die niet meer actueel zijn, maar die de huisarts toch in beeld wil houden., bijvoorbeeld hartinfact in verleden.)
+ZIB 2017-ZIB2020: actueel, niet actueel
+ZIB2024: aandoeningOfGesteldheid:Asymptomatisch, Verbeterd, Verslechterd, Onveranderd, Progressief, Opvlammend, Niet meer aanwezig</t>
+  </si>
+  <si>
+    <t>Spoedsamenvatting 2.2.0
+Zib 2017 
+zib 2020</t>
+  </si>
+  <si>
+    <t>additional binding nog toevoegen</t>
+  </si>
+  <si>
+    <t>CON-6</t>
+  </si>
+  <si>
+    <t>Bron</t>
+  </si>
+  <si>
+    <t>Van wie de informatie over de gezondheidstoestand vandaan komt</t>
+  </si>
+  <si>
+    <t>CON-6.1</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>De bron van de informatie over de conditie, bijvoorbeeld de patiënt zelf of zijn/haar naaste. Gebruikt in gevallen waarin de patiënt de informatie zelf heeft opgesteld of de auteur door de patiënt verstrekte informatie heeft aangeleverd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gecodeerde concept </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ja (asserter) </t>
   </si>
   <si>
     <t>Ja (Reference model: Information Provider) 0..1 Dit kan de patiënt zijn; een vertegenwoordiger van de patiënt, bijvoorbeeld een ouder of voogd; de behandelaar of een apparaat/software.</t>
   </si>
   <si>
-    <t>nee, niet voor elke zib klinisch relevant, en bovendien niet voor elke zib duidelijk wat hiermee bedoeld wordt, met name in relatie tot het element Auteur.</t>
-  </si>
-  <si>
-    <t>ja, informatiebron als basiselement</t>
-  </si>
-  <si>
-    <t>ja met zib registratiegegevens</t>
-  </si>
-  <si>
     <t>[PAT-306] header.source mapping FHIR condition.asserter - BITS - Jira</t>
   </si>
   <si>
+    <t>Dit is antwoord van PAT-306: Vraag 2: type van header.source is een codeableconcept. type van condition.asserter is een referentie naar meerdere profielen... hoe werkt dat? is het wel juist? indien wel juist, gaat dat goed met interoperabliteit? Wat kiezen wij voor in art-decor? Het EU LIM is nooit basismodel. R4 FHIR of openEHR wel. Het EU LIM geeft je een requirement om .source indien afwijkend van .author vast te leggen. Als je FHIR R4 Condition als basismodel gebruikt dan is de koppeling dus een datatype Reference. Reference heeft ook een .type dus als je echter helemaal niets zou weten van de Patient of RelatedPerson, dan zou je Reference.type = Patient of Reference.type = RelatedPerson kunnen zetten. Normaal weet je veel meer van die persoon en kun je dus ook een nette Patient of RelatedPerson resource eraan koppelen. Op logisch-/afspraakmodel zou je uit moeten gaan van Patient en RelatedPerson. Op technisch model kun je de bijzondere situatie dat je echt helemaal niets zou weten van die persoon en dus alleen type kunt weten, specifiek moeten duiden. &gt; Vraag 5: Hoe mappen wij header.source naar FHIR R4 als dit door HL7 Europe in de EHDSMapping al naar .asserter is gemapt? Als FHIR R4 je basismodel levert, dan gebruik je dus ook de Condition.asserter. EHDS levert je vooral requirements voor je basismodel: het is niet het basismodel zelf.</t>
+  </si>
+  <si>
     <t>CON-6.2</t>
-  </si>
-  <si>
-    <t>Information Provider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Een persoon of instantie die de informatie heeft verstrekt. Dit kan de patiënt zijn; een vertegenwoordiger van de patiënt, bijvoorbeeld een ouder of voogd; de behandelaar of een apparaat/software. Het wordt over het algemeen alleen gebruikt wanneer de informatieverstrekker expliciet moet worden vermeld 
-</t>
-  </si>
-  <si>
-    <t>party proxy. referentie na een ID van een:
-* the patient
-* a patient agent, e.g. parent, guardian
-* the clinician
-* a device or software</t>
-  </si>
-  <si>
-    <t>CON-6.3</t>
   </si>
   <si>
     <t>Informatiebron</t>
@@ -899,16 +1020,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Aptos Narrow"/>
       </rPr>
-      <t xml:space="preserve">. of wijzevanverkrijgen?
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-      </rPr>
-      <t>Geen behoefte vanuit spoedsamenvatting om de bron vast te leggen; bron van de informatie zoals beschreven in de LIM is mogelijk wat anders dan bronsysteem 'wie is eigenaar van de vastgestelde aandoening'</t>
+      <t>. of wijzevanverkrijgen?</t>
     </r>
   </si>
   <si>
@@ -928,29 +1040,28 @@
         <color rgb="FFFF0000"/>
         <rFont val="Aptos Narrow"/>
       </rPr>
-      <t xml:space="preserve">of vrije tekst
-</t>
+      <t>of vrije tekst</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-      </rPr>
-      <t>spoedsamenvatting: geen</t>
-    </r>
-  </si>
-  <si>
-    <t>Zib 2017 https://www.zibs.nl/images/2/2a/Architectuurdocument_Registratie_aan_de_bron_-_Volume_1_v1.1.pdf
-ZIB2020
-ZIB2024 https://www.zibs.nl/wiki/RegistratieGegevens-v1.1.2(2024NL)
-spoedsamenvatting</t>
+  </si>
+  <si>
+    <t>Zib 2017
+ZIB 2020
+ZIB 2024</t>
+  </si>
+  <si>
+    <t>Geen behoefte vanuit spoedsamenvatting om de bron vast te leggen; bron van de informatie zoals beschreven in de LIM is mogelijk wat anders dan bronsysteem 'wie is eigenaar van de vastgestelde aandoening'</t>
+  </si>
+  <si>
+    <t>Vraag aan Wouter/Yasmin, hoe krijg je vrije tekst erbij , als vanuit EU-core alleen een referentie kan?</t>
   </si>
   <si>
     <t>CON-7</t>
   </si>
   <si>
     <t>Taal</t>
+  </si>
+  <si>
+    <t>Language</t>
   </si>
   <si>
     <t>De taal waarin het object is geschreven.De taal wordt aangegeven met de IETF-taalcode.</t>
@@ -979,19 +1090,22 @@
     </r>
   </si>
   <si>
+    <t>Vraag staat al uit bij PAT, maar EU-core definieert nu ook een additional binding, dus dat is wat anders dan nationale afspraken. Hoe gaan we daarmee om. voor nu alleen main binding in art-decor</t>
+  </si>
+  <si>
     <t>CON-8</t>
   </si>
   <si>
     <t>Naam van de conditie</t>
   </si>
   <si>
+    <t>De naam van de gezondheidstoestand</t>
+  </si>
+  <si>
     <t>Ja (code, 0..1)</t>
   </si>
   <si>
     <t>Ja (Problem / Diagnosis name)</t>
-  </si>
-  <si>
-    <t>Ja, ProbleemNaam</t>
   </si>
   <si>
     <t>CON-8.1</t>
@@ -1034,6 +1148,11 @@
     <t>Zib 2017, zib 2020</t>
   </si>
   <si>
+    <t>Additional bindings die gelden binnen Nederland:
+DHD Diagnosethesaurus; ICD-10 (dutch translation); SNOMED CT; NANDA-I; ICF; ICPC-1 NL; DSM-IV; DSM-5; GGZ Diagnoselijst
+tijdelijk uit profiel gehaald ivm plugathon</t>
+  </si>
+  <si>
     <t>CON-8.4</t>
   </si>
   <si>
@@ -1050,6 +1169,21 @@
     <t>Spoedsamenvatting 2.2.0 https://referentiemodel.nhg.org/node/1487/volledig/published</t>
   </si>
   <si>
+    <t>CON-8.5</t>
+  </si>
+  <si>
+    <t>Diagnose.DiagnoseNaam</t>
+  </si>
+  <si>
+    <t>De term met bijbehorende code die de zorgverlener kiest uit de gebruikte codelijst met ziekten/condities.</t>
+  </si>
+  <si>
+    <t>Waardelijsten: DHD Diagnosethesaurus, ICD-10, SNOMED CT, ICF, ICPC-1, DMS-IV, DSM-5, GGZ Diagnoselijst</t>
+  </si>
+  <si>
+    <t>Zib 2024 : zie CON-8.1</t>
+  </si>
+  <si>
     <t>CON-9</t>
   </si>
   <si>
@@ -1066,9 +1200,6 @@
   </si>
   <si>
     <t>ja 0..1 Date/time of onset</t>
-  </si>
-  <si>
-    <t>Ja, ProbleemBeginDatum</t>
   </si>
   <si>
     <t>CON-9.1</t>
@@ -1140,9 +1271,6 @@
   </si>
   <si>
     <t>De datum of geschatte datum waarop de conditie in remissie ging of verdween</t>
-  </si>
-  <si>
-    <t>Ja, ProbleemEindDatum</t>
   </si>
   <si>
     <t>CON-10.2</t>
@@ -1183,6 +1311,9 @@
     <t>Categorie(ën) van het probleem (bijv. POA - aanwezig bij opname, HAC - in het ziekenhuis opgelopen aandoening, en andere categorisaties. Door de probleemcategorie te kiezen, kunnen aandoeningen die tijdens het ziekenhuisverblijf zijn ontstaan, worden gemarkeerd. Het is een behoefte uit de discharge report. https://health.ec.europa.eu/system/files/2024-01/ehn_hdr_guidelines_en.pdf</t>
   </si>
   <si>
+    <t>Gecodeerde concept (https://hl7.org/fhir/R4/valueset-condition-category.html)</t>
+  </si>
+  <si>
     <t>Ja (category)</t>
   </si>
   <si>
@@ -1259,19 +1390,16 @@
     <t>Ja Severity (optional)</t>
   </si>
   <si>
+    <t>geen NL behoefte van ZIB2017 en ZIB2020 of spoedsamenvatting voor dit element gevonden om gestructureerd te registeren: Huisartsen registreren de ernst in de episodenaam https://www.nhg.org/wp-content/uploads/2026/04/260033_-Herziene-Richtlijn-ADEPD_v4.pdf.</t>
+  </si>
+  <si>
     <t>CON-13.1</t>
   </si>
   <si>
-    <t>geen NL behoefte van ZIB2017 en ZIB2020 of spoedsamenvatting voor dit element gevonden om gestructureerd te registeren: Huisartsen registreren de ernst in de episodenaam https://www.nhg.org/wp-content/uploads/2026/04/260033_-Herziene-Richtlijn-ADEPD_v4.pdf.</t>
-  </si>
-  <si>
-    <t>CON-13.2</t>
-  </si>
-  <si>
-    <t>Ernst</t>
-  </si>
-  <si>
-    <t>NL behoefte zib2024: element ernst in zib aandoeningofgesteldheid. Duiding van de ernst van de aandoening of gesteldheid. Een aandoening of gesteldheid kan weinig klachten geven en toch ernstig zijn, maar het omgekeerde kan ook. -&gt; Wie deze wens heeft en waarom is niet gevonden in ZIB-project.</t>
+    <t>aandoeningofgesteldheid.Ernst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NL behoefte zib2024: element ernst in zib aandoeningofgesteldheid. Duiding van de ernst van de aandoening of gesteldheid. Een aandoening of gesteldheid kan weinig klachten geven en toch ernstig zijn, maar het omgekeerde kan ook. -&gt; Wie deze wens heeft en waarom is niet gevonden in ZIB-project. Vanuit  </t>
   </si>
   <si>
     <t>Waardelijst: Licht, Licht tot matig, Matig, Matig tot ernstig, Ernstig, Van levensbedreigende ernst, Levensbedreigend, Fataal</t>
@@ -1313,6 +1441,18 @@
     <t>Lateraliteit verbijzondert de anatomische locatie door, indien van toepassing, de zijdigheid vast te leggen, bijvoorbeeld links.</t>
   </si>
   <si>
+    <t>CON-14.3</t>
+  </si>
+  <si>
+    <t>Diagnose.AnatomischeLocatie</t>
+  </si>
+  <si>
+    <t>De plaats(en) op en/of in het lichaam die blijkens de diagnostiek aangedaan is/zijn.</t>
+  </si>
+  <si>
+    <t>ZIB 2024</t>
+  </si>
+  <si>
     <t>CON-15</t>
   </si>
   <si>
@@ -1334,24 +1474,47 @@
     <t>https://nictiz.atlassian.net/browse/PAT-304</t>
   </si>
   <si>
+    <t>CON-15.1</t>
+  </si>
+  <si>
+    <t>Geen data-element vanuit ZIB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NL behoefte ZIB 2017: geen behoefte opgeschreven
+NL behoefte ZIB 2020: geen behoefte opgeschreven
+NL behoefte ZIB 2024: geen behoefte opgeschreven </t>
+  </si>
+  <si>
+    <t>Zib 2017; zib 2020; Zib 2024</t>
+  </si>
+  <si>
+    <t>CON-15-2</t>
+  </si>
+  <si>
+    <t>Geen data-element vanuit HIS</t>
+  </si>
+  <si>
     <t>HIS-behoefte: classificaties , zoals TNM, worden geregistreerd in de eipsodenaam https://www.nhg.org/wp-content/uploads/2026/04/260033_-Herziene-Richtlijn-ADEPD_v4.pdf.</t>
   </si>
   <si>
+    <t>NHG ; https://www.nhg.org/wp-content/uploads/2026/04/260033_-Herziene-Richtlijn-ADEPD_v4.pdf.</t>
+  </si>
+  <si>
     <t>CON-16</t>
   </si>
   <si>
     <t>Status van verificatie van de conditie</t>
   </si>
   <si>
+    <t>Een bewering over de zekerheid die aan een diagnose is verbonden. Diagnostisch en/of klinisch bewijs van een aandoening</t>
+  </si>
+  <si>
     <t>CON-16.1</t>
   </si>
   <si>
     <t>diagnosisAssertionStatus</t>
   </si>
   <si>
-    <t>Een bewering over de zekerheid die aan een diagnose is verbonden. Diagnostisch en/of klinisch bewijs van een aandoening</t>
-  </si>
-  <si>
     <t>Waardelijst (preferred): HL7 Condition Verification Status (unconfirmed, provisional, differential, confirmed, refuted, entered-in-error )</t>
   </si>
   <si>
@@ -1361,58 +1524,129 @@
     <t>Ja? DiagnosticCertainty? proberbly, confermed, supsected OF VIA cluster "Diagnostic status" : Preliminary ; Working ; Established ; Refuted</t>
   </si>
   <si>
-    <t>VerificatieStatus ZIB!</t>
-  </si>
-  <si>
-    <t>CON-P16.2</t>
+    <t>Additional bindings volgens zibs:
+VerificatieCodelijst; 2.16.840.1.113883.2.4.3.11.60.40.2.5.1.4
+tijdelijk uit profiel gehaald ivm plugathon</t>
+  </si>
+  <si>
+    <t>CON-16.2</t>
   </si>
   <si>
     <t>VerificatieStatus</t>
   </si>
   <si>
-    <t>Klinische status van het probleem of de diagnose.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VerificatieStatusCodelijst </t>
+    <t>NL behoefte ZIB 2017:Klinische status van het probleem of de diagnose</t>
+  </si>
+  <si>
+    <t>VerificatieStatusCodelijst 
+Waardelijst met SNOMED kwalificatiewaarden: werk (Suspected -vermoedelijk SNOMED 415684004), Differentiaal (Known possible mogelijk SNOMED 410590009), Bevestigd (Confirmed present  SNOMED 410605003), Uitgesloten (Known absent SNOMED 410516002), Onbekend (Unknown HL7 NullFlavor code system UNK)</t>
+  </si>
+  <si>
+    <t>CON-16.3</t>
+  </si>
+  <si>
+    <t>geen NL-behoefte vanuit spoedsamenvatting: geen behoefte gevonden in de informatieparagraaf: https://www.zorginzicht.nl/kwaliteitsstandaarden/spoedzorgketen-kwaliteitskader
+HIS-behoefte: geen behoefte om deze gestructureerd te registreren. bron: https://referentiemodel.nhg.org/node/5/volledig/published. "Voeg in de vrije tekst bij episodenaam eventueel een werkhypothese of differentiële diagnose toe." bron: https://www.nhg.org/wp-content/uploads/2026/04/260033_-Herziene-Richtlijn-ADEPD_v4.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HIS </t>
   </si>
   <si>
     <t>CON-17</t>
   </si>
   <si>
+    <t>Contactgegevens van specialist</t>
+  </si>
+  <si>
+    <t>Een zorgverlener die specifiek betrokken is bij het probleem, als voorkeurscontactpersoon.</t>
+  </si>
+  <si>
+    <t>Ja note.text/careteam.reason</t>
+  </si>
+  <si>
+    <t>CON-17.1</t>
+  </si>
+  <si>
     <t>specialistContact</t>
   </si>
   <si>
-    <t>Een zorgverlener die specifiek betrokken is bij het probleem, als voorkeurscontactpersoon.</t>
-  </si>
-  <si>
     <t>Verwijzing naar de EHDSHealthProfessional</t>
   </si>
   <si>
-    <t>Ja note.text/careteam.reason</t>
-  </si>
-  <si>
     <t>Onduidelijk, mogelijk other participants mits je aan kan geven dat het een voorkeurscontactpersoon is -&gt; Wouter vragen</t>
   </si>
   <si>
+    <t>Additional bindings volgens zibs:
+ProbleemCodelijst;2.16.840.1.113883.2.4.3.11.60.40.2.5.1.2
+tijdelijk uit profiel gehaald ivm plugathon</t>
+  </si>
+  <si>
+    <t>CON-17.2</t>
+  </si>
+  <si>
+    <t>Geen data-element vanuit Zib</t>
+  </si>
+  <si>
+    <t>Geen behoefte gevonden vanuit Spoedsamenvatting, Zib 2017, Zib 2020, Zib 2024</t>
+  </si>
+  <si>
+    <t>Externe zorgverlener</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve">De Externe zorgverlener bevat de naam- en contactgegevens van een externe zorgverlener en/of zorgorganisatie, die bij de behandeling van de patiënt is betrokken in kader van zorgnetwerk. Naast de presentatierol kan de invoerder aangeven of de zorgverlener de regiebehandelaar is van de patiënt
+</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF467886"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>https://referentiemodel.nhg.org/node/2514/publieksversie/published</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">klasse zorgverlener </t>
+  </si>
+  <si>
     <t>CON-18</t>
   </si>
   <si>
+    <t>Externe bronnen</t>
+  </si>
+  <si>
+    <t>Externe bronnen die specifiek betrekking hebben op het probleem, bijvoorbeeld een link naar een probleem met een zeldzame ziekte en de bijbehorende richtlijnen</t>
+  </si>
+  <si>
+    <t>uri</t>
+  </si>
+  <si>
+    <t>Ja(structureDefinition.extension:relatedArtifact) FMM2</t>
+  </si>
+  <si>
+    <t>ja/nee Guideline Identifier (focust op richtlijnen of breder, LIM is breder)</t>
+  </si>
+  <si>
+    <t>CON-18.1</t>
+  </si>
+  <si>
     <t>externalResource</t>
   </si>
   <si>
-    <t>Externe bronnen die specifiek betrekking hebben op het probleem, bijvoorbeeld een link naar een probleem met een zeldzame ziekte en de bijbehorende richtlijnen</t>
-  </si>
-  <si>
-    <t>uri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0..* </t>
-  </si>
-  <si>
-    <t>Ja(structureDefinition.extension:relatedArtifact) FMM2</t>
-  </si>
-  <si>
-    <t>ja/nee Guideline Identifier (focust op richtlijnen of breder, LIM is breder)</t>
+    <t>CON-18.2</t>
+  </si>
+  <si>
+    <t>Geen data-element vanuit Zib, HIS</t>
+  </si>
+  <si>
+    <t>Geen NL-behoefte gevonden in ZIB, HIS, spoedsamenvatting</t>
   </si>
   <si>
     <t>CON-19</t>
@@ -1427,16 +1661,55 @@
     <t>Ja (comment)</t>
   </si>
   <si>
+    <t>CON-19.1</t>
+  </si>
+  <si>
+    <t>Diagnose.Toelichting</t>
+  </si>
+  <si>
+    <t>Een in vrije tekst geformuleerde toelichting bij de diagnose, die niet wordt gerepresenteerd door de andere dataelementen in het informatiemodel.</t>
+  </si>
+  <si>
+    <t>Zib 2024</t>
+  </si>
+  <si>
+    <t>Actie</t>
+  </si>
+  <si>
+    <t>Notitie</t>
+  </si>
+  <si>
+    <t>[Actie om te ondernemen, kies uit de 3 acties: cluster, andere bouwsteen en modelleren]</t>
+  </si>
+  <si>
+    <t>[Eventuele notitie]</t>
+  </si>
+  <si>
+    <t>[Naam van de informatie-requirement ]</t>
+  </si>
+  <si>
+    <t>CON-9.4</t>
+  </si>
+  <si>
+    <t>AandoeningOfGesteldheid.StatusDatum</t>
+  </si>
+  <si>
+    <t>Het moment vanaf wanneer de gegevens m.b.t. de aandoening of gesteldheid van toepassing zijn. Dit mag een vaag moment zijn.'</t>
+  </si>
+  <si>
     <t>CON-20</t>
   </si>
   <si>
-    <t>NadereSpecificatieProbleemNaam</t>
-  </si>
-  <si>
-    <t>BGZ-MSZ- behoefte: Wat is precies de behoefte van MBZ-MSZ voor een waardelijst als een naderespecificatie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">String en waardelijst </t>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>probleemType</t>
+  </si>
+  <si>
+    <t>Het type probleem</t>
+  </si>
+  <si>
+    <t>Waardelijst: diagnose, symptoom, klacht, functionele beperking, complicatie.</t>
   </si>
   <si>
     <t>Zib 2020; informatiestandaard BgZ-MSZ</t>
@@ -1448,19 +1721,192 @@
     <t>Ja, variant (tekst or coded tekst)</t>
   </si>
   <si>
-    <t>Actie</t>
-  </si>
-  <si>
-    <t>Notitie</t>
-  </si>
-  <si>
-    <t>[Actie om te ondernemen, kies uit de 3 acties: cluster, andere bouwsteen en modelleren]</t>
-  </si>
-  <si>
-    <t>[Eventuele notitie]</t>
-  </si>
-  <si>
-    <t>[Naam van de informatie-requirement ]</t>
+    <t>CON-21</t>
+  </si>
+  <si>
+    <t>symptoom</t>
+  </si>
+  <si>
+    <t>de zorgverlener heeft behoefte om symptomen los van de diagnose van de patient worden vastgesteld</t>
+  </si>
+  <si>
+    <t>string of waardelijst</t>
+  </si>
+  <si>
+    <t>CON-22</t>
+  </si>
+  <si>
+    <t>Periode</t>
+  </si>
+  <si>
+    <t>AandoeningofGesteldheid.PeriodeAanwezig::TijdsInterval</t>
+  </si>
+  <si>
+    <t>De periode waarin de aandoening of gesteldheid aanwezig is (geweest).</t>
+  </si>
+  <si>
+    <t>Tijdsinterval</t>
+  </si>
+  <si>
+    <t>CON-23</t>
+  </si>
+  <si>
+    <t>Beloop</t>
+  </si>
+  <si>
+    <t>AandoeningofGesteldheid.Beloop</t>
+  </si>
+  <si>
+    <t>Het beloop van de aandoening of gesteldheid. Dit staat los van het diagnostisch inzicht m.b.t. de aandoening of gesteldheid. Met het beloop geeft men aan hoe de aandoening of gesteldheid zich ontwikkelt, zoals bijv. stabiel, progressie, remissie, etc..</t>
+  </si>
+  <si>
+    <t>Waardelijst: BeloopCodelijst (Asymptomatisch, Verbeterd, Verslechterd, Onveranderd, Progressief, Opvlammend, Niet meer aanwezig, Anders)</t>
+  </si>
+  <si>
+    <t>Category CON11?</t>
+  </si>
+  <si>
+    <t>CON-24</t>
+  </si>
+  <si>
+    <t>Diagnosesteller</t>
+  </si>
+  <si>
+    <t>Diagnose.DiagnoseSteller::Zorgverlener</t>
+  </si>
+  <si>
+    <t>De zorgverlener die de diagnose heeft gesteld. Dit kan een ander individu zijn dan degene die de diagnose heeft geregistreerd.</t>
+  </si>
+  <si>
+    <t>CON-25</t>
+  </si>
+  <si>
+    <t>DiagnoseDatum</t>
+  </si>
+  <si>
+    <t>Diagnose.DiagnoseDatum</t>
+  </si>
+  <si>
+    <t>Datum (en tijdstip) waarop de zorgverlener tot het inzicht van de diagnose kwam.</t>
+  </si>
+  <si>
+    <t>Verschilt dus van registratiedatum en startdatum</t>
+  </si>
+  <si>
+    <t>CON-26</t>
+  </si>
+  <si>
+    <t>DiagnoseStatus</t>
+  </si>
+  <si>
+    <t>Diagnose.DiagnoseStatus</t>
+  </si>
+  <si>
+    <t>Geeft aan hoe het staat met het diagnostisch proces.</t>
+  </si>
+  <si>
+    <t>Waardelijst: DiagnoseStatusCodelijst (Voorlopige diagnose, Bevestigde diagnose, Differentiaaldiagnose)</t>
+  </si>
+  <si>
+    <t>Anders dan 'Status van het object'</t>
+  </si>
+  <si>
+    <t>CON-27</t>
+  </si>
+  <si>
+    <t>Wijze van vaststellen</t>
+  </si>
+  <si>
+    <t>Diagnose.WijzeVanVaststellen</t>
+  </si>
+  <si>
+    <t>De methode die de zorgverlener heeft gebruikt om de diagnose te stellen, zoals bijv. alleen anamnese, anamnese en lichamelijk onderzoek of  aanvullend onderzoek.</t>
+  </si>
+  <si>
+    <t>Waardelijst: WijzeVanVaststellenCodelijst</t>
+  </si>
+  <si>
+    <t>CON-28</t>
+  </si>
+  <si>
+    <t>NadereSpecificatieDiagnoseNaam</t>
+  </si>
+  <si>
+    <t>Diagnose.NadereSpecificatieDiagnoseNaam</t>
+  </si>
+  <si>
+    <t>Een in vrije tekst geformuleerde nadere detaillering van de DiagnoseNaam, wanneer dit detail niet beschikbaar is via de gebruikte codelijst.</t>
+  </si>
+  <si>
+    <t>CON-29</t>
+  </si>
+  <si>
+    <t>AandoeningOfGesteldheid</t>
+  </si>
+  <si>
+    <t>Diagnose.AandoeningOfGesteldheid</t>
+  </si>
+  <si>
+    <t>De Aandoening of gesteldheid waarop de Diagnose betrekking heeft.</t>
+  </si>
+  <si>
+    <t>CON-30</t>
+  </si>
+  <si>
+    <t>Complicatie</t>
+  </si>
+  <si>
+    <t>Diagnose.IsComplicatie</t>
+  </si>
+  <si>
+    <t>Geeft aan of de diagnose wel of niet een complicatie betreft.</t>
+  </si>
+  <si>
+    <t>CON-31</t>
+  </si>
+  <si>
+    <t>Aanleiding</t>
+  </si>
+  <si>
+    <t>Diagnose.Aanleiding</t>
+  </si>
+  <si>
+    <t>Een zorgverlener kan de behoefte hebben om bij een diagnose een aanleiding vast te leggen. Je kunt beargumenteren dat in feite de aandoening of gesteldheid een aanleiding heeft, maar de specificatie van de aanleiding berust op het inzicht om wat voor aandoening of gesteldheid het gaat. Daarom zien we de aanleiding als onderdeel van de diagnose.
+De aanleiding kan een incident zijn (bijv. een heupfractuur door een val), een verrichting (bijv. een darmperforatie door een colonoscopie) of een andere diagnose (bijv. neuropathie door diabetes). Er kan &gt; 1 Aanleiding zijn: bijv. een fractuur met als aanleiding de combinatie van een val en een aandoening die een verhoogd risico op fracturen met zich meebrengt.
+Los van het de diagnose als duiding van de aard van de aandoening of gesteldheid, kan men tot het inzicht komen dat het een complicatie betreft. Dit kan men apart representeren m.b.v. het element IsComplicatie. Of er sprake is van een complicatie hangt i.h.a. af van de aanleiding, maar er zijn uiteraard ook aanleidingen waarbij er geen sprake is van een complicatie in de zin van onbedoelde schade door medisch handelen.</t>
+  </si>
+  <si>
+    <t>CON-31.1</t>
+  </si>
+  <si>
+    <t>Incident</t>
+  </si>
+  <si>
+    <t>De onbedoelde gebeurtenis tijdens het zorgproces, die tot schade aan de patiënt heeft geleid, had kunnen leiden of (nog) zou kunnen leiden.</t>
+  </si>
+  <si>
+    <t>CON-31.2</t>
+  </si>
+  <si>
+    <t>Verrichting</t>
+  </si>
+  <si>
+    <t>De verrichting die aanleiding heeft gegeven tot de aandoening waarop de diagnose betrekking heeft.</t>
+  </si>
+  <si>
+    <t>CON-31.3</t>
+  </si>
+  <si>
+    <t>Diagnose</t>
+  </si>
+  <si>
+    <t>De diagnose m.b.t. een andere aandoening die als aanleiding wordt gezien voor de aandoening met de onderhavige diagnose.</t>
+  </si>
+  <si>
+    <t>Waardelijst (preferred): e.g. TNM, Bi-Rads, Li-Rads, …</t>
+  </si>
+  <si>
+    <t>Deze e.g. waardelijsten hebben geen OID en kunnen  niet opgenomen worden in AD. Zie PAT-304 ticket</t>
   </si>
   <si>
     <t>In het FHIR profiel is er voor de referentie voor auteur.Device nog geen Device profiel toegevoegd omdat nlcore-device nog niet bestaat. Deze moet tzt wel toegevoegd worden.</t>
@@ -1495,7 +1941,7 @@
   </si>
   <si>
     <t>Dit is een gecodeerde naam, maar dit was ook om voor te sorteren op zib2020. In de mapping naar FHIR is zib2020 uiteindelijk gekozen om deze specificatie in een notitie te zetten, aangezien dat meer was wat gevraagd werd. Zie: https://nictiz.atlassian.net/browse/ZIBFHIR-145. Het voorstel is: Condition.code.text
-Functioneel gezien maken ze gebruik van dezelfde codelijst als ProbleemNaam maar dit element is alleen van toepassing voor medisch specialisten. Onduidelijk wat hiermee bedoeld wordt omdat deze informatiestandaard zich al beperkt tot MSZ. Mogelijk is hier ook geen informatiebehoefte,</t>
+Functioneel gezien maken ze gebruik van dezelfde codelijst als ProbleemNaam maar dit element is alleen van toepassing voor medisch specialisten. Onduidelijk wat hiermee bedoeld wordt omdat deze informatiestandaard zich al beperkt tot MSZ. Mogelijk is hier ook geen informatiebehoefte.</t>
   </si>
   <si>
     <t>Episodetitel</t>
@@ -1533,54 +1979,13 @@
   <si>
     <t>LIMS omschrijving is "	
 The author of the condition information."  Het is gemapt met FHIR: Condition.recorder: de omschrijving is "Individual who recorded the record and takes responsibility for its content." -&gt; de registratie-persoon is niet altijd ook de verantwoordelijke.  Is dit een foute mapping?</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">FHIR Condition Maturity Level: 3 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>&amp;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> openEHR Problem/Diagnosis;latest revision / latest published  53 [1.7.4] 
-Na analyse blijkt FHIR beste keus, want: 
--categorie: bij openEHR zijn de keuzes voor cathegorie niet overeenkomend met de cathegorieen van de LIM -&gt; maar hoeft niet persé een deal-breaker te zijn
-- diagnosisAssertionStatus waardelijst komt niet precies overeen bij openEHR(mist differential en netered-in-error), wel volledige mapping met FHIR
-- stage komt niet precies overeen in openEHR, namelijk via extensie / uitbreiding van archetype Specific Details (cluster?), wel in FHIR
-- nadereSpecificatieProbleemNaam heeft in ZIBFHIR-145 een mapping gekregen op FHIR, maar is duidelijker in openEHR gemodelleerd als "variant" (echter variant is specifieker, dan LIMS/ZIB wil duiden )
--specialistcontact: in openEHR is het onduidelijk, mogelijk other participants mits je aan kan geven dat het een voorkeurscontactpersoon is. in FHIR ook niet ideaal, namelijk note.text of via careteam.reason</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">* Logisch informatie model EHDSCondition versie 1.0.0
-* Verplichte elementen uit FHIR R4 Condition 
-* Verplichte elementen uit openEHR Problem / Diagnosis versie 1.7.4 
-* Zib Probleem uit publicatie 2017 
-* Zib Probleem uit publicatie 2020 
-* Informatiestandaard BgZ-MSZ versie 2.0.2 
-* Usecase Spoedsamenvatting van informatiestandaard Acute Zorg versie 2.2.0 </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1603,6 +2008,13 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
@@ -1658,6 +2070,7 @@
       <sz val="11"/>
       <color rgb="FF242424"/>
       <name val="Aptos Narrow"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1680,7 +2093,6 @@
       <sz val="9"/>
       <color rgb="FF4D4D4D"/>
       <name val="Tahoma"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1705,6 +2117,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1722,8 +2135,32 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF467886"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFE97132"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF292A2E"/>
+      <name val="Atlassian Sans"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1754,8 +2191,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor theme="5" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1789,23 +2238,60 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="5" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="5" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="5" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="5" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="5" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="5" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="5" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="5" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1820,26 +2306,27 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1848,61 +2335,101 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="19">
     <dxf>
       <font>
         <color rgb="FF000000"/>
@@ -1992,12 +2519,6 @@
         <top/>
         <bottom/>
       </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2811,6 +3332,7 @@
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="Chevy Susanto" id="{E6DC4CC4-5331-4633-9C1C-269F406E61BD}" userId="S::chevy.susanto@nictiz.nl::4e93d0cc-e599-42c6-82b7-6ffb715c7e27" providerId="AD"/>
   <person displayName="Marija Zivlak" id="{86017760-9D2E-4C04-A548-4B0AED173840}" userId="S::marija.zivlak@nictiz.nl::bf2ce3ca-25b5-4480-970b-97ae1d2e4e23" providerId="AD"/>
+  <person displayName="Taco Spitters" id="{CAC062D8-726A-469C-9069-224CCD4B5EE1}" userId="S::taco.spitters@nictiz.nl::eff47e48-8544-4500-97c8-7e55e3c068e7" providerId="AD"/>
   <person displayName="Shenaida Hoogland" id="{67CE0BAC-4786-48DE-9DCD-69E1F3FACFC1}" userId="S::shenaida.hoogland@nictiz.nl::5cd1034b-031f-49e9-a727-e4ecba7d58df" providerId="AD"/>
 </personList>
 </file>
@@ -2820,45 +3342,44 @@
   <autoFilter ref="A2:C13" xr:uid="{7AAA9086-205B-4EC4-8920-A2DD04D02676}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{BDCFF82A-D4BE-440B-90DF-AA26F6831D5C}" name="Veld"/>
-    <tableColumn id="2" xr3:uid="{77503B9E-152C-4B39-87F4-D4FBBF1B3BDA}" name="Uitleg" dataDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{B530BE2A-715C-42B8-BFE1-95637D35484B}" name="Beschrijving"/>
+    <tableColumn id="2" xr3:uid="{77503B9E-152C-4B39-87F4-D4FBBF1B3BDA}" name="Beschrijving" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{B530BE2A-715C-42B8-BFE1-95637D35484B}" name="a.d.h.v. keuze FHIR als basismodel"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1B14A882-8085-4978-86D3-1A5B42023C72}" name="Tabel3" displayName="Tabel3" ref="A1:E17" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
-  <autoFilter ref="A1:E17" xr:uid="{1B14A882-8085-4978-86D3-1A5B42023C72}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1B14A882-8085-4978-86D3-1A5B42023C72}" name="Tabel3" displayName="Tabel3" ref="A1:E22" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
+  <autoFilter ref="A1:E22" xr:uid="{1B14A882-8085-4978-86D3-1A5B42023C72}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{2D5F85E5-856C-4A15-8C5D-D8D344B8F13C}" name="Type bron" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{062A7D5A-6D4F-45DD-9A5C-7A2D82A1266A}" name="Naam bron" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{24E64AAE-4BAD-402C-98B7-B46BE371B39E}" name="Toelichting" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{98DE6918-807C-41E0-ACBA-1E2221CF05FC}" name="Informatiebehoefte verwerkt in sheet 'informatiebeheofte'" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{8CFF4D4C-ABDD-49BC-8B49-237193168687}" name="Link naar bron informatie" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{2D5F85E5-856C-4A15-8C5D-D8D344B8F13C}" name="Type bron" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{062A7D5A-6D4F-45DD-9A5C-7A2D82A1266A}" name="Naam bron" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{24E64AAE-4BAD-402C-98B7-B46BE371B39E}" name="Toelichting" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{98DE6918-807C-41E0-ACBA-1E2221CF05FC}" name="Informatiebehoefte verwerkt in sheet 'informatiebeheofte'" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{8CFF4D4C-ABDD-49BC-8B49-237193168687}" name="Link naar bron informatie" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}" name="Tabel6" displayName="Tabel6" ref="A2:N59" totalsRowShown="0" headerRowDxfId="12">
-  <autoFilter ref="A2:N59" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}"/>
-  <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{51E2B1E8-BF1C-4C85-9A83-8C69A4006993}" name="Nummer" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{021C00E0-4FF4-4652-B8E3-674B1F145954}" name="Naam" dataDxfId="10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}" name="Tabel6" displayName="Tabel6" ref="A2:M87" totalsRowShown="0" headerRowDxfId="10">
+  <autoFilter ref="A2:M87" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{51E2B1E8-BF1C-4C85-9A83-8C69A4006993}" name="Nummer" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{021C00E0-4FF4-4652-B8E3-674B1F145954}" name="Naam" dataDxfId="8"/>
     <tableColumn id="12" xr3:uid="{721FE94A-B8C9-44E1-A03C-56E48CDCE2A3}" name="data-element"/>
-    <tableColumn id="3" xr3:uid="{12776FCA-6A89-4E9E-907F-2E30F0D43DA3}" name="Omschrijving" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{9E28C4DB-2A8B-484B-80F1-321440976652}" name="Variabiliteit" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{12776FCA-6A89-4E9E-907F-2E30F0D43DA3}" name="Omschrijving" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{9E28C4DB-2A8B-484B-80F1-321440976652}" name="Variabiliteit" dataDxfId="6"/>
     <tableColumn id="5" xr3:uid="{6FA3E114-7382-4230-B15E-A8DB28B8CE4B}" name="Aanwezigheid"/>
     <tableColumn id="6" xr3:uid="{E8FFDBDF-8B88-4089-89D0-252402D12764}" name="Verleden/heden/toekomst"/>
     <tableColumn id="7" xr3:uid="{BB9C62AB-9839-431A-90A2-B6A6D70DF1FB}" name="Herkomst"/>
     <tableColumn id="8" xr3:uid="{6BE87E7D-EFAE-42FD-9334-11E5EBAC9DC3}" name="Komt het in FHIR R4 voor?"/>
     <tableColumn id="9" xr3:uid="{C6EE00AA-2B37-4BE3-B349-AF61C6E68575}" name="Komt het in openEHR voor?"/>
-    <tableColumn id="10" xr3:uid="{943D4BF3-315C-41FB-99E4-8DB8C54604A4}" name="Komt voor in ZIBProbleem-v4.4? (2020)"/>
-    <tableColumn id="14" xr3:uid="{8B1A7EB4-D690-4A36-9698-ACA592C2A715}" name="Komt voor in ZIBProbleem? (2017)" dataDxfId="7"/>
-    <tableColumn id="13" xr3:uid="{51A57E0A-A216-45BB-973D-E0D8C72BEEEC}" name="Komt voor in ZIBProbleem? (2024)" dataDxfId="6"/>
     <tableColumn id="11" xr3:uid="{E7EDB106-7E3F-4122-A864-3B3AE59C9D87}" name="Opmerking"/>
+    <tableColumn id="10" xr3:uid="{2A08085B-3D25-4805-90D0-47506CCECECF}" name="Kolom1"/>
+    <tableColumn id="13" xr3:uid="{40C0B86E-8EDD-4F57-895D-7FF399948ED0}" name="Kolom2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3213,13 +3734,8 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="K20" dT="2026-07-20T09:26:12.56" personId="{E6DC4CC4-5331-4633-9C1C-269F406E61BD}" id="{B3533A99-0CB6-4646-9417-20A66FEFD573}">
-    <text>1. Actief
-2. Inactief
-Kortere waardelijst</text>
-  </threadedComment>
-  <threadedComment ref="K26" dT="2026-07-20T09:50:58.06" personId="{E6DC4CC4-5331-4633-9C1C-269F406E61BD}" id="{20B2A504-5F6F-4996-9921-E2104F9548D8}">
-    <text>Wel in metadata!</text>
+  <threadedComment ref="A3" dT="2026-07-23T07:54:32.60" personId="{E6DC4CC4-5331-4633-9C1C-269F406E61BD}" id="{FC56F738-FB65-495B-9B48-E0F47216F010}">
+    <text>AllergyInt heeft een andere naam conventie voor ‘Nummer’. Controleren welke juist is.</text>
   </threadedComment>
   <threadedComment ref="E29" dT="2026-07-20T11:55:56.61" personId="{86017760-9D2E-4C04-A548-4B0AED173840}" id="{DC3A08E9-01DD-48D1-B7F5-357810DE5428}">
     <text>Onduidelijk welke waardelijst gehandeerd moet worden</text>
@@ -3230,8 +3746,16 @@
   <threadedComment ref="C31" dT="2026-07-22T10:46:13.79" personId="{67CE0BAC-4786-48DE-9DCD-69E1F3FACFC1}" id="{00D6E7CD-1959-4C9A-8BC1-A1E323A0102F}">
     <text>ter discussie</text>
   </threadedComment>
-  <threadedComment ref="C39" dT="2026-07-22T10:57:31.61" personId="{67CE0BAC-4786-48DE-9DCD-69E1F3FACFC1}" id="{065B39A6-9843-49BF-88E8-0C2BF95F8D00}">
+  <threadedComment ref="C40" dT="2026-07-22T10:57:31.61" personId="{67CE0BAC-4786-48DE-9DCD-69E1F3FACFC1}" id="{065B39A6-9843-49BF-88E8-0C2BF95F8D00}">
     <text>ter discussie</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment3.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="D4" dT="2026-09-07T11:51:51.49" personId="{CAC062D8-726A-469C-9069-224CCD4B5EE1}" id="{75AC27D5-B4F8-442C-9CA0-BF0C6D98019C}">
+    <text>geen voorsortering geweest op de zib 2020. Wij wilden coded, dat is text. Dus zelf toegevoegd aan BgZ-MSZ</text>
   </threadedComment>
 </ThreadedComments>
 </file>
@@ -3239,15 +3763,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F1013F7-63B2-4F83-92B0-1C8153859891}">
   <dimension ref="A1:C19"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="218.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" ht="15" customHeight="1">
       <c r="A1" s="3"/>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:3">
       <c r="B18">
         <f>(510*132.5) + (160*132.5)</f>
         <v>88775</v>
@@ -3256,7 +3780,7 @@
         <v>5832</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:3">
       <c r="B19">
         <f>(542*132.5)</f>
         <v>71815</v>
@@ -3274,138 +3798,138 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CC1E3B3-D087-4A2B-920B-9BA971FAD64B}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
     <col min="2" max="2" width="46.7109375" customWidth="1"/>
-    <col min="3" max="3" width="59.7109375" customWidth="1"/>
+    <col min="3" max="3" width="74.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="190.5" customHeight="1">
       <c r="A1" s="3"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>373</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="81" customHeight="1">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="105" customHeight="1">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="330" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="250.5" customHeight="1">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="60">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="57.75">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="90.75" customHeight="1">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="105">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="135" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="45">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="45">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="315" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="255.75" customHeight="1">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12" s="7"/>
-      <c r="C12" s="3" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C12" s="38" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B13" s="7"/>
     </row>
@@ -3424,220 +3948,351 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8AA88E1-0CFC-4A69-A682-35DA329C9688}">
-  <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.28515625" customWidth="1"/>
     <col min="2" max="2" width="51.28515625" customWidth="1"/>
-    <col min="3" max="3" width="67.28515625" customWidth="1"/>
+    <col min="3" max="3" width="69.85546875" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
     <col min="5" max="5" width="58.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="28.5" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="45">
       <c r="A2" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="30">
+      <c r="A3" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="B3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="45">
+      <c r="A4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="29.25">
+      <c r="A5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="57.75">
+      <c r="A7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="43.5">
+      <c r="A8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" s="37" t="s">
+        <v>64</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="72.75">
+      <c r="A9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="E9" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="30">
+      <c r="A10" s="3" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
+      <c r="B10" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>71</v>
+      </c>
       <c r="E10" s="6"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
+    <row r="11" spans="1:5" ht="30">
+      <c r="A11" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>71</v>
+      </c>
       <c r="E11" s="6"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
+    <row r="12" spans="1:5" ht="30">
+      <c r="A12" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>71</v>
+      </c>
       <c r="E12" s="6"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
+    <row r="13" spans="1:5" ht="30">
+      <c r="A13" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>71</v>
+      </c>
       <c r="E13" s="4"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
+    <row r="14" spans="1:5" ht="30">
+      <c r="A14" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>71</v>
+      </c>
       <c r="E14" s="4"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
+    <row r="15" spans="1:5" ht="30">
+      <c r="A15" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>71</v>
+      </c>
       <c r="E15" s="4"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
+    <row r="16" spans="1:5" ht="30">
+      <c r="A16" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>71</v>
+      </c>
       <c r="E16" s="4"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
+    <row r="17" spans="1:5" ht="30">
+      <c r="A17" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>71</v>
+      </c>
       <c r="E17" s="3"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3"/>
+      <c r="B18" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18" s="38"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+    </row>
+    <row r="19" spans="1:5" ht="30">
+      <c r="A19" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" s="3"/>
+    </row>
+    <row r="20" spans="1:5" ht="30">
+      <c r="A20" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E20" s="3"/>
+    </row>
+    <row r="21" spans="1:5" ht="30">
+      <c r="A21" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E21" s="3"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>83</v>
+      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3646,8 +4301,8 @@
     <hyperlink ref="E7" r:id="rId3" xr:uid="{612DD86C-3891-43E3-B27A-AA6071C8917D}"/>
     <hyperlink ref="E6" r:id="rId4" xr:uid="{104C1F39-D7B8-4AE4-9031-EE6CE3C7F3A7}"/>
     <hyperlink ref="E5" r:id="rId5" xr:uid="{B27B79EC-18DD-4070-9630-609E711CCC3B}"/>
-    <hyperlink ref="E8" r:id="rId6" xr:uid="{20F24860-A30F-4C37-9DE0-9FABA5DC318C}"/>
-    <hyperlink ref="E4" r:id="rId7" display="https://ckm.openehr.org/ckm/archetypes/1013.1.169" xr:uid="{6DB1F6B2-19D1-473C-A11F-4BEC97E8171B}"/>
+    <hyperlink ref="E4" r:id="rId6" display="https://ckm.openehr.org/ckm/archetypes/1013.1.169" xr:uid="{6DB1F6B2-19D1-473C-A11F-4BEC97E8171B}"/>
+    <hyperlink ref="E8" r:id="rId7" xr:uid="{20F24860-A30F-4C37-9DE0-9FABA5DC318C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -3658,1769 +4313,2267 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7034CDAF-2A08-4BE8-92C3-F4E7A6F24E1B}">
-  <dimension ref="A1:O65"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M90"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="1" max="1" width="17.85546875" customWidth="1"/>
     <col min="2" max="2" width="29.28515625" customWidth="1"/>
-    <col min="3" max="3" width="32.7109375" customWidth="1"/>
-    <col min="4" max="4" width="87.42578125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="78" style="3" customWidth="1"/>
+    <col min="3" max="3" width="39" customWidth="1"/>
+    <col min="4" max="4" width="76.7109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" style="3" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
     <col min="7" max="7" width="11.42578125" customWidth="1"/>
     <col min="8" max="8" width="32.42578125" customWidth="1"/>
     <col min="9" max="9" width="28.140625" customWidth="1"/>
     <col min="10" max="10" width="51.28515625" customWidth="1"/>
-    <col min="11" max="11" width="38.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="38.42578125" customWidth="1"/>
-    <col min="14" max="14" width="33.28515625" customWidth="1"/>
+    <col min="11" max="11" width="33.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="99.75" customHeight="1"/>
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="182.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>80</v>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="71.25" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="C3" s="18"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
-      <c r="I3" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="K3" s="19" t="s">
-        <v>84</v>
-      </c>
-      <c r="L3" s="19" t="s">
-        <v>84</v>
-      </c>
-      <c r="M3" s="19" t="s">
-        <v>84</v>
-      </c>
-      <c r="N3" s="19"/>
-      <c r="O3" s="9"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-    </row>
-    <row r="5" spans="1:15" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="B5" s="8"/>
+      <c r="D3" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="92.25" customHeight="1">
+      <c r="A4" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C4" s="19"/>
+      <c r="D4" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="K4" s="20"/>
+      <c r="L4" s="9"/>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="20" t="s">
+        <v>109</v>
+      </c>
       <c r="C5" s="8" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-    </row>
-    <row r="6" spans="1:15" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
-        <v>96</v>
+    </row>
+    <row r="6" spans="1:13" ht="60">
+      <c r="A6" s="20" t="s">
+        <v>115</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
-        <v>41</v>
+        <v>119</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-    </row>
-    <row r="7" spans="1:15" ht="105" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>99</v>
+    </row>
+    <row r="7" spans="1:13" ht="30">
+      <c r="A7" s="20" t="s">
+        <v>120</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>102</v>
+        <v>43</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-    </row>
-    <row r="8" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:13" ht="105.75" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="C8" s="8"/>
+        <v>123</v>
+      </c>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8" t="s">
+        <v>124</v>
+      </c>
       <c r="D8" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F8" s="3"/>
+        <v>125</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>113</v>
+      </c>
       <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
+      <c r="H8" s="3" t="s">
+        <v>127</v>
+      </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>107</v>
-      </c>
+    </row>
+    <row r="9" spans="1:13" ht="29.25">
+      <c r="A9" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="C9" s="8"/>
       <c r="D9" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>109</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="F9" s="3"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="B10" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" ht="43.5">
+      <c r="A10" s="20" t="s">
+        <v>131</v>
+      </c>
       <c r="C10" s="3" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>116</v>
+        <v>133</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>134</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
+        <v>114</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>137</v>
+      </c>
       <c r="K10" s="3"/>
-      <c r="L10" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" ht="75" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="C11" s="10"/>
+    </row>
+    <row r="11" spans="1:13" ht="29.25">
+      <c r="A11" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3" t="s">
+        <v>139</v>
+      </c>
       <c r="D11" s="3" t="s">
-        <v>121</v>
+        <v>140</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>139</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="J11" s="23" t="s">
-        <v>124</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" ht="105" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="C12" s="10"/>
       <c r="D12" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="F12" s="3"/>
+        <v>145</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>146</v>
+      </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" ht="180.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="J12" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="K12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" ht="130.5">
+      <c r="A13" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
-        <v>142</v>
+        <v>56</v>
+      </c>
+      <c r="K13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" ht="180.75" customHeight="1">
+      <c r="A14" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="F14" s="3"/>
+        <v>160</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>161</v>
+      </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>90</v>
+        <v>162</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" ht="135" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>147</v>
+        <v>56</v>
+      </c>
+      <c r="K14" s="3"/>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="20" t="s">
+        <v>164</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="D15" s="23" t="s">
-        <v>150</v>
+        <v>166</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>167</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="F15" s="3"/>
+        <v>168</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>161</v>
+      </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="K15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" ht="135" customHeight="1">
       <c r="A16" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="B16" s="22" t="s">
-        <v>155</v>
-      </c>
-      <c r="C16" s="3"/>
-      <c r="F16" s="3"/>
+        <v>170</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>173</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F16" s="35" t="s">
+        <v>135</v>
+      </c>
       <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
+      <c r="H16" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>71</v>
+      </c>
       <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3" t="s">
-        <v>157</v>
-      </c>
+    </row>
+    <row r="17" spans="1:13" ht="29.25">
+      <c r="A17" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="C17" s="3"/>
       <c r="D17" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>160</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="F17" s="3"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="J17" s="32" t="s">
-        <v>162</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="1:14" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
-        <v>163</v>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+    </row>
+    <row r="18" spans="1:13" ht="54.75" customHeight="1">
+      <c r="A18" s="20" t="s">
+        <v>179</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>89</v>
+        <v>183</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
+        <v>114</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="J18" s="31" t="s">
+        <v>185</v>
+      </c>
       <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="B19" s="22" t="s">
-        <v>169</v>
-      </c>
-      <c r="C19" s="3"/>
+    </row>
+    <row r="19" spans="1:13" ht="85.5" customHeight="1">
+      <c r="A19" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3" t="s">
+        <v>187</v>
+      </c>
       <c r="D19" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="F19" s="3"/>
+        <v>188</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>113</v>
+      </c>
       <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
+      <c r="H19" s="3" t="s">
+        <v>142</v>
+      </c>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="1:14" ht="101.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="B20" s="22" t="s">
-        <v>169</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>172</v>
-      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>191</v>
+      </c>
+      <c r="C20" s="3"/>
       <c r="D20" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E20" s="37" t="s">
-        <v>174</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>89</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="F20" s="3"/>
       <c r="G20" s="3"/>
-      <c r="H20" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="J20" s="20" t="s">
-        <v>176</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="4" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="108" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
-        <v>179</v>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+    </row>
+    <row r="21" spans="1:13" ht="101.25" customHeight="1">
+      <c r="A21" s="20" t="s">
+        <v>193</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>181</v>
+        <v>195</v>
+      </c>
+      <c r="E21" s="36" t="s">
+        <v>196</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3" t="s">
-        <v>182</v>
+        <v>114</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="J21" s="56" t="s">
+        <v>198</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="L21" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="162.75" customHeight="1">
+      <c r="A22" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="C23" s="10"/>
+      <c r="D23" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="24"/>
+      <c r="K23" s="3"/>
+    </row>
+    <row r="24" spans="1:13" ht="57.75">
+      <c r="A24" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="B24" s="3"/>
+      <c r="C24" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="C22" s="10"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="23"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="36"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="1:14" ht="60" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="23" t="s">
-        <v>186</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="I23" s="38" t="s">
-        <v>189</v>
-      </c>
-      <c r="J23" s="23" t="s">
-        <v>190</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="L23" s="36" t="s">
-        <v>192</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="N23" s="5" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="75" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>160</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="I24" s="38"/>
-      <c r="J24" s="23"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="39"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="5"/>
-    </row>
-    <row r="25" spans="1:14" ht="149.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+      <c r="I24" s="37" t="s">
+        <v>213</v>
+      </c>
+      <c r="J24" s="24" t="s">
+        <v>214</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="M24" s="55" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="132.75" customHeight="1">
       <c r="A25" s="9" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="B25" s="3"/>
-      <c r="C25" s="36" t="s">
-        <v>200</v>
-      </c>
-      <c r="D25" s="37" t="s">
-        <v>201</v>
-      </c>
-      <c r="E25" s="37" t="s">
-        <v>202</v>
+      <c r="C25" s="35" t="s">
+        <v>218</v>
+      </c>
+      <c r="D25" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="E25" s="36" t="s">
+        <v>220</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="I25" s="3"/>
-      <c r="J25" s="23"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="1:14" ht="45" x14ac:dyDescent="0.25">
-      <c r="A26" s="19" t="s">
-        <v>204</v>
+      <c r="J25" s="24"/>
+      <c r="K25" s="35" t="s">
+        <v>222</v>
+      </c>
+      <c r="L25" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="43.5">
+      <c r="A26" s="20" t="s">
+        <v>224</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="C26" s="10"/>
+        <v>225</v>
+      </c>
+      <c r="C26" s="38" t="s">
+        <v>226</v>
+      </c>
       <c r="D26" s="3" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="3" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="19" t="s">
-        <v>210</v>
-      </c>
-      <c r="B27" s="22" t="s">
-        <v>211</v>
-      </c>
-      <c r="C27" s="22"/>
+        <v>230</v>
+      </c>
+      <c r="K26" s="3"/>
+      <c r="L26" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>233</v>
+      </c>
+      <c r="C27" s="23"/>
+      <c r="D27" s="3" t="s">
+        <v>234</v>
+      </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3" t="s">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="1:14" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="19" t="s">
-        <v>215</v>
+        <v>236</v>
+      </c>
+      <c r="K27" s="3"/>
+    </row>
+    <row r="28" spans="1:13" ht="47.25" customHeight="1">
+      <c r="A28" s="20" t="s">
+        <v>237</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="I28" s="3"/>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="19" t="s">
-        <v>219</v>
+      <c r="K28" s="3"/>
+    </row>
+    <row r="29" spans="1:13" ht="27.75" customHeight="1">
+      <c r="A29" s="20" t="s">
+        <v>241</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>222</v>
+        <v>244</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="19" t="s">
-        <v>223</v>
+    </row>
+    <row r="30" spans="1:13" ht="123.75" customHeight="1">
+      <c r="A30" s="20" t="s">
+        <v>245</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3" t="s">
-        <v>227</v>
+        <v>249</v>
       </c>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="1:14" ht="219" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="19" t="s">
-        <v>228</v>
+      <c r="K30" s="3" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="243" customHeight="1">
+      <c r="A31" s="20" t="s">
+        <v>251</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>230</v>
+        <v>253</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="G31" s="3"/>
       <c r="H31" s="3" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
-      <c r="L31" s="3"/>
-      <c r="M31" s="3"/>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:13" ht="219" customHeight="1">
       <c r="A32" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>234</v>
-      </c>
-      <c r="C32" s="10"/>
+        <v>256</v>
+      </c>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3" t="s">
+        <v>257</v>
+      </c>
       <c r="D32" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="L32" s="3"/>
-      <c r="M32" s="3"/>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="19" t="s">
-        <v>240</v>
-      </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3" t="s">
-        <v>241</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+    </row>
+    <row r="33" spans="1:11" ht="37.5" customHeight="1">
+      <c r="A33" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="C33" s="10"/>
       <c r="D33" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="1:14" ht="162" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="19" t="s">
-        <v>243</v>
+        <v>263</v>
+      </c>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="K33" s="3"/>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="20" t="s">
+        <v>267</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="3" t="s">
-        <v>244</v>
+        <v>268</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>245</v>
+        <v>269</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>246</v>
+        <v>182</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="I34" s="3"/>
-      <c r="J34" s="31"/>
+        <v>114</v>
+      </c>
       <c r="K34" s="3"/>
-      <c r="L34" s="3"/>
-      <c r="M34" s="3"/>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="1:14" ht="121.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="9" t="s">
-        <v>248</v>
+    </row>
+    <row r="35" spans="1:11" ht="162" customHeight="1">
+      <c r="A35" s="20" t="s">
+        <v>270</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3" t="s">
-        <v>249</v>
+        <v>271</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>250</v>
+        <v>272</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>89</v>
+        <v>183</v>
       </c>
       <c r="G35" s="3"/>
       <c r="H35" s="3" t="s">
-        <v>252</v>
+        <v>274</v>
       </c>
       <c r="I35" s="3"/>
-      <c r="J35" s="3"/>
+      <c r="J35" s="30"/>
       <c r="K35" s="3"/>
-      <c r="L35" s="3"/>
-      <c r="M35" s="3"/>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="36" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:11" ht="121.5" customHeight="1">
       <c r="A36" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="B36" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="C36" s="10"/>
+        <v>275</v>
+      </c>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="D36" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>258</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
       <c r="K36" s="3"/>
-      <c r="L36" s="3"/>
-      <c r="M36" s="3"/>
-      <c r="N36" s="3"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3" t="s">
-        <v>260</v>
-      </c>
+    </row>
+    <row r="37" spans="1:11" ht="30">
+      <c r="A37" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="C37" s="10"/>
       <c r="D37" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="G37" s="3"/>
-      <c r="H37" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="L37" s="3"/>
-      <c r="M37" s="3"/>
-      <c r="N37" s="3"/>
-    </row>
-    <row r="38" spans="1:14" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="19" t="s">
-        <v>263</v>
+        <v>282</v>
+      </c>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="K37" s="3"/>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" s="20" t="s">
+        <v>286</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>265</v>
+        <v>288</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>266</v>
+        <v>182</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="I38" s="3"/>
-      <c r="J38" s="3"/>
+        <v>114</v>
+      </c>
       <c r="K38" s="3"/>
-      <c r="L38" s="3"/>
-      <c r="M38" s="3"/>
-      <c r="N38" s="3"/>
-    </row>
-    <row r="39" spans="1:14" ht="178.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="9" t="s">
-        <v>267</v>
+    </row>
+    <row r="39" spans="1:11" ht="66.75" customHeight="1">
+      <c r="A39" s="20" t="s">
+        <v>289</v>
       </c>
       <c r="B39" s="3"/>
-      <c r="C39" s="34" t="s">
-        <v>268</v>
-      </c>
-      <c r="D39" s="17" t="s">
-        <v>269</v>
+      <c r="C39" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>291</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>159</v>
+        <v>292</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="3" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-      <c r="L39" s="3"/>
-      <c r="M39" s="3"/>
-      <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="1:14" ht="135" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="19" t="s">
-        <v>271</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="C40" s="10"/>
-      <c r="D40" s="3" t="s">
-        <v>273</v>
+    </row>
+    <row r="40" spans="1:11" ht="178.5" customHeight="1">
+      <c r="A40" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="B40" s="3"/>
+      <c r="C40" s="33" t="s">
+        <v>294</v>
+      </c>
+      <c r="D40" s="17" t="s">
+        <v>295</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>109</v>
+        <v>183</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="J40" s="20" t="s">
-        <v>275</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-      <c r="L40" s="3"/>
-      <c r="M40" s="3"/>
-      <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="B41" s="3"/>
+    </row>
+    <row r="41" spans="1:11" ht="135" customHeight="1">
+      <c r="A41" s="20" t="s">
+        <v>297</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>298</v>
+      </c>
       <c r="C41" s="10"/>
       <c r="D41" s="3" t="s">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="3" t="s">
-        <v>279</v>
+        <v>114</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="J41" s="3"/>
+        <v>301</v>
+      </c>
+      <c r="J41" s="21" t="s">
+        <v>302</v>
+      </c>
       <c r="K41" s="3"/>
-      <c r="L41" s="3"/>
-      <c r="M41" s="3"/>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="1:14" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:11" ht="54.75" customHeight="1">
       <c r="A42" s="9" t="s">
-        <v>280</v>
+        <v>303</v>
       </c>
       <c r="B42" s="3"/>
       <c r="C42" s="10"/>
       <c r="D42" s="3" t="s">
-        <v>281</v>
+        <v>304</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>282</v>
+        <v>305</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="I42" s="3"/>
-      <c r="J42" s="3" t="s">
-        <v>284</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="J42" s="3"/>
       <c r="K42" s="3"/>
-      <c r="L42" s="3"/>
-      <c r="M42" s="3"/>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A43" s="19" t="s">
-        <v>285</v>
-      </c>
-      <c r="B43" s="10" t="s">
-        <v>286</v>
-      </c>
+    </row>
+    <row r="43" spans="1:11" ht="124.5" customHeight="1">
+      <c r="A43" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="B43" s="3"/>
       <c r="C43" s="10"/>
       <c r="D43" s="3" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="I43" s="33" t="s">
-        <v>289</v>
-      </c>
-      <c r="J43" s="33" t="s">
-        <v>290</v>
+        <v>310</v>
+      </c>
+      <c r="I43" s="3"/>
+      <c r="J43" s="3" t="s">
+        <v>311</v>
       </c>
       <c r="K43" s="3"/>
-      <c r="L43" s="3"/>
-      <c r="M43" s="3"/>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="1:14" ht="45" x14ac:dyDescent="0.25">
-      <c r="A44" s="9"/>
-      <c r="B44" s="3"/>
+    </row>
+    <row r="44" spans="1:11" ht="115.5">
+      <c r="A44" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>313</v>
+      </c>
       <c r="C44" s="10"/>
       <c r="D44" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="F44" s="3"/>
+        <v>314</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>183</v>
+      </c>
       <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
-      <c r="I44" s="33"/>
-      <c r="J44" s="33"/>
-      <c r="K44" s="3"/>
-      <c r="L44" s="3"/>
-      <c r="M44" s="3"/>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="19" t="s">
-        <v>292</v>
-      </c>
-      <c r="B45" s="10" t="s">
-        <v>293</v>
-      </c>
+      <c r="H44" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I44" s="32" t="s">
+        <v>316</v>
+      </c>
+      <c r="J44" s="32" t="s">
+        <v>317</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" s="9"/>
+      <c r="B45" s="3"/>
       <c r="C45" s="10"/>
-      <c r="D45" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>298</v>
-      </c>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="32"/>
+      <c r="J45" s="32"/>
       <c r="K45" s="3"/>
-      <c r="L45" s="3"/>
-      <c r="M45" s="3"/>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="B46" s="3"/>
+    </row>
+    <row r="46" spans="1:11" ht="37.5" customHeight="1">
+      <c r="A46" s="20" t="s">
+        <v>319</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>320</v>
+      </c>
       <c r="C46" s="10"/>
       <c r="D46" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
-      <c r="I46" s="3"/>
-      <c r="J46" s="3"/>
-      <c r="K46" s="3"/>
-      <c r="L46" s="3"/>
-      <c r="M46" s="3"/>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="1:14" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>321</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="59.25" customHeight="1">
       <c r="A47" s="9" t="s">
-        <v>301</v>
+        <v>327</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="3" t="s">
-        <v>302</v>
+        <v>328</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>303</v>
+        <v>329</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>304</v>
+        <v>330</v>
       </c>
       <c r="F47" s="3">
         <v>1</v>
       </c>
       <c r="G47" s="3"/>
       <c r="H47" s="3" t="s">
-        <v>283</v>
+        <v>310</v>
       </c>
       <c r="I47" s="3"/>
       <c r="J47" s="3"/>
       <c r="K47" s="3"/>
-      <c r="L47" s="3"/>
-      <c r="M47" s="3"/>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A48" s="19" t="s">
-        <v>305</v>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" s="20" t="s">
+        <v>331</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="C48" s="10"/>
       <c r="D48" s="3" t="s">
-        <v>307</v>
+        <v>333</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>308</v>
+        <v>334</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>309</v>
+        <v>335</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>310</v>
+        <v>336</v>
       </c>
       <c r="K48" s="3"/>
-      <c r="L48" s="3"/>
-      <c r="M48" s="3"/>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="19" t="s">
-        <v>311</v>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" s="20" t="s">
+        <v>337</v>
       </c>
       <c r="B49" s="3"/>
       <c r="C49" s="3" t="s">
-        <v>312</v>
+        <v>338</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>313</v>
+        <v>339</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="G49" s="3"/>
       <c r="H49" s="3" t="s">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
       <c r="K49" s="3"/>
-      <c r="L49" s="3"/>
-      <c r="M49" s="3"/>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A50" s="19" t="s">
-        <v>314</v>
-      </c>
-      <c r="B50" s="3"/>
+    </row>
+    <row r="50" spans="1:11" ht="30">
+      <c r="A50" s="20" t="s">
+        <v>340</v>
+      </c>
       <c r="C50" s="3" t="s">
-        <v>315</v>
+        <v>341</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>316</v>
+        <v>342</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="G50" s="3"/>
       <c r="H50" s="3" t="s">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="I50" s="3"/>
       <c r="J50" s="3"/>
       <c r="K50" s="3"/>
-      <c r="L50" s="3"/>
-      <c r="M50" s="3"/>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A51" s="19" t="s">
-        <v>317</v>
-      </c>
-      <c r="B51" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="C51" s="10"/>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3" t="s">
+        <v>344</v>
+      </c>
       <c r="D51" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>320</v>
+        <v>345</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="G51" s="3"/>
       <c r="H51" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="J51" s="24" t="s">
-        <v>322</v>
-      </c>
-      <c r="K51" s="4"/>
-      <c r="L51" s="3"/>
-      <c r="M51" s="3"/>
-      <c r="N51" s="4" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A52" s="9"/>
-      <c r="B52" s="3"/>
+        <v>346</v>
+      </c>
+      <c r="I51" s="3"/>
+      <c r="J51" s="3"/>
+      <c r="K51" s="3"/>
+    </row>
+    <row r="52" spans="1:11" ht="45">
+      <c r="A52" s="20" t="s">
+        <v>347</v>
+      </c>
+      <c r="B52" s="10" t="s">
+        <v>348</v>
+      </c>
       <c r="C52" s="10"/>
       <c r="D52" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="F52" s="3"/>
+        <v>349</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>135</v>
+      </c>
       <c r="G52" s="3"/>
-      <c r="H52" s="3"/>
-      <c r="I52" s="3"/>
-      <c r="J52" s="24"/>
-      <c r="K52" s="4"/>
-      <c r="L52" s="3"/>
-      <c r="M52" s="3"/>
-      <c r="N52" s="4"/>
-    </row>
-    <row r="53" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="H52" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="J52" s="25" t="s">
+        <v>352</v>
+      </c>
+      <c r="K52" s="4" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="45">
       <c r="A53" s="9" t="s">
-        <v>325</v>
-      </c>
-      <c r="B53" s="10" t="s">
-        <v>326</v>
-      </c>
-      <c r="C53" s="10"/>
+        <v>354</v>
+      </c>
+      <c r="B53" s="3"/>
+      <c r="C53" s="38" t="s">
+        <v>355</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>356</v>
+      </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
-      <c r="H53" s="3"/>
+      <c r="H53" s="3" t="s">
+        <v>357</v>
+      </c>
       <c r="I53" s="3"/>
-      <c r="J53" s="23"/>
-      <c r="K53" s="3"/>
-      <c r="L53" s="3"/>
-      <c r="M53" s="3"/>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="1:14" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="19" t="s">
-        <v>327</v>
-      </c>
-      <c r="B54" s="10"/>
-      <c r="C54" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>329</v>
+      <c r="J53" s="24"/>
+      <c r="K53" s="4"/>
+    </row>
+    <row r="54" spans="1:11" ht="45" customHeight="1">
+      <c r="A54" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="B54" s="3"/>
+      <c r="C54" s="38" t="s">
+        <v>359</v>
+      </c>
+      <c r="D54" s="17" t="s">
+        <v>360</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>160</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="F54" s="3"/>
       <c r="G54" s="3"/>
       <c r="H54" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="J54" s="20" t="s">
-        <v>332</v>
-      </c>
-      <c r="K54" s="25" t="s">
-        <v>333</v>
-      </c>
-      <c r="L54" s="25"/>
-      <c r="M54" s="25"/>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+        <v>361</v>
+      </c>
+      <c r="I54" s="3"/>
+      <c r="J54" s="24"/>
+      <c r="K54" s="4"/>
+    </row>
+    <row r="55" spans="1:11" ht="30">
       <c r="A55" s="9" t="s">
-        <v>334</v>
-      </c>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3" t="s">
-        <v>335</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="C55" s="10"/>
       <c r="D55" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>160</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="F55" s="3"/>
       <c r="G55" s="3"/>
-      <c r="H55" s="3" t="s">
-        <v>247</v>
-      </c>
+      <c r="H55" s="3"/>
       <c r="I55" s="3"/>
-      <c r="J55" s="3"/>
-      <c r="K55" s="25"/>
-      <c r="L55" s="17"/>
-      <c r="M55" s="17"/>
-      <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="1:14" ht="45" x14ac:dyDescent="0.25">
-      <c r="A56" s="19" t="s">
-        <v>338</v>
-      </c>
-      <c r="B56" s="10" t="s">
-        <v>339</v>
-      </c>
-      <c r="C56" s="10"/>
+      <c r="J55" s="24"/>
+      <c r="K55" s="3"/>
+    </row>
+    <row r="56" spans="1:11" ht="73.5" customHeight="1">
+      <c r="A56" s="20" t="s">
+        <v>365</v>
+      </c>
+      <c r="B56" s="10"/>
+      <c r="C56" s="3" t="s">
+        <v>366</v>
+      </c>
       <c r="D56" s="3" t="s">
-        <v>340</v>
+        <v>364</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>341</v>
+        <v>367</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>109</v>
+        <v>183</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="I56" s="33" t="s">
-        <v>342</v>
-      </c>
-      <c r="J56" s="20" t="s">
-        <v>343</v>
-      </c>
-      <c r="K56" s="3"/>
-      <c r="L56" s="3"/>
-      <c r="M56" s="3"/>
-      <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A57" s="19" t="s">
-        <v>344</v>
-      </c>
-      <c r="B57" s="10" t="s">
-        <v>345</v>
-      </c>
-      <c r="C57" s="10"/>
+        <v>114</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="J56" s="21" t="s">
+        <v>369</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="102.75" customHeight="1">
+      <c r="A57" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3" t="s">
+        <v>372</v>
+      </c>
       <c r="D57" s="3" t="s">
-        <v>346</v>
+        <v>373</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>347</v>
+        <v>374</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>348</v>
+        <v>183</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3" t="s">
-        <v>90</v>
+        <v>274</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>350</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="J57" s="21"/>
       <c r="K57" s="3"/>
-      <c r="L57" s="3"/>
-      <c r="M57" s="3"/>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="19" t="s">
-        <v>351</v>
-      </c>
-      <c r="B58" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="C58" s="27"/>
+    </row>
+    <row r="58" spans="1:11" ht="124.5" customHeight="1">
+      <c r="A58" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
       <c r="D58" s="3" t="s">
-        <v>352</v>
+        <v>376</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>160</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="F58" s="3"/>
       <c r="G58" s="3"/>
       <c r="H58" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>354</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="I58" s="3"/>
+      <c r="J58" s="3"/>
       <c r="K58" s="3"/>
-      <c r="L58" s="3"/>
-      <c r="M58" s="3"/>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="1:14" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="B59" t="s">
-        <v>356</v>
-      </c>
-      <c r="D59" s="21" t="s">
-        <v>357</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="H59" t="s">
-        <v>359</v>
-      </c>
-      <c r="I59" t="s">
-        <v>360</v>
-      </c>
-      <c r="J59" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B63" s="28"/>
-      <c r="C63" s="28"/>
-    </row>
-    <row r="64" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="29"/>
-      <c r="C64" s="30"/>
-    </row>
-    <row r="65" spans="2:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="28"/>
-      <c r="C65" s="28"/>
+    </row>
+    <row r="59" spans="1:11" ht="29.25">
+      <c r="A59" s="20" t="s">
+        <v>378</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="C59" s="10"/>
+      <c r="D59" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G59" s="3"/>
+      <c r="H59" s="3"/>
+      <c r="I59" s="32" t="s">
+        <v>381</v>
+      </c>
+      <c r="J59" s="3"/>
+      <c r="K59" s="3"/>
+    </row>
+    <row r="60" spans="1:11" ht="72.75">
+      <c r="A60" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="B60" s="3"/>
+      <c r="C60" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G60" s="3"/>
+      <c r="H60" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I60" s="32"/>
+      <c r="J60" s="21" t="s">
+        <v>385</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
+      <c r="A61" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="B61" s="3"/>
+      <c r="C61" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3"/>
+      <c r="H61" s="3"/>
+      <c r="I61" s="32"/>
+      <c r="J61" s="21"/>
+      <c r="K61" s="3"/>
+    </row>
+    <row r="62" spans="1:11" ht="75">
+      <c r="A62" s="9"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="D62" s="49" t="s">
+        <v>391</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G62" s="3"/>
+      <c r="H62" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="I62" s="32"/>
+      <c r="J62" s="21"/>
+      <c r="K62" s="3"/>
+    </row>
+    <row r="63" spans="1:11" ht="30">
+      <c r="A63" s="20" t="s">
+        <v>393</v>
+      </c>
+      <c r="B63" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="C63" s="10"/>
+      <c r="D63" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="G63" s="3"/>
+      <c r="H63" s="3"/>
+      <c r="I63" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="K63" s="3"/>
+    </row>
+    <row r="64" spans="1:11" ht="30">
+      <c r="A64" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="G64" s="3"/>
+      <c r="H64" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I64" s="3"/>
+      <c r="J64" s="3"/>
+      <c r="K64" s="3"/>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="B65" s="3"/>
+      <c r="C65" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="F65" s="3"/>
+      <c r="G65" s="3"/>
+      <c r="H65" s="3"/>
+      <c r="I65" s="3"/>
+      <c r="J65" s="3"/>
+      <c r="K65" s="3"/>
+    </row>
+    <row r="66" spans="1:11" ht="27" customHeight="1">
+      <c r="A66" s="20" t="s">
+        <v>404</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G66" s="3"/>
+      <c r="H66" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="K66" s="3"/>
+    </row>
+    <row r="67" spans="1:11" ht="27" customHeight="1">
+      <c r="A67" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="C67" t="s">
+        <v>409</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G67" s="3"/>
+      <c r="H67" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="I67" s="3"/>
+      <c r="J67" s="3"/>
+      <c r="K67" s="3"/>
+    </row>
+    <row r="68" spans="1:11" ht="30.75" customHeight="1">
+      <c r="A68" s="9"/>
+      <c r="D68" s="22"/>
+    </row>
+    <row r="69" spans="1:11">
+      <c r="A69" s="9"/>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" s="9"/>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" s="9"/>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" s="9"/>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" s="9"/>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="B88" s="27"/>
+      <c r="C88" s="27"/>
+    </row>
+    <row r="89" spans="1:3" ht="15.75" thickBot="1">
+      <c r="B89" s="28"/>
+      <c r="C89" s="29"/>
+    </row>
+    <row r="90" spans="1:3" ht="15.75" thickTop="1">
+      <c r="B90" s="27"/>
+      <c r="C90" s="27"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="N51" r:id="rId1" xr:uid="{F83F3B55-B4C2-4802-934F-C9E3C14B805B}"/>
-    <hyperlink ref="N23" r:id="rId2" xr:uid="{B73C5555-EF90-4C17-AFEA-F4306780E8B3}"/>
-    <hyperlink ref="N20" r:id="rId3" xr:uid="{FEF2826C-4538-4BD0-84C3-18169970B566}"/>
+    <hyperlink ref="K52" r:id="rId1" xr:uid="{F83F3B55-B4C2-4802-934F-C9E3C14B805B}"/>
+    <hyperlink ref="K24" r:id="rId2" xr:uid="{B73C5555-EF90-4C17-AFEA-F4306780E8B3}"/>
+    <hyperlink ref="K21" r:id="rId3" xr:uid="{FEF2826C-4538-4BD0-84C3-18169970B566}"/>
+    <hyperlink ref="D62" r:id="rId4" display="https://referentiemodel.nhg.org/node/2514/publieksversie/published" xr:uid="{492B872A-3084-4D09-AB05-8A8C42E62B8A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
-  <drawing r:id="rId5"/>
-  <legacyDrawing r:id="rId6"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
+  <drawing r:id="rId6"/>
+  <legacyDrawing r:id="rId7"/>
   <tableParts count="1">
-    <tablePart r:id="rId7"/>
+    <tablePart r:id="rId8"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{273AFAA3-99F7-4E93-9580-DCAE2B14D938}">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K22"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.140625" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" customWidth="1"/>
+    <col min="3" max="3" width="36.28515625" customWidth="1"/>
+    <col min="4" max="4" width="46.7109375" customWidth="1"/>
     <col min="5" max="5" width="16.7109375" customWidth="1"/>
     <col min="6" max="6" width="16.42578125" customWidth="1"/>
-    <col min="7" max="7" width="41.42578125" customWidth="1"/>
+    <col min="7" max="7" width="41.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="195.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="195.75" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>362</v>
+        <v>412</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>363</v>
+        <v>413</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
-        <v>364</v>
+        <v>414</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>365</v>
+        <v>415</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>366</v>
+        <v>416</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>79</v>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="71.25" customHeight="1">
+      <c r="A6" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="21" t="s">
+        <v>418</v>
+      </c>
+      <c r="D6" s="43" t="s">
+        <v>419</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+    </row>
+    <row r="7" spans="1:11" ht="71.25" customHeight="1">
+      <c r="A7" s="44" t="s">
+        <v>420</v>
+      </c>
+      <c r="B7" s="39" t="s">
+        <v>421</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="D7" s="50" t="s">
+        <v>423</v>
+      </c>
+      <c r="E7" s="45" t="s">
+        <v>424</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="39" t="s">
+        <v>425</v>
+      </c>
+      <c r="I7" s="39" t="s">
+        <v>426</v>
+      </c>
+      <c r="J7" s="39" t="s">
+        <v>427</v>
+      </c>
+      <c r="K7" s="3"/>
+    </row>
+    <row r="8" spans="1:11" ht="30">
+      <c r="A8" s="44" t="s">
+        <v>428</v>
+      </c>
+      <c r="B8" t="s">
+        <v>429</v>
+      </c>
+      <c r="D8" s="45" t="s">
+        <v>430</v>
+      </c>
+      <c r="E8" t="s">
+        <v>431</v>
+      </c>
+      <c r="F8" t="s">
+        <v>183</v>
+      </c>
+      <c r="H8" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="30">
+      <c r="A9" s="44" t="s">
+        <v>432</v>
+      </c>
+      <c r="B9" s="39" t="s">
+        <v>433</v>
+      </c>
+      <c r="C9" s="39" t="s">
+        <v>434</v>
+      </c>
+      <c r="D9" s="45" t="s">
+        <v>435</v>
+      </c>
+      <c r="E9" s="45" t="s">
+        <v>436</v>
+      </c>
+      <c r="F9" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="G9" s="39"/>
+      <c r="H9" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="I9" s="39"/>
+      <c r="J9" s="39"/>
+      <c r="K9" s="40"/>
+    </row>
+    <row r="10" spans="1:11" ht="165">
+      <c r="A10" s="46" t="s">
+        <v>437</v>
+      </c>
+      <c r="B10" s="41" t="s">
+        <v>438</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>439</v>
+      </c>
+      <c r="D10" s="47" t="s">
+        <v>440</v>
+      </c>
+      <c r="E10" s="47" t="s">
+        <v>441</v>
+      </c>
+      <c r="F10" s="41" t="s">
+        <v>183</v>
+      </c>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41" t="s">
+        <v>411</v>
+      </c>
+      <c r="I10" s="41"/>
+      <c r="J10" s="41"/>
+      <c r="K10" s="42" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="45">
+      <c r="A11" s="44" t="s">
+        <v>443</v>
+      </c>
+      <c r="B11" s="39" t="s">
+        <v>444</v>
+      </c>
+      <c r="C11" s="39" t="s">
+        <v>445</v>
+      </c>
+      <c r="D11" s="45" t="s">
+        <v>446</v>
+      </c>
+      <c r="E11" s="45"/>
+      <c r="F11" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="G11" s="39"/>
+      <c r="H11" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="I11" s="39"/>
+      <c r="J11" s="39"/>
+      <c r="K11" s="40"/>
+    </row>
+    <row r="12" spans="1:11" ht="30">
+      <c r="A12" s="46" t="s">
+        <v>447</v>
+      </c>
+      <c r="B12" s="41" t="s">
+        <v>448</v>
+      </c>
+      <c r="C12" s="41" t="s">
+        <v>449</v>
+      </c>
+      <c r="D12" s="47" t="s">
+        <v>450</v>
+      </c>
+      <c r="E12" s="47"/>
+      <c r="F12" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="G12" s="41"/>
+      <c r="H12" s="41" t="s">
+        <v>411</v>
+      </c>
+      <c r="I12" s="41"/>
+      <c r="J12" s="41"/>
+      <c r="K12" s="42" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="135">
+      <c r="A13" s="44" t="s">
+        <v>452</v>
+      </c>
+      <c r="B13" s="39" t="s">
+        <v>453</v>
+      </c>
+      <c r="C13" s="39" t="s">
+        <v>454</v>
+      </c>
+      <c r="D13" s="45" t="s">
+        <v>455</v>
+      </c>
+      <c r="E13" s="45" t="s">
+        <v>456</v>
+      </c>
+      <c r="F13" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="G13" s="39"/>
+      <c r="H13" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="I13" s="39"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="40" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="60">
+      <c r="A14" s="46" t="s">
+        <v>458</v>
+      </c>
+      <c r="B14" s="41" t="s">
+        <v>459</v>
+      </c>
+      <c r="C14" s="41" t="s">
+        <v>460</v>
+      </c>
+      <c r="D14" s="47" t="s">
+        <v>461</v>
+      </c>
+      <c r="E14" s="47" t="s">
+        <v>462</v>
+      </c>
+      <c r="F14" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41" t="s">
+        <v>411</v>
+      </c>
+      <c r="I14" s="41"/>
+      <c r="J14" s="41"/>
+      <c r="K14" s="42"/>
+    </row>
+    <row r="15" spans="1:11" ht="45">
+      <c r="A15" s="44" t="s">
+        <v>463</v>
+      </c>
+      <c r="B15" s="39" t="s">
+        <v>464</v>
+      </c>
+      <c r="C15" s="39" t="s">
+        <v>465</v>
+      </c>
+      <c r="D15" s="45" t="s">
+        <v>466</v>
+      </c>
+      <c r="E15" s="45" t="s">
+        <v>315</v>
+      </c>
+      <c r="F15" s="39" t="s">
+        <v>183</v>
+      </c>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="40"/>
+    </row>
+    <row r="16" spans="1:11" ht="30">
+      <c r="A16" s="48" t="s">
+        <v>467</v>
+      </c>
+      <c r="B16" s="41" t="s">
+        <v>468</v>
+      </c>
+      <c r="C16" s="41" t="s">
+        <v>469</v>
+      </c>
+      <c r="D16" s="47" t="s">
+        <v>470</v>
+      </c>
+      <c r="E16" s="47"/>
+      <c r="F16" s="41" t="s">
+        <v>183</v>
+      </c>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41" t="s">
+        <v>411</v>
+      </c>
+      <c r="I16" s="41"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="42"/>
+    </row>
+    <row r="17" spans="1:11" ht="30">
+      <c r="A17" s="44" t="s">
+        <v>471</v>
+      </c>
+      <c r="B17" s="39" t="s">
+        <v>472</v>
+      </c>
+      <c r="C17" s="39" t="s">
+        <v>473</v>
+      </c>
+      <c r="D17" s="45" t="s">
+        <v>474</v>
+      </c>
+      <c r="E17" s="45" t="s">
+        <v>309</v>
+      </c>
+      <c r="F17" s="39" t="s">
+        <v>183</v>
+      </c>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="40"/>
+    </row>
+    <row r="18" spans="1:11" ht="89.45" customHeight="1">
+      <c r="A18" s="48" t="s">
+        <v>475</v>
+      </c>
+      <c r="B18" s="41" t="s">
+        <v>476</v>
+      </c>
+      <c r="C18" s="41" t="s">
+        <v>477</v>
+      </c>
+      <c r="D18" s="47" t="s">
+        <v>478</v>
+      </c>
+      <c r="E18" s="47"/>
+      <c r="F18" s="41" t="s">
+        <v>135</v>
+      </c>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41" t="s">
+        <v>411</v>
+      </c>
+      <c r="I18" s="41"/>
+      <c r="J18" s="41"/>
+      <c r="K18" s="42"/>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="44" t="s">
+        <v>479</v>
+      </c>
+      <c r="B19" s="39" t="s">
+        <v>480</v>
+      </c>
+      <c r="C19" s="39" t="s">
+        <v>481</v>
+      </c>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="39"/>
+      <c r="K19" s="40"/>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="46" t="s">
+        <v>482</v>
+      </c>
+      <c r="B20" s="41" t="s">
+        <v>483</v>
+      </c>
+      <c r="C20" s="41" t="s">
+        <v>484</v>
+      </c>
+      <c r="D20" s="47"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="41"/>
+      <c r="K20" s="42"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="44" t="s">
+        <v>485</v>
+      </c>
+      <c r="B21" s="39" t="s">
+        <v>486</v>
+      </c>
+      <c r="C21" s="39" t="s">
+        <v>487</v>
+      </c>
+      <c r="D21" s="45"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="39"/>
+      <c r="K21" s="40"/>
+    </row>
+    <row r="22" spans="1:11" ht="210">
+      <c r="A22" s="51" t="s">
+        <v>347</v>
+      </c>
+      <c r="B22" s="52" t="s">
+        <v>348</v>
+      </c>
+      <c r="C22" s="52"/>
+      <c r="D22" s="45" t="s">
+        <v>349</v>
+      </c>
+      <c r="E22" s="45" t="s">
+        <v>488</v>
+      </c>
+      <c r="F22" s="45" t="s">
+        <v>135</v>
+      </c>
+      <c r="G22" s="45"/>
+      <c r="H22" s="45" t="s">
+        <v>114</v>
+      </c>
+      <c r="I22" s="45"/>
+      <c r="J22" s="53"/>
+      <c r="K22" s="54" t="s">
+        <v>489</v>
       </c>
     </row>
   </sheetData>
@@ -5432,12 +6585,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2489EBC-5098-4697-9724-F190D24E1C3D}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1" ht="111" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" ht="111" customHeight="1"/>
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>367</v>
+        <v>490</v>
       </c>
     </row>
   </sheetData>
@@ -5449,31 +6602,31 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0062C35-A590-498D-8635-16DE3DC0B82A}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="36.42578125" customWidth="1"/>
+    <col min="1" max="1" width="36.5703125" customWidth="1"/>
     <col min="2" max="2" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="B1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="30">
       <c r="A2" t="s">
-        <v>368</v>
+        <v>491</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>370</v>
+        <v>493</v>
       </c>
     </row>
   </sheetData>
@@ -5485,72 +6638,72 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9E8E4E8-143C-4C64-99FB-1306F2338EFB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9E8E4E8-143C-4C64-99FB-1306F2338EFB}">
   <dimension ref="A2:J9"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="27.7109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="27.42578125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="27.5703125" style="3" customWidth="1"/>
     <col min="4" max="4" width="60.140625" style="3" customWidth="1"/>
     <col min="5" max="5" width="47.7109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10">
       <c r="B2" s="15" t="s">
-        <v>371</v>
+        <v>494</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
       <c r="E2" s="12"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10">
       <c r="B3" s="16" t="s">
-        <v>372</v>
+        <v>495</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>373</v>
+        <v>496</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="156" customHeight="1" x14ac:dyDescent="0.25">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="156" customHeight="1">
       <c r="B4" s="14" t="s">
-        <v>375</v>
+        <v>498</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>376</v>
+        <v>499</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>377</v>
+        <v>500</v>
       </c>
       <c r="E4" s="14"/>
     </row>
-    <row r="5" spans="1:10" ht="182.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="182.25" customHeight="1">
       <c r="B5" s="14" t="s">
-        <v>378</v>
+        <v>501</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>279</v>
+        <v>306</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>379</v>
+        <v>502</v>
       </c>
       <c r="E5" s="14"/>
     </row>
-    <row r="6" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="19"/>
+    <row r="6" spans="1:10" ht="45.75" customHeight="1">
+      <c r="A6" s="20"/>
       <c r="B6" s="3" t="s">
-        <v>339</v>
+        <v>383</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>381</v>
+        <v>503</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>504</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
@@ -5558,58 +6711,50 @@
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="30">
       <c r="B7" s="14" t="s">
-        <v>382</v>
+        <v>505</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>380</v>
+        <v>503</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>383</v>
+        <v>506</v>
       </c>
       <c r="E7" s="14"/>
     </row>
-    <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="30">
       <c r="B8" s="14" t="s">
-        <v>384</v>
+        <v>507</v>
       </c>
       <c r="C8" s="14"/>
-      <c r="D8" s="35" t="s">
-        <v>385</v>
+      <c r="D8" s="34" t="s">
+        <v>508</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="90">
       <c r="B9" s="14"/>
       <c r="C9" s="14" t="s">
-        <v>387</v>
+        <v>510</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>388</v>
-      </c>
-      <c r="E9" s="23"/>
+        <v>511</v>
+      </c>
+      <c r="E9" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="bb18a1b9-ddba-4244-9634-64732d0cb267">
@@ -5620,7 +6765,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D5656983173B1142A9B62A9C329F89A7" ma:contentTypeVersion="13" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="71caa5f225d89a4181f0614974a0635b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bb18a1b9-ddba-4244-9634-64732d0cb267" xmlns:ns3="06294a2e-6f87-4144-83b8-94a4d04d144a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d74eef483bec37fcdf125766e7bdb283" ns2:_="" ns3:_="">
     <xsd:import namespace="bb18a1b9-ddba-4244-9634-64732d0cb267"/>
@@ -5827,46 +6972,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{148267B0-4CF5-48A7-B543-CDE45AF0A8FC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E3A9028-3436-4B29-A420-9ED5B8A085B1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E3A9028-3436-4B29-A420-9ED5B8A085B1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="bb18a1b9-ddba-4244-9634-64732d0cb267"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="06294a2e-6f87-4144-83b8-94a4d04d144a"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14B9AD58-A794-48C7-986D-80A9DB4B3205}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14B9AD58-A794-48C7-986D-80A9DB4B3205}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="bb18a1b9-ddba-4244-9634-64732d0cb267"/>
-    <ds:schemaRef ds:uri="06294a2e-6f87-4144-83b8-94a4d04d144a"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{148267B0-4CF5-48A7-B543-CDE45AF0A8FC}"/>
 </file>
--- a/input/requirements/Condition.xlsx
+++ b/input/requirements/Condition.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30613"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nictiznl.sharepoint.com/sites/Zib-transitiecommunity/Gedeelde documenten/Architectuur/Werkgroepen ZIBS 2.0 Implementatie/Bouwblokken/Condition/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edelman_nict1\IGs\GBB-IG\input\requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{89866ED0-A22E-4686-A559-9500B72E2D08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E15BA777-63BA-4A20-8B94-138FB720C249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="3" activeTab="3" xr2:uid="{71855D19-E937-4D4D-85D2-5BCEBB780255}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{71855D19-E937-4D4D-85D2-5BCEBB780255}"/>
   </bookViews>
   <sheets>
     <sheet name="Uitleg" sheetId="5" r:id="rId1"/>
@@ -63,22 +63,33 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={FC56F738-FB65-495B-9B48-E0F47216F010}</author>
+    <author>tc={B3533A99-0CB6-4646-9417-20A66FEFD573}</author>
+    <author>tc={20B2A504-5F6F-4996-9921-E2104F9548D8}</author>
     <author>tc={DC3A08E9-01DD-48D1-B7F5-357810DE5428}</author>
     <author>tc={035A58F6-6A6B-4788-883F-2110C3BA07ED}</author>
     <author>tc={00D6E7CD-1959-4C9A-8BC1-A1E323A0102F}</author>
     <author>tc={065B39A6-9843-49BF-88E8-0C2BF95F8D00}</author>
   </authors>
   <commentList>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{FC56F738-FB65-495B-9B48-E0F47216F010}">
+    <comment ref="K20" authorId="0" shapeId="0" xr:uid="{B3533A99-0CB6-4646-9417-20A66FEFD573}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    AllergyInt heeft een andere naam conventie voor ‘Nummer’. Controleren welke juist is.</t>
+    1. Actief
+2. Inactief
+Kortere waardelijst</t>
       </text>
     </comment>
-    <comment ref="E29" authorId="1" shapeId="0" xr:uid="{DC3A08E9-01DD-48D1-B7F5-357810DE5428}">
+    <comment ref="K26" authorId="1" shapeId="0" xr:uid="{20B2A504-5F6F-4996-9921-E2104F9548D8}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Wel in metadata!</t>
+      </text>
+    </comment>
+    <comment ref="E29" authorId="2" shapeId="0" xr:uid="{DC3A08E9-01DD-48D1-B7F5-357810DE5428}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -86,7 +97,7 @@
     Onduidelijk welke waardelijst gehandeerd moet worden</t>
       </text>
     </comment>
-    <comment ref="B31" authorId="2" shapeId="0" xr:uid="{035A58F6-6A6B-4788-883F-2110C3BA07ED}">
+    <comment ref="B31" authorId="3" shapeId="0" xr:uid="{035A58F6-6A6B-4788-883F-2110C3BA07ED}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -94,7 +105,7 @@
     ter discussie</t>
       </text>
     </comment>
-    <comment ref="C31" authorId="3" shapeId="0" xr:uid="{00D6E7CD-1959-4C9A-8BC1-A1E323A0102F}">
+    <comment ref="C31" authorId="4" shapeId="0" xr:uid="{00D6E7CD-1959-4C9A-8BC1-A1E323A0102F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -102,7 +113,7 @@
     ter discussie</t>
       </text>
     </comment>
-    <comment ref="C40" authorId="4" shapeId="0" xr:uid="{065B39A6-9843-49BF-88E8-0C2BF95F8D00}">
+    <comment ref="C39" authorId="5" shapeId="0" xr:uid="{065B39A6-9843-49BF-88E8-0C2BF95F8D00}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -114,34 +125,13 @@
 </comments>
 </file>
 
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>tc={75AC27D5-B4F8-442C-9CA0-BF0C6D98019C}</author>
-  </authors>
-  <commentList>
-    <comment ref="D4" authorId="0" shapeId="0" xr:uid="{75AC27D5-B4F8-442C-9CA0-BF0C6D98019C}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    geen voorsortering geweest op de zib 2020. Wij wilden coded, dat is text. Dus zelf toegevoegd aan BgZ-MSZ</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="391">
   <si>
     <t>Veld</t>
   </si>
   <si>
     <t>Beschrijving</t>
-  </si>
-  <si>
-    <t>a.d.h.v. keuze FHIR als basismodel</t>
   </si>
   <si>
     <t>Conceptbeschrijving</t>
@@ -173,8 +163,7 @@
 Spoedsamenvatting 2.2.0, bij het opstellen van de episodes en problemen 
 BgZ-MSZ: bij klachten en diagnoses
 eOverdracht: problemen
-Eerstelijnszorg: problemen/episode
-Medicatieproces: om te duiden waarom bepaalde medicatie wordt voorschreven / toegediend</t>
+Eerstelijnszorg: problemen</t>
   </si>
   <si>
     <t>Representatie</t>
@@ -192,7 +181,7 @@
     <t>[Alle bekende synoniemen voor het concept.]</t>
   </si>
   <si>
-    <t>episode, diagnose, aandoening, probleem, klacht(als het geen onderdeel is van de aandoening), functionele beperking, complicatie, symptoom(als het geen onderdeel is van de aandoening, dus alleen als zelfstandig klinisch relevant probleem en niet voor losse of kortdurende symptomen. )</t>
+    <t>episode, diagnose, aandoening, probleem, klacht(als het geen onderdeel is van de aandoening), functionele beperking, complicatie, symptoom(als het geen onderdeel is van de aandoening)</t>
   </si>
   <si>
     <t>Juist gebruik</t>
@@ -210,7 +199,7 @@
     <t>[Beschrijf hier waar het concept niet voor bedoeld is, en geef waar mogelijk aan welk concept er wel geschikt voor is.]</t>
   </si>
   <si>
-    <t>Het concept is niet bedoeld voor losse metingen, bevindingen of kortdurende symptomen of als de symptomen bijdragen  tot het komen van een diagnose/gezondheidstoestand; gebruik hiervoor Observation. Het is ook niet bedoeld om de uitgevoerde ingreep zelf vast te leggen; gebruik daarvoor Procedure. Voor allergieën en intoleranties die klinische beslisondersteuning moeten activeren, is AllergyIntolerance het aangewezen concept. Een blijvende toestand na een ingreep kan wel als conditie worden vastgelegd.</t>
+    <t>Het concept is niet bedoeld voor losse metingen, bevindingen of kortdurende symptomen; gebruik hiervoor Observation. Het is ook niet bedoeld om de uitgevoerde ingreep zelf vast te leggen; gebruik daarvoor Procedure. Voor allergieën en intoleranties die klinische beslisondersteuning moeten activeren, is AllergyIntolerance het aangewezen concept. Een blijvende toestand na een ingreep kan wel als conditie worden vastgelegd.</t>
   </si>
   <si>
     <t>Referenties</t>
@@ -232,42 +221,6 @@
   </si>
   <si>
     <t>Keuze Basismodel</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">FHIR Condition Maturity Level: 3 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>&amp;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> openEHR Problem/Diagnosis;latest revision / latest published  53 [1.7.4] 
-Na analyse blijkt FHIR beste keus, want: 
-- categorie: bij openEHR zijn de keuzes voor categorie niet overeenkomend met de categorieen van de LIM -&gt; maar hoeft niet persé een deal-breaker te zijn
-- diagnosisAssertionStatus waardelijst komt niet precies overeen bij openEHR(mist differential en netered-in-error), wel volledige mapping met FHIR
-- stage komt niet precies overeen in openEHR, namelijk via extensie / uitbreiding van archetype Specific Details (cluster?), wel in FHIR
-- nadereSpecificatieProbleemNaam heeft in ZIBFHIR-145 een mapping gekregen op FHIR, maar is duidelijker in openEHR gemodelleerd als "variant" (echter variant is specifieker, dan LIMS/ZIB wil duiden )
-- specialistcontact: in openEHR is het onduidelijk, mogelijk other participants mits je aan kan geven dat het een voorkeurscontactpersoon is. in FHIR ook niet ideaal, namelijk note.text of via careteam.reason</t>
-    </r>
   </si>
   <si>
     <t>Concept-sheet is opgemaakt met spelregel: https://nictiz.atlassian.net/browse/DAGIM-72</t>
@@ -310,16 +263,13 @@
     <t>Volgens DAGIM-19 is het nodig dat alle verplichte elementen van de FHIR resource opgenomen worden als informatiebehoefte.</t>
   </si>
   <si>
-    <t>Ja, alleen verplichte elementen</t>
-  </si>
-  <si>
     <t xml:space="preserve">openEHR archetype Problem/Diagnosis </t>
   </si>
   <si>
-    <t>Volgens DAGIM-21 l is het nodig dat alle verplichte elementen van de openEHR archetype opgenomen worden als informatiebehoefte. latest published  53 [1.7.4]</t>
-  </si>
-  <si>
-    <t>Clinical Knowledge Manager (openEHR Problem/Diagnosis 1.7.4)</t>
+    <t>Volgens DAGIM-21 l is het nodig dat alle verplichte elementen van de openEHR archetype opgenomen worden als informatiebehoefte.</t>
+  </si>
+  <si>
+    <t>Clinical Knowledge Manager</t>
   </si>
   <si>
     <t>Zib</t>
@@ -331,11 +281,7 @@
     <t>Geen baseline. Onduidelijk of deze meegenomen moet worden. Is het nodig om AandoeningOfGesteldheid en Symptoom uit 2024 ook mee te nemen?</t>
   </si>
   <si>
-    <t>ja, deels</t>
-  </si>
-  <si>
-    <t>Diagnose-v2.0(2024NL) - Zorginformatiebouwstenen 
-https://www.zibs.nl/wiki/RegistratieGegevens-v1.1.2(2024NL)</t>
+    <t>Diagnose-v2.0(2024NL) - Zorginformatiebouwstenen</t>
   </si>
   <si>
     <t>Zib Probleem v4.4 2020</t>
@@ -344,20 +290,13 @@
     <t>Baseline</t>
   </si>
   <si>
-    <t>ja</t>
-  </si>
-  <si>
     <t>Probleem-v4.4(2020NL) - Zorginformatiebouwstenen</t>
   </si>
   <si>
     <t>Zib Probleem V4.1 2017</t>
   </si>
   <si>
-    <t>ja, behoudens data-element probleemtype</t>
-  </si>
-  <si>
-    <t>Probleem-v4.1(2017NL) - Zorginformatiebouwstenen
-https://www.zibs.nl/images/2/2a/Architectuurdocument_Registratie_aan_de_bron_-_Volume_1_v1.1.pdf</t>
+    <t>Probleem-v4.1(2017NL) - Zorginformatiebouwstenen</t>
   </si>
   <si>
     <t>Informatiestandaard</t>
@@ -366,36 +305,7 @@
     <t>Informatiestandaard BgZ-MSZ 2.0.2</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Volgens de DoD Q3 moet dit opgenomen worden in deze iteratie van de GBB. De informatiebehoefte is identiek aan zib 2017 op één element na. Bij dit element</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFE97132"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>staat de informatiestandaard als herkomst beschreven.</t>
-    </r>
-  </si>
-  <si>
-    <t>Ja, behoudens data-element NadereSpecificatieProbleemNaam</t>
+    <t>Volgens de DoD Q3 moet dit opgenomen worden in deze iteratie van de GBB. De informatiebehoefte is identiek aan zib 2017 op één element na. Bij dit element staat de informatiestandaard als herkomst beschreven.</t>
   </si>
   <si>
     <t>Dataset (voor transactie) 2.16.840.1.113883.2.4.3.11.60.42.4.42 - Sturen</t>
@@ -408,80 +318,7 @@
   </si>
   <si>
     <t>https://referentiemodel.nhg.org/
-https://www.nhg.org/wp-content/uploads/2023/02/Richtlijn-Gegevensuitwisseling-acute-zorg-versie-4-2022.pdf
-KEZO Overdracht Concern, 2.16.840.1.113883.2.4.3.11.60.66.10.212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeugdgezondheidszorg </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Volgens de DoD Q3 wordt deze informatiestandaard </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">niet </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>in deze iteratie van de GBB meegenomen</t>
-    </r>
-  </si>
-  <si>
-    <t>nee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vaccinatie-Immunisatie </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MedMij (Zelfmetingen, eAfspraak, PDF/A, Dossierwijzigingsverzoek) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uitkomstgerichte Zorg </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Huisartsenzorg (eerstelijnszorg) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Geboortezorg </t>
-  </si>
-  <si>
-    <t xml:space="preserve">eOverdracht  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BgLz,  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BgGGZ </t>
-  </si>
-  <si>
-    <t>Beeldbeschikbaarheid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Labuitwisseling  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MedicatieProces </t>
-  </si>
-  <si>
-    <t>zie ook scopebepaling: https://nictiznl.sharepoint.com/:w:/r/sites/Zib-transitiecommunity/_layouts/15/Doc.aspx?sourcedoc=%7B638068DB-18FC-40E3-99DD-94FDB108BAB0%7D&amp;file=scopebepaling-condition.docx&amp;action=default&amp;mobileredirect=true</t>
+https://www.nhg.org/wp-content/uploads/2023/02/Richtlijn-Gegevensuitwisseling-acute-zorg-versie-4-2022.pdf</t>
   </si>
   <si>
     <t>Nummer</t>
@@ -514,21 +351,18 @@
     <t>Komt het in openEHR voor?</t>
   </si>
   <si>
+    <t>Komt voor in ZIBProbleem-v4.4? (2020)</t>
+  </si>
+  <si>
+    <t>Komt voor in ZIBProbleem? (2017)</t>
+  </si>
+  <si>
+    <t>Komt voor in ZIBProbleem? (2024)</t>
+  </si>
+  <si>
     <t>Opmerking</t>
   </si>
   <si>
-    <t>Kolom1</t>
-  </si>
-  <si>
-    <t>Kolom2</t>
-  </si>
-  <si>
-    <t>[Nummer van de informatie-requirement start bij 1, sub behoeftes kunnen worden gemodelleerd met X.X of X.X.X]</t>
-  </si>
-  <si>
-    <t>[Naam waaraan de informatie-requirement te herkennen is]</t>
-  </si>
-  <si>
     <t>[Geef hier een tekstuele omschrijving van de behoefte die ingevuld wordt met de informatie-requirement]</t>
   </si>
   <si>
@@ -538,9 +372,6 @@
     <t>[Geef aan in welke situaties het element waarmee de informatie-requirement gedekt wordt er zou moeten zijn, en evt. wanneer het afwezig kan zijn]</t>
   </si>
   <si>
-    <t>[Geef aan of de informatie relevant is voor gebruik van het model voor zaken in het verleden, in het heden, en/of de toekomst. Vaak is slechts een van deze situaties in scope van het bouwblok, maar niet altijd]</t>
-  </si>
-  <si>
     <t>[Geef aan waar de behoefte vandaan komt, bv. een specifieke informatiestandaard of bepaalde zorgrichtlijn]</t>
   </si>
   <si>
@@ -550,15 +381,16 @@
     <t>Patient</t>
   </si>
   <si>
-    <t>Zorgverlener heeft de patient nodig om de gezondheidstoestand aan te koppelen.</t>
-  </si>
-  <si>
     <t>Ja (subject)</t>
   </si>
   <si>
     <t>Ja (Reference model: subject of care) 1:1</t>
   </si>
   <si>
+    <t>Nee, Kenmerken die relevant zijn voor een eenduidige definitie van het concept vormen de dataelementen van de zib. Een zib moet alle mogelijke eigenschappen van dat concept vatten voor zover relevant in gebruik van informatiesystemen binnen het zorg- en gezondheidsdomein
+Kenmerken die wel relevant zijn voor een compleet begrip, maar ook los van het concept herbruikbaar zijn worden als aparte zib middels een relaties vormgegeven</t>
+  </si>
+  <si>
     <t>CON-1.1</t>
   </si>
   <si>
@@ -568,7 +400,7 @@
     <t>De patiënt waarover de gezondheidstoestand gaat</t>
   </si>
   <si>
-    <t>Verwijzing naar EHDSPatient</t>
+    <t>Verwijzing naar Patient</t>
   </si>
   <si>
     <t>1..1</t>
@@ -608,13 +440,10 @@
   </si>
   <si>
     <t>NL-behoefte vanuit zib-2017:Degene op wie de informatie betrekking heeft. Vaak zal dit de patiënt zijn, maar vooral bij kleine kinderen kan het informatie over de ouder of verzorger zijn. Vooral bij de verpleegkundige overdrachten speelt b.v. bekwaamheid en betrokkenheid van mantelzorgers een rol.
-NL-behoefte voor iemand anders dan patient komt te vervallen in zib- 2020:  impliciet is dit altijd de patiënt. In de sporadische gevallen dat de patiënt niet het onderwerp is, is dit in de betreffende zibs al expliciet gemodelleerd, zoals bijvoorbeeld in FamilieAnamnese.</t>
-  </si>
-  <si>
-    <t>Verwijzing naar Patient</t>
-  </si>
-  <si>
-    <t>ZIB 2017
+NL-behoefte komt te vervallen in zib- 2020:  impliciet is dit altijd de patiënt. In de sporadische gevallen dat de patiënt niet het onderwerp is, is dit in de betreffende zibs al expliciet gemodelleerd, zoals bijvoorbeeld in FamilieAnamnese.</t>
+  </si>
+  <si>
+    <t>ZIB 2017  (https://www.zibs.nl/images/2/2a/Architectuurdocument_Registratie_aan_de_bron_-_Volume_1_v1.1.pdf) 
 Spoedsamenvatting 2.2.0</t>
   </si>
   <si>
@@ -636,9 +465,6 @@
     <t>Business identifier van het object</t>
   </si>
   <si>
-    <t>Identifier</t>
-  </si>
-  <si>
     <t>0..*</t>
   </si>
   <si>
@@ -648,6 +474,12 @@
     <t>Ja (architype.id) maar komt niet voor in de archetypen, maar komt naar voren bij het opslaan (originating_system_item_ids : DV_IDENTIFIER). is 0..*</t>
   </si>
   <si>
+    <t>Nee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nee </t>
+  </si>
+  <si>
     <t>CON-2.2</t>
   </si>
   <si>
@@ -669,7 +501,9 @@
     <t>Auteur</t>
   </si>
   <si>
-    <t>De auteur van de informatie over de gezondheidstoestand.</t>
+    <t>De auteur van de informatie over de gezondheidstoestand.
+NL-behoefte voor auteur, informatiebron en vastlegger komt uit 'registratie aan de bron' voor zib2017.
+NL-behoefte komt te vervallen in zib2020</t>
   </si>
   <si>
     <t>0..* Choice of types</t>
@@ -707,6 +541,12 @@
     <t>Ja (RM:other_participations)</t>
   </si>
   <si>
+    <t>Auteur: niet voor elke zib klinisch relevant, en bovendien niet voor elke zib duidelijk wat hiermee bedoeld wordt, met name in relatie tot bron van de informatie en de vastlegger in het dossier.</t>
+  </si>
+  <si>
+    <t>JA, auteur als basiselement</t>
+  </si>
+  <si>
     <t>CON-3.1</t>
   </si>
   <si>
@@ -719,21 +559,22 @@
     <t xml:space="preserve">
 De zorgverlener die de informatie over de conditie invoert/registreert
 NL-behoefte: Waarom/meerwaarde vanuit de spoedsamenvatting; om verschil te maken tussen wie registreert en wie is verantwoordelijke dossierhouder; Er kunnen verschillende zorgverleners werken bij dezelfde organisatie -&gt; niet bekend of dit een informatiebehoefte is uit het zorgveld of uit HL7standaard V3 CDA (custiodian en author) 
-NL-behoefte voor auteur, informatiebron en vastlegger komt uit 'registratie aan de bron' voor zib2017.
-NL-behoefte komt te vervallen in zib2020</t>
+</t>
   </si>
   <si>
     <t>Verwijziging naar EHDSHealthProfessional</t>
   </si>
   <si>
-    <t>EHDS LIM EHDSCondition 1.0.0
-Zib 2017 
+    <t>EHDS LIM EHDSCondition 1.0.0, Zib 2017 (https://www.zibs.nl/images/2/2a/Architectuurdocument_Registratie_aan_de_bron_-_Volume_1_v1.1.pdf) 
 Spoedsamenvatting 2.2.0</t>
   </si>
   <si>
     <t>Ja (recorder = Practitioner of PractitionerRole)</t>
   </si>
   <si>
+    <t>ja</t>
+  </si>
+  <si>
     <t>CON-3.2</t>
   </si>
   <si>
@@ -743,15 +584,12 @@
     <t>authorEHDSOrganisation</t>
   </si>
   <si>
-    <t>De organisatie waaruit de informatie over de conditie afkomstig is.
+    <t xml:space="preserve">De organisatie waaruit de informatie over de conditie afkomstig is.
 NL-behoefte: waarom/meerwaarde vanuit de spoedsamenvatting: om verschil te maken tussen wie registreert en wie is verantwoordelijke dossierhouder; als in er kunnen verschillende zorgverleners werken bij dezelfde organisatie.-&gt; niet bekend of dit een informatiebehoefte is uit het zorgveld of uit  HL7standaard V3 CDA (custiodian en author) 
-NL-behoefte spoedsamenvatting: Bij het sturen van verwijzingen, rapportages, logistieke berichten en ambulanceberichten ligt het initiatief voor gegevensuitwisseling bij de brondossierhouder</t>
+Bij het sturen van verwijzingen, rapportages, logistieke berichten en ambulanceberichten ligt het initiatief voor gegevensuitwisseling bij de brondossierhouder (bron: https://www.nhg.org/wp-content/uploads/2023/02/Richtlijn-Gegevensuitwisseling-acute-zorg-versie-4-2022.pdf ). </t>
   </si>
   <si>
     <t>Verwijziging naar EHDSOrganization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0..* </t>
   </si>
   <si>
     <t>EHDS LIM EHDSCondition 1.0.0
@@ -774,9 +612,6 @@
   </si>
   <si>
     <t>Verwijziging naar EHDSDevice</t>
-  </si>
-  <si>
-    <t>Nee</t>
   </si>
   <si>
     <t>CON-3.4</t>
@@ -822,7 +657,10 @@
     <t>Verwijzing naar patient, zorgverlener, contactpersoon</t>
   </si>
   <si>
-    <t>Zib 2017</t>
+    <t>Zib 2017 (https://www.zibs.nl/images/2/2a/Architectuurdocument_Registratie_aan_de_bron_-_Volume_1_v1.1.pdf)</t>
+  </si>
+  <si>
+    <t>nee</t>
   </si>
   <si>
     <t>CON-4</t>
@@ -831,9 +669,6 @@
     <t>Datum en evt. tijd van registreren</t>
   </si>
   <si>
-    <t>Datum en eventueel tijdstip van registreren</t>
-  </si>
-  <si>
     <t>CON-4.1</t>
   </si>
   <si>
@@ -861,10 +696,13 @@
     <t xml:space="preserve">zorgepisode.startdatum </t>
   </si>
   <si>
-    <t xml:space="preserve">HIS-behoefte: Dit komt overeen met de tijd dat de concern in het patiëntendossier terecht is gekomen. HIS-referentiemodel geeft aan : startdatum episode: DatumTijd=systeemdatum. Datum van het eerste contact van de patiënt met de medisch medewerker over de gezondheidskwestie van de episode. De startdatum betreft de registratie van het eerste item in de episode; </t>
+    <t>HIS-behoefte: Dit komt overeen met de tijd dat de concern in het patiëntendossier terecht is gekomen. HIS-referentiemodel geeft aan : startdatum episode: DatumTijd=systeemdatum. Datum van het eerste contact van de patiënt met de medisch medewerker over de gezondheidskwestie van de episode. De startdatum betreft de registratie van het eerste item in de episode; cardinaliteit 1</t>
   </si>
   <si>
     <t>IVL_TS</t>
+  </si>
+  <si>
+    <t>Spoedsamenvatting 2.2.0 (bron: KEZO Overdracht Concern, 2.16.840.1.113883.2.4.3.11.60.66.10.212)</t>
   </si>
   <si>
     <t>CON-5</t>
@@ -903,7 +741,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="Aptos Narrow"/>
       </rPr>
-      <t>unknown(?)</t>
+      <t>unknown?</t>
     </r>
     <r>
       <rPr>
@@ -911,11 +749,62 @@
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
       </rPr>
-      <t>)</t>
+      <t xml:space="preserve">) </t>
     </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>PAT-301</t>
+    </r>
   </si>
   <si>
     <t>Ja (clinicalStatus)</t>
+  </si>
+  <si>
+    <t>Ja  0..1 (status) Problem/Diagnosis qualifier: Active/inactive met current/pass, mogelijk ook gecombineerd met level of control: Controlled Indeterminate Not controlled. En 'Remission status' Vraag aan Wouter: is dit allemaal te mappen op FHIR-uitwisseling?</t>
+  </si>
+  <si>
+    <t>Ja, ProbleemStatus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://nictiz.atlassian.net/browse/PAT-301 </t>
+  </si>
+  <si>
+    <t>CON-5.2</t>
+  </si>
+  <si>
+    <t>HIS-behoefte: vanuit episode. De status is actief of open, danwel gesloten. bijbehorende problemen worden niet gesloten, maar episode wel. Indien een probleem evolueert, bijvoorbeeld van hoesten naar longontsteking, dan verandert de episodenaam.
+Zib 2017: De probleemstatus beschrijft de toestand van het probleem: Actuele problemen zijn problemen waar de patiënt symptomen van ondervindt of waar bewijsmateriaal voor is.
+Problemen met status 'Niet actueel' verwijzen naar problemen waar de patiënt geen last meer van heeft of waar geen aanwijzingen meer voor zijn.</t>
+  </si>
+  <si>
+    <t>spoedsamenvatting: open, gesloten, gesloten met attentiewaarde (= active/remission/resolved; episodes uit het verleden die niet meer actueel zijn, maar die de huisarts toch in beeld wil houden., bijvoorbeeld hartinfact in verleden.)
+ZIB 2017-ZIB2020: actueel, niet actueel
+ZIB2024: aandoeningOfGesteldheid:Asymptomatisch, Verbeterd, Verslechterd, Onveranderd, Progressief, Opvlammend, Niet meer aanwezig</t>
+  </si>
+  <si>
+    <t>Spoedsamenvatting 2.2.0; Zib 2017; zib 2020</t>
+  </si>
+  <si>
+    <t>CON-6</t>
+  </si>
+  <si>
+    <t>Bron</t>
+  </si>
+  <si>
+    <t>CON-6.1</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>De bron van de informatie over de conditie, bijvoorbeeld de patiënt zelf of zijn/haar naaste. Gebruikt in gevallen waarin de patiënt de informatie zelf heeft opgesteld of de auteur door de patiënt verstrekte informatie heeft aangeleverd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gecodeerde concept </t>
   </si>
   <si>
     <r>
@@ -925,7 +814,7 @@
         <rFont val="Aptos Narrow"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">Ja  0..1 (status) Problem/Diagnosis qualifier: Active/inactive met current/pass, mogelijk ook gecombineerd met level of control: Controlled Indeterminate Not controlled. En 'Remission status' </t>
+      <t>Ja (asserter</t>
     </r>
     <r>
       <rPr>
@@ -934,71 +823,61 @@
         <rFont val="Aptos Narrow"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Vraag aan Wouter: is dit allemaal te mappen op FHIR-uitwisseling?</t>
+      <t>?</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">https://nictiz.atlassian.net/browse/PAT-301 </t>
-  </si>
-  <si>
-    <t>Vraag aan Wouter/Yasmin vanuit EU-core profiel is deze https://hl7.org/fhir/R4/valueset-condition-clinical.html , maar er is ook deze: https://build.fhir.org/ig/HL7/UTG/en/CodeSystem-condition-clinical.html en de id in artdecor is gelijk aan deze. maar de oid aan de eerste. de laatste heeft unknown erbij, welke moet het zijn?</t>
-  </si>
-  <si>
-    <t>CON-5.2</t>
-  </si>
-  <si>
-    <t>HIS-behoefte: vanuit episode. De status is actief of open, danwel gesloten. bijbehorende problemen worden niet gesloten, maar episode wel. Indien een probleem evolueert, bijvoorbeeld van hoesten naar longontsteking, dan verandert de episodenaam.
-Zib 2017: De probleemstatus beschrijft de toestand van het probleem: Actuele problemen zijn problemen waar de patiënt symptomen van ondervindt of waar bewijsmateriaal voor is.
-Problemen met status 'Niet actueel' verwijzen naar problemen waar de patiënt geen last meer van heeft of waar geen aanwijzingen meer voor zijn.</t>
-  </si>
-  <si>
-    <t>spoedsamenvatting: open, gesloten, gesloten met attentiewaarde (= inactive/remission/resolved; episodes uit het verleden die niet meer actueel zijn, maar die de huisarts toch in beeld wil houden., bijvoorbeeld hartinfact in verleden.)
-ZIB 2017-ZIB2020: actueel, niet actueel
-ZIB2024: aandoeningOfGesteldheid:Asymptomatisch, Verbeterd, Verslechterd, Onveranderd, Progressief, Opvlammend, Niet meer aanwezig</t>
-  </si>
-  <si>
-    <t>Spoedsamenvatting 2.2.0
-Zib 2017 
-zib 2020</t>
-  </si>
-  <si>
-    <t>additional binding nog toevoegen</t>
-  </si>
-  <si>
-    <t>CON-6</t>
-  </si>
-  <si>
-    <t>Bron</t>
-  </si>
-  <si>
-    <t>Van wie de informatie over de gezondheidstoestand vandaan komt</t>
-  </si>
-  <si>
-    <t>CON-6.1</t>
-  </si>
-  <si>
-    <t>Source</t>
-  </si>
-  <si>
-    <t>De bron van de informatie over de conditie, bijvoorbeeld de patiënt zelf of zijn/haar naaste. Gebruikt in gevallen waarin de patiënt de informatie zelf heeft opgesteld of de auteur door de patiënt verstrekte informatie heeft aangeleverd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gecodeerde concept </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ja (asserter) </t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PAT-306</t>
+    </r>
   </si>
   <si>
     <t>Ja (Reference model: Information Provider) 0..1 Dit kan de patiënt zijn; een vertegenwoordiger van de patiënt, bijvoorbeeld een ouder of voogd; de behandelaar of een apparaat/software.</t>
   </si>
   <si>
+    <t>nee, niet voor elke zib klinisch relevant, en bovendien niet voor elke zib duidelijk wat hiermee bedoeld wordt, met name in relatie tot het element Auteur.</t>
+  </si>
+  <si>
+    <t>ja, informatiebron als basiselement</t>
+  </si>
+  <si>
+    <t>ja met zib registratiegegevens</t>
+  </si>
+  <si>
     <t>[PAT-306] header.source mapping FHIR condition.asserter - BITS - Jira</t>
   </si>
   <si>
-    <t>Dit is antwoord van PAT-306: Vraag 2: type van header.source is een codeableconcept. type van condition.asserter is een referentie naar meerdere profielen... hoe werkt dat? is het wel juist? indien wel juist, gaat dat goed met interoperabliteit? Wat kiezen wij voor in art-decor? Het EU LIM is nooit basismodel. R4 FHIR of openEHR wel. Het EU LIM geeft je een requirement om .source indien afwijkend van .author vast te leggen. Als je FHIR R4 Condition als basismodel gebruikt dan is de koppeling dus een datatype Reference. Reference heeft ook een .type dus als je echter helemaal niets zou weten van de Patient of RelatedPerson, dan zou je Reference.type = Patient of Reference.type = RelatedPerson kunnen zetten. Normaal weet je veel meer van die persoon en kun je dus ook een nette Patient of RelatedPerson resource eraan koppelen. Op logisch-/afspraakmodel zou je uit moeten gaan van Patient en RelatedPerson. Op technisch model kun je de bijzondere situatie dat je echt helemaal niets zou weten van die persoon en dus alleen type kunt weten, specifiek moeten duiden. &gt; Vraag 5: Hoe mappen wij header.source naar FHIR R4 als dit door HL7 Europe in de EHDSMapping al naar .asserter is gemapt? Als FHIR R4 je basismodel levert, dan gebruik je dus ook de Condition.asserter. EHDS levert je vooral requirements voor je basismodel: het is niet het basismodel zelf.</t>
-  </si>
-  <si>
     <t>CON-6.2</t>
+  </si>
+  <si>
+    <t>Information Provider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Een persoon of instantie die de informatie heeft verstrekt. Dit kan de patiënt zijn; een vertegenwoordiger van de patiënt, bijvoorbeeld een ouder of voogd; de behandelaar of een apparaat/software. Het wordt over het algemeen alleen gebruikt wanneer de informatieverstrekker expliciet moet worden vermeld 
+</t>
+  </si>
+  <si>
+    <t>party proxy. referentie na een ID van een:
+* the patient
+* a patient agent, e.g. parent, guardian
+* the clinician
+* a device or software</t>
+  </si>
+  <si>
+    <t>CON-6.3</t>
   </si>
   <si>
     <t>Informatiebron</t>
@@ -1020,7 +899,16 @@
         <color rgb="FFFF0000"/>
         <rFont val="Aptos Narrow"/>
       </rPr>
-      <t>. of wijzevanverkrijgen?</t>
+      <t xml:space="preserve">. of wijzevanverkrijgen?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>Geen behoefte vanuit spoedsamenvatting om de bron vast te leggen; bron van de informatie zoals beschreven in de LIM is mogelijk wat anders dan bronsysteem 'wie is eigenaar van de vastgestelde aandoening'</t>
     </r>
   </si>
   <si>
@@ -1040,28 +928,29 @@
         <color rgb="FFFF0000"/>
         <rFont val="Aptos Narrow"/>
       </rPr>
-      <t>of vrije tekst</t>
+      <t xml:space="preserve">of vrije tekst
+</t>
     </r>
-  </si>
-  <si>
-    <t>Zib 2017
-ZIB 2020
-ZIB 2024</t>
-  </si>
-  <si>
-    <t>Geen behoefte vanuit spoedsamenvatting om de bron vast te leggen; bron van de informatie zoals beschreven in de LIM is mogelijk wat anders dan bronsysteem 'wie is eigenaar van de vastgestelde aandoening'</t>
-  </si>
-  <si>
-    <t>Vraag aan Wouter/Yasmin, hoe krijg je vrije tekst erbij , als vanuit EU-core alleen een referentie kan?</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>spoedsamenvatting: geen</t>
+    </r>
+  </si>
+  <si>
+    <t>Zib 2017 https://www.zibs.nl/images/2/2a/Architectuurdocument_Registratie_aan_de_bron_-_Volume_1_v1.1.pdf
+ZIB2020
+ZIB2024 https://www.zibs.nl/wiki/RegistratieGegevens-v1.1.2(2024NL)
+spoedsamenvatting</t>
   </si>
   <si>
     <t>CON-7</t>
   </si>
   <si>
     <t>Taal</t>
-  </si>
-  <si>
-    <t>Language</t>
   </si>
   <si>
     <t>De taal waarin het object is geschreven.De taal wordt aangegeven met de IETF-taalcode.</t>
@@ -1090,22 +979,19 @@
     </r>
   </si>
   <si>
-    <t>Vraag staat al uit bij PAT, maar EU-core definieert nu ook een additional binding, dus dat is wat anders dan nationale afspraken. Hoe gaan we daarmee om. voor nu alleen main binding in art-decor</t>
-  </si>
-  <si>
     <t>CON-8</t>
   </si>
   <si>
     <t>Naam van de conditie</t>
   </si>
   <si>
-    <t>De naam van de gezondheidstoestand</t>
-  </si>
-  <si>
     <t>Ja (code, 0..1)</t>
   </si>
   <si>
     <t>Ja (Problem / Diagnosis name)</t>
+  </si>
+  <si>
+    <t>Ja, ProbleemNaam</t>
   </si>
   <si>
     <t>CON-8.1</t>
@@ -1148,11 +1034,6 @@
     <t>Zib 2017, zib 2020</t>
   </si>
   <si>
-    <t>Additional bindings die gelden binnen Nederland:
-DHD Diagnosethesaurus; ICD-10 (dutch translation); SNOMED CT; NANDA-I; ICF; ICPC-1 NL; DSM-IV; DSM-5; GGZ Diagnoselijst
-tijdelijk uit profiel gehaald ivm plugathon</t>
-  </si>
-  <si>
     <t>CON-8.4</t>
   </si>
   <si>
@@ -1169,21 +1050,6 @@
     <t>Spoedsamenvatting 2.2.0 https://referentiemodel.nhg.org/node/1487/volledig/published</t>
   </si>
   <si>
-    <t>CON-8.5</t>
-  </si>
-  <si>
-    <t>Diagnose.DiagnoseNaam</t>
-  </si>
-  <si>
-    <t>De term met bijbehorende code die de zorgverlener kiest uit de gebruikte codelijst met ziekten/condities.</t>
-  </si>
-  <si>
-    <t>Waardelijsten: DHD Diagnosethesaurus, ICD-10, SNOMED CT, ICF, ICPC-1, DMS-IV, DSM-5, GGZ Diagnoselijst</t>
-  </si>
-  <si>
-    <t>Zib 2024 : zie CON-8.1</t>
-  </si>
-  <si>
     <t>CON-9</t>
   </si>
   <si>
@@ -1200,6 +1066,9 @@
   </si>
   <si>
     <t>ja 0..1 Date/time of onset</t>
+  </si>
+  <si>
+    <t>Ja, ProbleemBeginDatum</t>
   </si>
   <si>
     <t>CON-9.1</t>
@@ -1271,6 +1140,9 @@
   </si>
   <si>
     <t>De datum of geschatte datum waarop de conditie in remissie ging of verdween</t>
+  </si>
+  <si>
+    <t>Ja, ProbleemEindDatum</t>
   </si>
   <si>
     <t>CON-10.2</t>
@@ -1311,9 +1183,6 @@
     <t>Categorie(ën) van het probleem (bijv. POA - aanwezig bij opname, HAC - in het ziekenhuis opgelopen aandoening, en andere categorisaties. Door de probleemcategorie te kiezen, kunnen aandoeningen die tijdens het ziekenhuisverblijf zijn ontstaan, worden gemarkeerd. Het is een behoefte uit de discharge report. https://health.ec.europa.eu/system/files/2024-01/ehn_hdr_guidelines_en.pdf</t>
   </si>
   <si>
-    <t>Gecodeerde concept (https://hl7.org/fhir/R4/valueset-condition-category.html)</t>
-  </si>
-  <si>
     <t>Ja (category)</t>
   </si>
   <si>
@@ -1390,16 +1259,19 @@
     <t>Ja Severity (optional)</t>
   </si>
   <si>
+    <t>CON-13.1</t>
+  </si>
+  <si>
     <t>geen NL behoefte van ZIB2017 en ZIB2020 of spoedsamenvatting voor dit element gevonden om gestructureerd te registeren: Huisartsen registreren de ernst in de episodenaam https://www.nhg.org/wp-content/uploads/2026/04/260033_-Herziene-Richtlijn-ADEPD_v4.pdf.</t>
   </si>
   <si>
-    <t>CON-13.1</t>
-  </si>
-  <si>
-    <t>aandoeningofgesteldheid.Ernst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NL behoefte zib2024: element ernst in zib aandoeningofgesteldheid. Duiding van de ernst van de aandoening of gesteldheid. Een aandoening of gesteldheid kan weinig klachten geven en toch ernstig zijn, maar het omgekeerde kan ook. -&gt; Wie deze wens heeft en waarom is niet gevonden in ZIB-project. Vanuit  </t>
+    <t>CON-13.2</t>
+  </si>
+  <si>
+    <t>Ernst</t>
+  </si>
+  <si>
+    <t>NL behoefte zib2024: element ernst in zib aandoeningofgesteldheid. Duiding van de ernst van de aandoening of gesteldheid. Een aandoening of gesteldheid kan weinig klachten geven en toch ernstig zijn, maar het omgekeerde kan ook. -&gt; Wie deze wens heeft en waarom is niet gevonden in ZIB-project.</t>
   </si>
   <si>
     <t>Waardelijst: Licht, Licht tot matig, Matig, Matig tot ernstig, Ernstig, Van levensbedreigende ernst, Levensbedreigend, Fataal</t>
@@ -1441,18 +1313,6 @@
     <t>Lateraliteit verbijzondert de anatomische locatie door, indien van toepassing, de zijdigheid vast te leggen, bijvoorbeeld links.</t>
   </si>
   <si>
-    <t>CON-14.3</t>
-  </si>
-  <si>
-    <t>Diagnose.AnatomischeLocatie</t>
-  </si>
-  <si>
-    <t>De plaats(en) op en/of in het lichaam die blijkens de diagnostiek aangedaan is/zijn.</t>
-  </si>
-  <si>
-    <t>ZIB 2024</t>
-  </si>
-  <si>
     <t>CON-15</t>
   </si>
   <si>
@@ -1474,47 +1334,24 @@
     <t>https://nictiz.atlassian.net/browse/PAT-304</t>
   </si>
   <si>
-    <t>CON-15.1</t>
-  </si>
-  <si>
-    <t>Geen data-element vanuit ZIB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NL behoefte ZIB 2017: geen behoefte opgeschreven
-NL behoefte ZIB 2020: geen behoefte opgeschreven
-NL behoefte ZIB 2024: geen behoefte opgeschreven </t>
-  </si>
-  <si>
-    <t>Zib 2017; zib 2020; Zib 2024</t>
-  </si>
-  <si>
-    <t>CON-15-2</t>
-  </si>
-  <si>
-    <t>Geen data-element vanuit HIS</t>
-  </si>
-  <si>
     <t>HIS-behoefte: classificaties , zoals TNM, worden geregistreerd in de eipsodenaam https://www.nhg.org/wp-content/uploads/2026/04/260033_-Herziene-Richtlijn-ADEPD_v4.pdf.</t>
   </si>
   <si>
-    <t>NHG ; https://www.nhg.org/wp-content/uploads/2026/04/260033_-Herziene-Richtlijn-ADEPD_v4.pdf.</t>
-  </si>
-  <si>
     <t>CON-16</t>
   </si>
   <si>
     <t>Status van verificatie van de conditie</t>
   </si>
   <si>
+    <t>CON-16.1</t>
+  </si>
+  <si>
+    <t>diagnosisAssertionStatus</t>
+  </si>
+  <si>
     <t>Een bewering over de zekerheid die aan een diagnose is verbonden. Diagnostisch en/of klinisch bewijs van een aandoening</t>
   </si>
   <si>
-    <t>CON-16.1</t>
-  </si>
-  <si>
-    <t>diagnosisAssertionStatus</t>
-  </si>
-  <si>
     <t>Waardelijst (preferred): HL7 Condition Verification Status (unconfirmed, provisional, differential, confirmed, refuted, entered-in-error )</t>
   </si>
   <si>
@@ -1524,102 +1361,43 @@
     <t>Ja? DiagnosticCertainty? proberbly, confermed, supsected OF VIA cluster "Diagnostic status" : Preliminary ; Working ; Established ; Refuted</t>
   </si>
   <si>
-    <t>Additional bindings volgens zibs:
-VerificatieCodelijst; 2.16.840.1.113883.2.4.3.11.60.40.2.5.1.4
-tijdelijk uit profiel gehaald ivm plugathon</t>
-  </si>
-  <si>
-    <t>CON-16.2</t>
+    <t>VerificatieStatus ZIB!</t>
+  </si>
+  <si>
+    <t>CON-P16.2</t>
   </si>
   <si>
     <t>VerificatieStatus</t>
   </si>
   <si>
-    <t>NL behoefte ZIB 2017:Klinische status van het probleem of de diagnose</t>
-  </si>
-  <si>
-    <t>VerificatieStatusCodelijst 
-Waardelijst met SNOMED kwalificatiewaarden: werk (Suspected -vermoedelijk SNOMED 415684004), Differentiaal (Known possible mogelijk SNOMED 410590009), Bevestigd (Confirmed present  SNOMED 410605003), Uitgesloten (Known absent SNOMED 410516002), Onbekend (Unknown HL7 NullFlavor code system UNK)</t>
-  </si>
-  <si>
-    <t>CON-16.3</t>
-  </si>
-  <si>
-    <t>geen NL-behoefte vanuit spoedsamenvatting: geen behoefte gevonden in de informatieparagraaf: https://www.zorginzicht.nl/kwaliteitsstandaarden/spoedzorgketen-kwaliteitskader
-HIS-behoefte: geen behoefte om deze gestructureerd te registreren. bron: https://referentiemodel.nhg.org/node/5/volledig/published. "Voeg in de vrije tekst bij episodenaam eventueel een werkhypothese of differentiële diagnose toe." bron: https://www.nhg.org/wp-content/uploads/2026/04/260033_-Herziene-Richtlijn-ADEPD_v4.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HIS </t>
+    <t>Klinische status van het probleem of de diagnose.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VerificatieStatusCodelijst </t>
   </si>
   <si>
     <t>CON-17</t>
   </si>
   <si>
-    <t>Contactgegevens van specialist</t>
+    <t>specialistContact</t>
   </si>
   <si>
     <t>Een zorgverlener die specifiek betrokken is bij het probleem, als voorkeurscontactpersoon.</t>
   </si>
   <si>
+    <t>Verwijzing naar de EHDSHealthProfessional</t>
+  </si>
+  <si>
     <t>Ja note.text/careteam.reason</t>
   </si>
   <si>
-    <t>CON-17.1</t>
-  </si>
-  <si>
-    <t>specialistContact</t>
-  </si>
-  <si>
-    <t>Verwijzing naar de EHDSHealthProfessional</t>
-  </si>
-  <si>
     <t>Onduidelijk, mogelijk other participants mits je aan kan geven dat het een voorkeurscontactpersoon is -&gt; Wouter vragen</t>
   </si>
   <si>
-    <t>Additional bindings volgens zibs:
-ProbleemCodelijst;2.16.840.1.113883.2.4.3.11.60.40.2.5.1.2
-tijdelijk uit profiel gehaald ivm plugathon</t>
-  </si>
-  <si>
-    <t>CON-17.2</t>
-  </si>
-  <si>
-    <t>Geen data-element vanuit Zib</t>
-  </si>
-  <si>
-    <t>Geen behoefte gevonden vanuit Spoedsamenvatting, Zib 2017, Zib 2020, Zib 2024</t>
-  </si>
-  <si>
-    <t>Externe zorgverlener</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-      </rPr>
-      <t xml:space="preserve">De Externe zorgverlener bevat de naam- en contactgegevens van een externe zorgverlener en/of zorgorganisatie, die bij de behandeling van de patiënt is betrokken in kader van zorgnetwerk. Naast de presentatierol kan de invoerder aangeven of de zorgverlener de regiebehandelaar is van de patiënt
-</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF467886"/>
-        <rFont val="Aptos Narrow"/>
-      </rPr>
-      <t>https://referentiemodel.nhg.org/node/2514/publieksversie/published</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">klasse zorgverlener </t>
-  </si>
-  <si>
     <t>CON-18</t>
   </si>
   <si>
-    <t>Externe bronnen</t>
+    <t>externalResource</t>
   </si>
   <si>
     <t>Externe bronnen die specifiek betrekking hebben op het probleem, bijvoorbeeld een link naar een probleem met een zeldzame ziekte en de bijbehorende richtlijnen</t>
@@ -1628,27 +1406,15 @@
     <t>uri</t>
   </si>
   <si>
+    <t xml:space="preserve">0..* </t>
+  </si>
+  <si>
     <t>Ja(structureDefinition.extension:relatedArtifact) FMM2</t>
   </si>
   <si>
     <t>ja/nee Guideline Identifier (focust op richtlijnen of breder, LIM is breder)</t>
   </si>
   <si>
-    <t>CON-18.1</t>
-  </si>
-  <si>
-    <t>externalResource</t>
-  </si>
-  <si>
-    <t>CON-18.2</t>
-  </si>
-  <si>
-    <t>Geen data-element vanuit Zib, HIS</t>
-  </si>
-  <si>
-    <t>Geen NL-behoefte gevonden in ZIB, HIS, spoedsamenvatting</t>
-  </si>
-  <si>
     <t>CON-19</t>
   </si>
   <si>
@@ -1661,16 +1427,25 @@
     <t>Ja (comment)</t>
   </si>
   <si>
-    <t>CON-19.1</t>
-  </si>
-  <si>
-    <t>Diagnose.Toelichting</t>
-  </si>
-  <si>
-    <t>Een in vrije tekst geformuleerde toelichting bij de diagnose, die niet wordt gerepresenteerd door de andere dataelementen in het informatiemodel.</t>
-  </si>
-  <si>
-    <t>Zib 2024</t>
+    <t>CON-20</t>
+  </si>
+  <si>
+    <t>NadereSpecificatieProbleemNaam</t>
+  </si>
+  <si>
+    <t>BGZ-MSZ- behoefte: Wat is precies de behoefte van MBZ-MSZ voor een waardelijst als een naderespecificatie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">String en waardelijst </t>
+  </si>
+  <si>
+    <t>Zib 2020; informatiestandaard BgZ-MSZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ja/nee (code.text) </t>
+  </si>
+  <si>
+    <t>Ja, variant (tekst or coded tekst)</t>
   </si>
   <si>
     <t>Actie</t>
@@ -1686,227 +1461,6 @@
   </si>
   <si>
     <t>[Naam van de informatie-requirement ]</t>
-  </si>
-  <si>
-    <t>CON-9.4</t>
-  </si>
-  <si>
-    <t>AandoeningOfGesteldheid.StatusDatum</t>
-  </si>
-  <si>
-    <t>Het moment vanaf wanneer de gegevens m.b.t. de aandoening of gesteldheid van toepassing zijn. Dit mag een vaag moment zijn.'</t>
-  </si>
-  <si>
-    <t>CON-20</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>probleemType</t>
-  </si>
-  <si>
-    <t>Het type probleem</t>
-  </si>
-  <si>
-    <t>Waardelijst: diagnose, symptoom, klacht, functionele beperking, complicatie.</t>
-  </si>
-  <si>
-    <t>Zib 2020; informatiestandaard BgZ-MSZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ja/nee (code.text) </t>
-  </si>
-  <si>
-    <t>Ja, variant (tekst or coded tekst)</t>
-  </si>
-  <si>
-    <t>CON-21</t>
-  </si>
-  <si>
-    <t>symptoom</t>
-  </si>
-  <si>
-    <t>de zorgverlener heeft behoefte om symptomen los van de diagnose van de patient worden vastgesteld</t>
-  </si>
-  <si>
-    <t>string of waardelijst</t>
-  </si>
-  <si>
-    <t>CON-22</t>
-  </si>
-  <si>
-    <t>Periode</t>
-  </si>
-  <si>
-    <t>AandoeningofGesteldheid.PeriodeAanwezig::TijdsInterval</t>
-  </si>
-  <si>
-    <t>De periode waarin de aandoening of gesteldheid aanwezig is (geweest).</t>
-  </si>
-  <si>
-    <t>Tijdsinterval</t>
-  </si>
-  <si>
-    <t>CON-23</t>
-  </si>
-  <si>
-    <t>Beloop</t>
-  </si>
-  <si>
-    <t>AandoeningofGesteldheid.Beloop</t>
-  </si>
-  <si>
-    <t>Het beloop van de aandoening of gesteldheid. Dit staat los van het diagnostisch inzicht m.b.t. de aandoening of gesteldheid. Met het beloop geeft men aan hoe de aandoening of gesteldheid zich ontwikkelt, zoals bijv. stabiel, progressie, remissie, etc..</t>
-  </si>
-  <si>
-    <t>Waardelijst: BeloopCodelijst (Asymptomatisch, Verbeterd, Verslechterd, Onveranderd, Progressief, Opvlammend, Niet meer aanwezig, Anders)</t>
-  </si>
-  <si>
-    <t>Category CON11?</t>
-  </si>
-  <si>
-    <t>CON-24</t>
-  </si>
-  <si>
-    <t>Diagnosesteller</t>
-  </si>
-  <si>
-    <t>Diagnose.DiagnoseSteller::Zorgverlener</t>
-  </si>
-  <si>
-    <t>De zorgverlener die de diagnose heeft gesteld. Dit kan een ander individu zijn dan degene die de diagnose heeft geregistreerd.</t>
-  </si>
-  <si>
-    <t>CON-25</t>
-  </si>
-  <si>
-    <t>DiagnoseDatum</t>
-  </si>
-  <si>
-    <t>Diagnose.DiagnoseDatum</t>
-  </si>
-  <si>
-    <t>Datum (en tijdstip) waarop de zorgverlener tot het inzicht van de diagnose kwam.</t>
-  </si>
-  <si>
-    <t>Verschilt dus van registratiedatum en startdatum</t>
-  </si>
-  <si>
-    <t>CON-26</t>
-  </si>
-  <si>
-    <t>DiagnoseStatus</t>
-  </si>
-  <si>
-    <t>Diagnose.DiagnoseStatus</t>
-  </si>
-  <si>
-    <t>Geeft aan hoe het staat met het diagnostisch proces.</t>
-  </si>
-  <si>
-    <t>Waardelijst: DiagnoseStatusCodelijst (Voorlopige diagnose, Bevestigde diagnose, Differentiaaldiagnose)</t>
-  </si>
-  <si>
-    <t>Anders dan 'Status van het object'</t>
-  </si>
-  <si>
-    <t>CON-27</t>
-  </si>
-  <si>
-    <t>Wijze van vaststellen</t>
-  </si>
-  <si>
-    <t>Diagnose.WijzeVanVaststellen</t>
-  </si>
-  <si>
-    <t>De methode die de zorgverlener heeft gebruikt om de diagnose te stellen, zoals bijv. alleen anamnese, anamnese en lichamelijk onderzoek of  aanvullend onderzoek.</t>
-  </si>
-  <si>
-    <t>Waardelijst: WijzeVanVaststellenCodelijst</t>
-  </si>
-  <si>
-    <t>CON-28</t>
-  </si>
-  <si>
-    <t>NadereSpecificatieDiagnoseNaam</t>
-  </si>
-  <si>
-    <t>Diagnose.NadereSpecificatieDiagnoseNaam</t>
-  </si>
-  <si>
-    <t>Een in vrije tekst geformuleerde nadere detaillering van de DiagnoseNaam, wanneer dit detail niet beschikbaar is via de gebruikte codelijst.</t>
-  </si>
-  <si>
-    <t>CON-29</t>
-  </si>
-  <si>
-    <t>AandoeningOfGesteldheid</t>
-  </si>
-  <si>
-    <t>Diagnose.AandoeningOfGesteldheid</t>
-  </si>
-  <si>
-    <t>De Aandoening of gesteldheid waarop de Diagnose betrekking heeft.</t>
-  </si>
-  <si>
-    <t>CON-30</t>
-  </si>
-  <si>
-    <t>Complicatie</t>
-  </si>
-  <si>
-    <t>Diagnose.IsComplicatie</t>
-  </si>
-  <si>
-    <t>Geeft aan of de diagnose wel of niet een complicatie betreft.</t>
-  </si>
-  <si>
-    <t>CON-31</t>
-  </si>
-  <si>
-    <t>Aanleiding</t>
-  </si>
-  <si>
-    <t>Diagnose.Aanleiding</t>
-  </si>
-  <si>
-    <t>Een zorgverlener kan de behoefte hebben om bij een diagnose een aanleiding vast te leggen. Je kunt beargumenteren dat in feite de aandoening of gesteldheid een aanleiding heeft, maar de specificatie van de aanleiding berust op het inzicht om wat voor aandoening of gesteldheid het gaat. Daarom zien we de aanleiding als onderdeel van de diagnose.
-De aanleiding kan een incident zijn (bijv. een heupfractuur door een val), een verrichting (bijv. een darmperforatie door een colonoscopie) of een andere diagnose (bijv. neuropathie door diabetes). Er kan &gt; 1 Aanleiding zijn: bijv. een fractuur met als aanleiding de combinatie van een val en een aandoening die een verhoogd risico op fracturen met zich meebrengt.
-Los van het de diagnose als duiding van de aard van de aandoening of gesteldheid, kan men tot het inzicht komen dat het een complicatie betreft. Dit kan men apart representeren m.b.v. het element IsComplicatie. Of er sprake is van een complicatie hangt i.h.a. af van de aanleiding, maar er zijn uiteraard ook aanleidingen waarbij er geen sprake is van een complicatie in de zin van onbedoelde schade door medisch handelen.</t>
-  </si>
-  <si>
-    <t>CON-31.1</t>
-  </si>
-  <si>
-    <t>Incident</t>
-  </si>
-  <si>
-    <t>De onbedoelde gebeurtenis tijdens het zorgproces, die tot schade aan de patiënt heeft geleid, had kunnen leiden of (nog) zou kunnen leiden.</t>
-  </si>
-  <si>
-    <t>CON-31.2</t>
-  </si>
-  <si>
-    <t>Verrichting</t>
-  </si>
-  <si>
-    <t>De verrichting die aanleiding heeft gegeven tot de aandoening waarop de diagnose betrekking heeft.</t>
-  </si>
-  <si>
-    <t>CON-31.3</t>
-  </si>
-  <si>
-    <t>Diagnose</t>
-  </si>
-  <si>
-    <t>De diagnose m.b.t. een andere aandoening die als aanleiding wordt gezien voor de aandoening met de onderhavige diagnose.</t>
-  </si>
-  <si>
-    <t>Waardelijst (preferred): e.g. TNM, Bi-Rads, Li-Rads, …</t>
-  </si>
-  <si>
-    <t>Deze e.g. waardelijsten hebben geen OID en kunnen  niet opgenomen worden in AD. Zie PAT-304 ticket</t>
   </si>
   <si>
     <t>In het FHIR profiel is er voor de referentie voor auteur.Device nog geen Device profiel toegevoegd omdat nlcore-device nog niet bestaat. Deze moet tzt wel toegevoegd worden.</t>
@@ -1941,7 +1495,7 @@
   </si>
   <si>
     <t>Dit is een gecodeerde naam, maar dit was ook om voor te sorteren op zib2020. In de mapping naar FHIR is zib2020 uiteindelijk gekozen om deze specificatie in een notitie te zetten, aangezien dat meer was wat gevraagd werd. Zie: https://nictiz.atlassian.net/browse/ZIBFHIR-145. Het voorstel is: Condition.code.text
-Functioneel gezien maken ze gebruik van dezelfde codelijst als ProbleemNaam maar dit element is alleen van toepassing voor medisch specialisten. Onduidelijk wat hiermee bedoeld wordt omdat deze informatiestandaard zich al beperkt tot MSZ. Mogelijk is hier ook geen informatiebehoefte.</t>
+Functioneel gezien maken ze gebruik van dezelfde codelijst als ProbleemNaam maar dit element is alleen van toepassing voor medisch specialisten. Onduidelijk wat hiermee bedoeld wordt omdat deze informatiestandaard zich al beperkt tot MSZ. Mogelijk is hier ook geen informatiebehoefte,</t>
   </si>
   <si>
     <t>Episodetitel</t>
@@ -1979,13 +1533,54 @@
   <si>
     <t>LIMS omschrijving is "	
 The author of the condition information."  Het is gemapt met FHIR: Condition.recorder: de omschrijving is "Individual who recorded the record and takes responsibility for its content." -&gt; de registratie-persoon is niet altijd ook de verantwoordelijke.  Is dit een foute mapping?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">FHIR Condition Maturity Level: 3 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&amp;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> openEHR Problem/Diagnosis;latest revision / latest published  53 [1.7.4] 
+Na analyse blijkt FHIR beste keus, want: 
+-categorie: bij openEHR zijn de keuzes voor cathegorie niet overeenkomend met de cathegorieen van de LIM -&gt; maar hoeft niet persé een deal-breaker te zijn
+- diagnosisAssertionStatus waardelijst komt niet precies overeen bij openEHR(mist differential en netered-in-error), wel volledige mapping met FHIR
+- stage komt niet precies overeen in openEHR, namelijk via extensie / uitbreiding van archetype Specific Details (cluster?), wel in FHIR
+- nadereSpecificatieProbleemNaam heeft in ZIBFHIR-145 een mapping gekregen op FHIR, maar is duidelijker in openEHR gemodelleerd als "variant" (echter variant is specifieker, dan LIMS/ZIB wil duiden )
+-specialistcontact: in openEHR is het onduidelijk, mogelijk other participants mits je aan kan geven dat het een voorkeurscontactpersoon is. in FHIR ook niet ideaal, namelijk note.text of via careteam.reason</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">* Logisch informatie model EHDSCondition versie 1.0.0
+* Verplichte elementen uit FHIR R4 Condition 
+* Verplichte elementen uit openEHR Problem / Diagnosis versie 1.7.4 
+* Zib Probleem uit publicatie 2017 
+* Zib Probleem uit publicatie 2020 
+* Informatiestandaard BgZ-MSZ versie 2.0.2 
+* Usecase Spoedsamenvatting van informatiestandaard Acute Zorg versie 2.2.0 </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="27">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2008,13 +1603,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
@@ -2070,7 +1658,6 @@
       <sz val="11"/>
       <color rgb="FF242424"/>
       <name val="Aptos Narrow"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
@@ -2093,6 +1680,7 @@
       <sz val="9"/>
       <color rgb="FF4D4D4D"/>
       <name val="Tahoma"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2117,7 +1705,6 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2135,32 +1722,8 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF467886"/>
-      <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFE97132"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF292A2E"/>
-      <name val="Atlassian Sans"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2191,20 +1754,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor theme="5" tint="0.79998168889431442"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="6">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -2238,60 +1789,23 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color theme="5" tint="0.39997558519241921"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="5" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="5" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="5" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="5" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="5" tint="0.39997558519241921"/>
-      </right>
-      <top style="thin">
-        <color theme="5" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="5" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2306,27 +1820,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2335,101 +1848,61 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="21">
     <dxf>
       <font>
         <color rgb="FF000000"/>
@@ -2519,6 +1992,12 @@
         <top/>
         <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -3332,7 +2811,6 @@
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="Chevy Susanto" id="{E6DC4CC4-5331-4633-9C1C-269F406E61BD}" userId="S::chevy.susanto@nictiz.nl::4e93d0cc-e599-42c6-82b7-6ffb715c7e27" providerId="AD"/>
   <person displayName="Marija Zivlak" id="{86017760-9D2E-4C04-A548-4B0AED173840}" userId="S::marija.zivlak@nictiz.nl::bf2ce3ca-25b5-4480-970b-97ae1d2e4e23" providerId="AD"/>
-  <person displayName="Taco Spitters" id="{CAC062D8-726A-469C-9069-224CCD4B5EE1}" userId="S::taco.spitters@nictiz.nl::eff47e48-8544-4500-97c8-7e55e3c068e7" providerId="AD"/>
   <person displayName="Shenaida Hoogland" id="{67CE0BAC-4786-48DE-9DCD-69E1F3FACFC1}" userId="S::shenaida.hoogland@nictiz.nl::5cd1034b-031f-49e9-a727-e4ecba7d58df" providerId="AD"/>
 </personList>
 </file>
@@ -3342,44 +2820,45 @@
   <autoFilter ref="A2:C13" xr:uid="{7AAA9086-205B-4EC4-8920-A2DD04D02676}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{BDCFF82A-D4BE-440B-90DF-AA26F6831D5C}" name="Veld"/>
-    <tableColumn id="2" xr3:uid="{77503B9E-152C-4B39-87F4-D4FBBF1B3BDA}" name="Beschrijving" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{B530BE2A-715C-42B8-BFE1-95637D35484B}" name="a.d.h.v. keuze FHIR als basismodel"/>
+    <tableColumn id="2" xr3:uid="{77503B9E-152C-4B39-87F4-D4FBBF1B3BDA}" name="Uitleg" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{B530BE2A-715C-42B8-BFE1-95637D35484B}" name="Beschrijving"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1B14A882-8085-4978-86D3-1A5B42023C72}" name="Tabel3" displayName="Tabel3" ref="A1:E22" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
-  <autoFilter ref="A1:E22" xr:uid="{1B14A882-8085-4978-86D3-1A5B42023C72}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1B14A882-8085-4978-86D3-1A5B42023C72}" name="Tabel3" displayName="Tabel3" ref="A1:E17" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+  <autoFilter ref="A1:E17" xr:uid="{1B14A882-8085-4978-86D3-1A5B42023C72}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{2D5F85E5-856C-4A15-8C5D-D8D344B8F13C}" name="Type bron" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{062A7D5A-6D4F-45DD-9A5C-7A2D82A1266A}" name="Naam bron" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{24E64AAE-4BAD-402C-98B7-B46BE371B39E}" name="Toelichting" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{98DE6918-807C-41E0-ACBA-1E2221CF05FC}" name="Informatiebehoefte verwerkt in sheet 'informatiebeheofte'" dataDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{8CFF4D4C-ABDD-49BC-8B49-237193168687}" name="Link naar bron informatie" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{2D5F85E5-856C-4A15-8C5D-D8D344B8F13C}" name="Type bron" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{062A7D5A-6D4F-45DD-9A5C-7A2D82A1266A}" name="Naam bron" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{24E64AAE-4BAD-402C-98B7-B46BE371B39E}" name="Toelichting" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{98DE6918-807C-41E0-ACBA-1E2221CF05FC}" name="Informatiebehoefte verwerkt in sheet 'informatiebeheofte'" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{8CFF4D4C-ABDD-49BC-8B49-237193168687}" name="Link naar bron informatie" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}" name="Tabel6" displayName="Tabel6" ref="A2:M87" totalsRowShown="0" headerRowDxfId="10">
-  <autoFilter ref="A2:M87" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}"/>
-  <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{51E2B1E8-BF1C-4C85-9A83-8C69A4006993}" name="Nummer" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{021C00E0-4FF4-4652-B8E3-674B1F145954}" name="Naam" dataDxfId="8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}" name="Tabel6" displayName="Tabel6" ref="A2:N59" totalsRowShown="0" headerRowDxfId="12">
+  <autoFilter ref="A2:N59" xr:uid="{2D02605E-6993-49A7-90CB-92D41480A08E}"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{51E2B1E8-BF1C-4C85-9A83-8C69A4006993}" name="Nummer" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{021C00E0-4FF4-4652-B8E3-674B1F145954}" name="Naam" dataDxfId="10"/>
     <tableColumn id="12" xr3:uid="{721FE94A-B8C9-44E1-A03C-56E48CDCE2A3}" name="data-element"/>
-    <tableColumn id="3" xr3:uid="{12776FCA-6A89-4E9E-907F-2E30F0D43DA3}" name="Omschrijving" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{9E28C4DB-2A8B-484B-80F1-321440976652}" name="Variabiliteit" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{12776FCA-6A89-4E9E-907F-2E30F0D43DA3}" name="Omschrijving" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{9E28C4DB-2A8B-484B-80F1-321440976652}" name="Variabiliteit" dataDxfId="8"/>
     <tableColumn id="5" xr3:uid="{6FA3E114-7382-4230-B15E-A8DB28B8CE4B}" name="Aanwezigheid"/>
     <tableColumn id="6" xr3:uid="{E8FFDBDF-8B88-4089-89D0-252402D12764}" name="Verleden/heden/toekomst"/>
     <tableColumn id="7" xr3:uid="{BB9C62AB-9839-431A-90A2-B6A6D70DF1FB}" name="Herkomst"/>
     <tableColumn id="8" xr3:uid="{6BE87E7D-EFAE-42FD-9334-11E5EBAC9DC3}" name="Komt het in FHIR R4 voor?"/>
     <tableColumn id="9" xr3:uid="{C6EE00AA-2B37-4BE3-B349-AF61C6E68575}" name="Komt het in openEHR voor?"/>
+    <tableColumn id="10" xr3:uid="{943D4BF3-315C-41FB-99E4-8DB8C54604A4}" name="Komt voor in ZIBProbleem-v4.4? (2020)"/>
+    <tableColumn id="14" xr3:uid="{8B1A7EB4-D690-4A36-9698-ACA592C2A715}" name="Komt voor in ZIBProbleem? (2017)" dataDxfId="7"/>
+    <tableColumn id="13" xr3:uid="{51A57E0A-A216-45BB-973D-E0D8C72BEEEC}" name="Komt voor in ZIBProbleem? (2024)" dataDxfId="6"/>
     <tableColumn id="11" xr3:uid="{E7EDB106-7E3F-4122-A864-3B3AE59C9D87}" name="Opmerking"/>
-    <tableColumn id="10" xr3:uid="{2A08085B-3D25-4805-90D0-47506CCECECF}" name="Kolom1"/>
-    <tableColumn id="13" xr3:uid="{40C0B86E-8EDD-4F57-895D-7FF399948ED0}" name="Kolom2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3734,8 +3213,13 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="A3" dT="2026-07-23T07:54:32.60" personId="{E6DC4CC4-5331-4633-9C1C-269F406E61BD}" id="{FC56F738-FB65-495B-9B48-E0F47216F010}">
-    <text>AllergyInt heeft een andere naam conventie voor ‘Nummer’. Controleren welke juist is.</text>
+  <threadedComment ref="K20" dT="2026-07-20T09:26:12.56" personId="{E6DC4CC4-5331-4633-9C1C-269F406E61BD}" id="{B3533A99-0CB6-4646-9417-20A66FEFD573}">
+    <text>1. Actief
+2. Inactief
+Kortere waardelijst</text>
+  </threadedComment>
+  <threadedComment ref="K26" dT="2026-07-20T09:50:58.06" personId="{E6DC4CC4-5331-4633-9C1C-269F406E61BD}" id="{20B2A504-5F6F-4996-9921-E2104F9548D8}">
+    <text>Wel in metadata!</text>
   </threadedComment>
   <threadedComment ref="E29" dT="2026-07-20T11:55:56.61" personId="{86017760-9D2E-4C04-A548-4B0AED173840}" id="{DC3A08E9-01DD-48D1-B7F5-357810DE5428}">
     <text>Onduidelijk welke waardelijst gehandeerd moet worden</text>
@@ -3746,16 +3230,8 @@
   <threadedComment ref="C31" dT="2026-07-22T10:46:13.79" personId="{67CE0BAC-4786-48DE-9DCD-69E1F3FACFC1}" id="{00D6E7CD-1959-4C9A-8BC1-A1E323A0102F}">
     <text>ter discussie</text>
   </threadedComment>
-  <threadedComment ref="C40" dT="2026-07-22T10:57:31.61" personId="{67CE0BAC-4786-48DE-9DCD-69E1F3FACFC1}" id="{065B39A6-9843-49BF-88E8-0C2BF95F8D00}">
+  <threadedComment ref="C39" dT="2026-07-22T10:57:31.61" personId="{67CE0BAC-4786-48DE-9DCD-69E1F3FACFC1}" id="{065B39A6-9843-49BF-88E8-0C2BF95F8D00}">
     <text>ter discussie</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
-<file path=xl/threadedComments/threadedComment3.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="D4" dT="2026-09-07T11:51:51.49" personId="{CAC062D8-726A-469C-9069-224CCD4B5EE1}" id="{75AC27D5-B4F8-442C-9CA0-BF0C6D98019C}">
-    <text>geen voorsortering geweest op de zib 2020. Wij wilden coded, dat is text. Dus zelf toegevoegd aan BgZ-MSZ</text>
   </threadedComment>
 </ThreadedComments>
 </file>
@@ -3763,15 +3239,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F1013F7-63B2-4F83-92B0-1C8153859891}">
   <dimension ref="A1:C19"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="218.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15" customHeight="1">
+    <row r="1" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
     </row>
-    <row r="18" spans="2:3">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18">
         <f>(510*132.5) + (160*132.5)</f>
         <v>88775</v>
@@ -3780,7 +3256,7 @@
         <v>5832</v>
       </c>
     </row>
-    <row r="19" spans="2:3">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19">
         <f>(542*132.5)</f>
         <v>71815</v>
@@ -3798,138 +3274,138 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CC1E3B3-D087-4A2B-920B-9BA971FAD64B}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
     <col min="2" max="2" width="46.7109375" customWidth="1"/>
-    <col min="3" max="3" width="74.85546875" customWidth="1"/>
+    <col min="3" max="3" width="59.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="190.5" customHeight="1">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="s">
+    </row>
+    <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="81" customHeight="1">
-      <c r="A3" t="s">
+      <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="C3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="3" t="s">
+    </row>
+    <row r="4" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="105" customHeight="1">
-      <c r="A4" t="s">
+      <c r="B4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="C4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="3" t="s">
+    </row>
+    <row r="5" spans="1:3" ht="330" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="250.5" customHeight="1">
-      <c r="A5" t="s">
+      <c r="B5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="C5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="3" t="s">
+    </row>
+    <row r="6" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="60">
-      <c r="A6" t="s">
+      <c r="B6" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="C6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="3" t="s">
+    </row>
+    <row r="7" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="57.75">
-      <c r="A7" t="s">
+      <c r="B7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="C7" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="17" t="s">
+    </row>
+    <row r="8" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="90.75" customHeight="1">
-      <c r="A8" t="s">
+      <c r="B8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="C8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="3" t="s">
+    </row>
+    <row r="9" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="105">
-      <c r="A9" t="s">
+      <c r="B9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="C9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="3" t="s">
+    </row>
+    <row r="10" spans="1:3" ht="135" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="45">
-      <c r="A10" t="s">
+      <c r="B10" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="45">
-      <c r="A11" t="s">
+      <c r="B11" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="C11" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="3" t="s">
+    </row>
+    <row r="12" spans="1:3" ht="315" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="255.75" customHeight="1">
-      <c r="A12" t="s">
+      <c r="B12" s="7"/>
+      <c r="C12" s="3" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>30</v>
-      </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="38" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>32</v>
       </c>
       <c r="B13" s="7"/>
     </row>
@@ -3948,351 +3424,220 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8AA88E1-0CFC-4A69-A682-35DA329C9688}">
-  <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" customWidth="1"/>
     <col min="2" max="2" width="51.28515625" customWidth="1"/>
-    <col min="3" max="3" width="69.85546875" customWidth="1"/>
+    <col min="3" max="3" width="67.28515625" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
     <col min="5" max="5" width="58.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.5" customHeight="1">
+    <row r="1" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="B2" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="45">
-      <c r="A2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="3" t="s">
+    </row>
+    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="30">
-      <c r="A3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="D3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="37" t="s">
+      <c r="D4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="45">
-      <c r="A4" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="3" t="s">
+    </row>
+    <row r="5" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="B5" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="C5" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="29.25">
-      <c r="A5" s="3" t="s">
+      <c r="D5" s="3"/>
+      <c r="E5" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="3" t="s">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D6" s="3"/>
+      <c r="E6" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E5" s="4" t="s">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="C7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="3" t="s">
+    </row>
+    <row r="8" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="B8" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="C8" s="3" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="57.75">
-      <c r="A7" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="D8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C7" s="3" t="s">
+    </row>
+    <row r="9" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D7" s="38" t="s">
+      <c r="B9" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="43.5">
-      <c r="A8" s="3" t="s">
+      <c r="D9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="37" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8" s="37" t="s">
-        <v>64</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="72.75">
-      <c r="A9" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="30">
+    </row>
+    <row r="10" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>71</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
       <c r="E10" s="6"/>
     </row>
-    <row r="11" spans="1:5" ht="30">
-      <c r="A11" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>71</v>
-      </c>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
       <c r="E11" s="6"/>
     </row>
-    <row r="12" spans="1:5" ht="30">
-      <c r="A12" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>71</v>
-      </c>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
       <c r="E12" s="6"/>
     </row>
-    <row r="13" spans="1:5" ht="30">
-      <c r="A13" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>71</v>
-      </c>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
       <c r="E13" s="4"/>
     </row>
-    <row r="14" spans="1:5" ht="30">
-      <c r="A14" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C14" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>71</v>
-      </c>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
       <c r="E14" s="4"/>
     </row>
-    <row r="15" spans="1:5" ht="30">
-      <c r="A15" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>71</v>
-      </c>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
       <c r="E15" s="4"/>
     </row>
-    <row r="16" spans="1:5" ht="30">
-      <c r="A16" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>71</v>
-      </c>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
       <c r="E16" s="4"/>
     </row>
-    <row r="17" spans="1:5" ht="30">
-      <c r="A17" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B17" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>71</v>
-      </c>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
       <c r="E17" s="3"/>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3"/>
-      <c r="B18" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="C18" s="38"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-    </row>
-    <row r="19" spans="1:5" ht="30">
-      <c r="A19" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B19" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="C19" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E19" s="3"/>
-    </row>
-    <row r="20" spans="1:5" ht="30">
-      <c r="A20" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C20" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E20" s="3"/>
-    </row>
-    <row r="21" spans="1:5" ht="30">
-      <c r="A21" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C21" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E21" s="3"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" t="s">
-        <v>83</v>
-      </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -4301,8 +3646,8 @@
     <hyperlink ref="E7" r:id="rId3" xr:uid="{612DD86C-3891-43E3-B27A-AA6071C8917D}"/>
     <hyperlink ref="E6" r:id="rId4" xr:uid="{104C1F39-D7B8-4AE4-9031-EE6CE3C7F3A7}"/>
     <hyperlink ref="E5" r:id="rId5" xr:uid="{B27B79EC-18DD-4070-9630-609E711CCC3B}"/>
-    <hyperlink ref="E4" r:id="rId6" display="https://ckm.openehr.org/ckm/archetypes/1013.1.169" xr:uid="{6DB1F6B2-19D1-473C-A11F-4BEC97E8171B}"/>
-    <hyperlink ref="E8" r:id="rId7" xr:uid="{20F24860-A30F-4C37-9DE0-9FABA5DC318C}"/>
+    <hyperlink ref="E8" r:id="rId6" xr:uid="{20F24860-A30F-4C37-9DE0-9FABA5DC318C}"/>
+    <hyperlink ref="E4" r:id="rId7" display="https://ckm.openehr.org/ckm/archetypes/1013.1.169" xr:uid="{6DB1F6B2-19D1-473C-A11F-4BEC97E8171B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -4313,2267 +3658,1769 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7034CDAF-2A08-4BE8-92C3-F4E7A6F24E1B}">
-  <dimension ref="A1:M90"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:O65"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.85546875" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
     <col min="2" max="2" width="29.28515625" customWidth="1"/>
-    <col min="3" max="3" width="39" customWidth="1"/>
-    <col min="4" max="4" width="76.7109375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="43.28515625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="32.7109375" customWidth="1"/>
+    <col min="4" max="4" width="87.42578125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="78" style="3" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
     <col min="7" max="7" width="11.42578125" customWidth="1"/>
     <col min="8" max="8" width="32.42578125" customWidth="1"/>
     <col min="9" max="9" width="28.140625" customWidth="1"/>
     <col min="10" max="10" width="51.28515625" customWidth="1"/>
-    <col min="11" max="11" width="33.28515625" customWidth="1"/>
+    <col min="11" max="11" width="38.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="38.42578125" customWidth="1"/>
+    <col min="14" max="14" width="33.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="99.75" customHeight="1"/>
-    <row r="2" spans="1:13">
+    <row r="1" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="182.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="18"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K3" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="B2" t="s">
+      <c r="L3" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="M3" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="N3" s="19"/>
+      <c r="O3" s="9"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C4" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D4" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E4" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G4" s="3"/>
+      <c r="H4" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+    </row>
+    <row r="5" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="B5" s="8"/>
+      <c r="C5" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="D5" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="71.25" customHeight="1">
-      <c r="A3" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="92.25" customHeight="1">
-      <c r="A4" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="C4" s="19"/>
-      <c r="D4" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="K4" s="20"/>
-      <c r="L4" s="9"/>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>112</v>
-      </c>
       <c r="F5" s="3" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
-    </row>
-    <row r="6" spans="1:13" ht="60">
-      <c r="A6" s="20" t="s">
-        <v>115</v>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+    </row>
+    <row r="6" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="19" t="s">
+        <v>96</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
-        <v>119</v>
+        <v>41</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
-    </row>
-    <row r="7" spans="1:13" ht="30">
-      <c r="A7" s="20" t="s">
-        <v>120</v>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+    </row>
+    <row r="7" spans="1:15" ht="105" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>43</v>
+        <v>102</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
-    </row>
-    <row r="8" spans="1:13" ht="105.75" customHeight="1">
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+    </row>
+    <row r="8" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8" t="s">
-        <v>124</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8" s="8"/>
       <c r="D8" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="3" t="s">
-        <v>127</v>
-      </c>
+      <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" ht="29.25">
-      <c r="A9" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="B9" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="C9" s="8"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>107</v>
+      </c>
       <c r="D9" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="F9" s="3"/>
+        <v>108</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>109</v>
+      </c>
       <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" ht="43.5">
-      <c r="A10" s="20" t="s">
-        <v>131</v>
-      </c>
+      <c r="H9" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="B10" s="3"/>
       <c r="C10" s="3" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>137</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
       <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" ht="29.25">
-      <c r="A11" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3" t="s">
-        <v>139</v>
-      </c>
+      <c r="L10" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" ht="75" x14ac:dyDescent="0.25">
+      <c r="A11" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C11" s="10"/>
       <c r="D11" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="C12" s="10"/>
+        <v>90</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J11" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" ht="105" x14ac:dyDescent="0.25">
+      <c r="A12" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>129</v>
+      </c>
       <c r="D12" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>146</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="J12" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" ht="130.5">
-      <c r="A13" s="20" t="s">
-        <v>149</v>
+        <v>133</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" ht="180.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="19" t="s">
+        <v>135</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>135</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" ht="180.75" customHeight="1">
-      <c r="A14" s="20" t="s">
-        <v>156</v>
+        <v>134</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="19" t="s">
+        <v>142</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>161</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>162</v>
+        <v>90</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>163</v>
+        <v>112</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="20" t="s">
-        <v>164</v>
+        <v>134</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" ht="135" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>167</v>
+        <v>149</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>150</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>161</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3" t="s">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" ht="135" customHeight="1">
+        <v>153</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>173</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="F16" s="35" t="s">
-        <v>135</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>71</v>
-      </c>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="1:13" ht="29.25">
-      <c r="A17" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="B17" s="23" t="s">
-        <v>177</v>
-      </c>
-      <c r="C17" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3" t="s">
+        <v>157</v>
+      </c>
       <c r="D17" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="F17" s="3"/>
+        <v>158</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>160</v>
+      </c>
       <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="1:13" ht="54.75" customHeight="1">
-      <c r="A18" s="20" t="s">
-        <v>179</v>
+      <c r="H17" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="J17" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="1:14" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="19" t="s">
+        <v>163</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>183</v>
+        <v>89</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="J18" s="31" t="s">
-        <v>185</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
       <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="1:13" ht="85.5" customHeight="1">
-      <c r="A19" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3" t="s">
-        <v>187</v>
-      </c>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>169</v>
+      </c>
+      <c r="C19" s="3"/>
       <c r="D19" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>113</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="F19" s="3"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="3" t="s">
-        <v>142</v>
-      </c>
+      <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="1:13">
-      <c r="A20" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="B20" s="23" t="s">
-        <v>191</v>
-      </c>
-      <c r="C20" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="1:14" ht="101.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>169</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>172</v>
+      </c>
       <c r="D20" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="F20" s="3"/>
+        <v>173</v>
+      </c>
+      <c r="E20" s="37" t="s">
+        <v>174</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>89</v>
+      </c>
       <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="1:13" ht="101.25" customHeight="1">
-      <c r="A21" s="20" t="s">
-        <v>193</v>
+      <c r="H20" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J20" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="108" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="19" t="s">
+        <v>179</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="E21" s="36" t="s">
-        <v>196</v>
+        <v>180</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>181</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3" t="s">
-        <v>114</v>
+        <v>182</v>
       </c>
       <c r="I21" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="C22" s="10"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="36"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+      <c r="A23" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="I23" s="38" t="s">
+        <v>189</v>
+      </c>
+      <c r="J23" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="L23" s="36" t="s">
+        <v>192</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="N23" s="5" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+      <c r="A24" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="B24" s="3"/>
+      <c r="C24" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="J21" s="56" t="s">
+      <c r="E24" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="K21" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="L21" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="162.75" customHeight="1">
-      <c r="A22" s="20" t="s">
-        <v>201</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
-      <c r="A23" s="20" t="s">
-        <v>206</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="C23" s="10"/>
-      <c r="D23" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="1:13" ht="57.75">
-      <c r="A24" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="24" t="s">
-        <v>210</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>212</v>
-      </c>
       <c r="F24" s="3" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="I24" s="37" t="s">
-        <v>213</v>
-      </c>
-      <c r="J24" s="24" t="s">
-        <v>214</v>
-      </c>
-      <c r="K24" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="M24" s="55" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="132.75" customHeight="1">
+        <v>95</v>
+      </c>
+      <c r="I24" s="38"/>
+      <c r="J24" s="23"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="39"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="5"/>
+    </row>
+    <row r="25" spans="1:14" ht="149.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="B25" s="3"/>
-      <c r="C25" s="35" t="s">
-        <v>218</v>
-      </c>
-      <c r="D25" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="E25" s="36" t="s">
-        <v>220</v>
+      <c r="C25" s="36" t="s">
+        <v>200</v>
+      </c>
+      <c r="D25" s="37" t="s">
+        <v>201</v>
+      </c>
+      <c r="E25" s="37" t="s">
+        <v>202</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="I25" s="3"/>
-      <c r="J25" s="24"/>
-      <c r="K25" s="35" t="s">
-        <v>222</v>
-      </c>
-      <c r="L25" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="43.5">
-      <c r="A26" s="20" t="s">
-        <v>224</v>
+      <c r="J25" s="23"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="A26" s="19" t="s">
+        <v>204</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="C26" s="38" t="s">
-        <v>226</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="C26" s="10"/>
       <c r="D26" s="3" t="s">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>228</v>
+        <v>207</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="3" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>229</v>
+        <v>208</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="K26" s="3"/>
-      <c r="L26" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
-      <c r="A27" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="B27" s="23" t="s">
-        <v>233</v>
-      </c>
-      <c r="C27" s="23"/>
-      <c r="D27" s="3" t="s">
-        <v>234</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="B27" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="C27" s="22"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3" t="s">
-        <v>235</v>
+        <v>212</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="1:13" ht="47.25" customHeight="1">
-      <c r="A28" s="20" t="s">
-        <v>237</v>
+        <v>213</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="1:14" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="19" t="s">
+        <v>215</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3" t="s">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>240</v>
+        <v>218</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="I28" s="3"/>
-      <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="1:13" ht="27.75" customHeight="1">
-      <c r="A29" s="20" t="s">
-        <v>241</v>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="19" t="s">
+        <v>219</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="3" t="s">
-        <v>242</v>
+        <v>220</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>244</v>
+        <v>222</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
-    </row>
-    <row r="30" spans="1:13" ht="123.75" customHeight="1">
-      <c r="A30" s="20" t="s">
-        <v>245</v>
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="19" t="s">
+        <v>223</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="3" t="s">
-        <v>246</v>
+        <v>224</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>247</v>
+        <v>225</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>248</v>
+        <v>226</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3" t="s">
-        <v>249</v>
+        <v>227</v>
       </c>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
-      <c r="K30" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="243" customHeight="1">
-      <c r="A31" s="20" t="s">
-        <v>251</v>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="1:14" ht="219" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="19" t="s">
+        <v>228</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3" t="s">
-        <v>252</v>
+        <v>229</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>253</v>
+        <v>230</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>254</v>
+        <v>231</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="G31" s="3"/>
       <c r="H31" s="3" t="s">
-        <v>255</v>
+        <v>232</v>
       </c>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
-    </row>
-    <row r="32" spans="1:13" ht="219" customHeight="1">
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3" t="s">
-        <v>257</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="C32" s="10"/>
       <c r="D32" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
-    </row>
-    <row r="33" spans="1:11" ht="37.5" customHeight="1">
-      <c r="A33" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="B33" s="10" t="s">
-        <v>262</v>
-      </c>
-      <c r="C33" s="10"/>
+        <v>235</v>
+      </c>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3" t="s">
+        <v>241</v>
+      </c>
       <c r="D33" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="K33" s="3"/>
-    </row>
-    <row r="34" spans="1:11">
-      <c r="A34" s="20" t="s">
-        <v>267</v>
+        <v>242</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="1:14" ht="162" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="19" t="s">
+        <v>243</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="3" t="s">
-        <v>268</v>
+        <v>244</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>269</v>
+        <v>245</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>182</v>
+        <v>246</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3" t="s">
-        <v>114</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="I34" s="3"/>
+      <c r="J34" s="31"/>
       <c r="K34" s="3"/>
-    </row>
-    <row r="35" spans="1:11" ht="162" customHeight="1">
-      <c r="A35" s="20" t="s">
-        <v>270</v>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="1:14" ht="121.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="9" t="s">
+        <v>248</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="3" t="s">
-        <v>271</v>
+        <v>249</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>272</v>
+        <v>250</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>183</v>
+        <v>89</v>
       </c>
       <c r="G35" s="3"/>
       <c r="H35" s="3" t="s">
-        <v>274</v>
+        <v>252</v>
       </c>
       <c r="I35" s="3"/>
-      <c r="J35" s="30"/>
+      <c r="J35" s="3"/>
       <c r="K35" s="3"/>
-    </row>
-    <row r="36" spans="1:11" ht="121.5" customHeight="1">
+      <c r="L35" s="3"/>
+      <c r="M35" s="3"/>
+      <c r="N35" s="3"/>
+    </row>
+    <row r="36" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3" t="s">
-        <v>276</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="C36" s="10"/>
       <c r="D36" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
+        <v>255</v>
+      </c>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>258</v>
+      </c>
       <c r="K36" s="3"/>
-    </row>
-    <row r="37" spans="1:11" ht="30">
-      <c r="A37" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>281</v>
-      </c>
-      <c r="C37" s="10"/>
+      <c r="L36" s="3"/>
+      <c r="M36" s="3"/>
+      <c r="N36" s="3"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3" t="s">
+        <v>260</v>
+      </c>
       <c r="D37" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="K37" s="3"/>
-    </row>
-    <row r="38" spans="1:11">
-      <c r="A38" s="20" t="s">
-        <v>286</v>
+        <v>261</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="L37" s="3"/>
+      <c r="M37" s="3"/>
+      <c r="N37" s="3"/>
+    </row>
+    <row r="38" spans="1:14" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="19" t="s">
+        <v>263</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="3" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>182</v>
+        <v>266</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="3" t="s">
-        <v>114</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
       <c r="K38" s="3"/>
-    </row>
-    <row r="39" spans="1:11" ht="66.75" customHeight="1">
-      <c r="A39" s="20" t="s">
-        <v>289</v>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3"/>
+    </row>
+    <row r="39" spans="1:14" ht="178.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="9" t="s">
+        <v>267</v>
       </c>
       <c r="B39" s="3"/>
-      <c r="C39" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>291</v>
+      <c r="C39" s="34" t="s">
+        <v>268</v>
+      </c>
+      <c r="D39" s="17" t="s">
+        <v>269</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>292</v>
+        <v>159</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="3" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="1:11" ht="178.5" customHeight="1">
-      <c r="A40" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="B40" s="3"/>
-      <c r="C40" s="33" t="s">
-        <v>294</v>
-      </c>
-      <c r="D40" s="17" t="s">
-        <v>295</v>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="1:14" ht="135" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="C40" s="10"/>
+      <c r="D40" s="3" t="s">
+        <v>273</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>183</v>
+        <v>109</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="I40" s="3"/>
-      <c r="J40" s="3"/>
+        <v>90</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="J40" s="20" t="s">
+        <v>275</v>
+      </c>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="1:11" ht="135" customHeight="1">
-      <c r="A41" s="20" t="s">
-        <v>297</v>
-      </c>
-      <c r="B41" s="10" t="s">
-        <v>298</v>
-      </c>
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="B41" s="3"/>
       <c r="C41" s="10"/>
       <c r="D41" s="3" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="3" t="s">
-        <v>114</v>
+        <v>279</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="J41" s="21" t="s">
-        <v>302</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="J41" s="3"/>
       <c r="K41" s="3"/>
-    </row>
-    <row r="42" spans="1:11" ht="54.75" customHeight="1">
+      <c r="L41" s="3"/>
+      <c r="M41" s="3"/>
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="1:14" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
-        <v>303</v>
+        <v>280</v>
       </c>
       <c r="B42" s="3"/>
       <c r="C42" s="10"/>
       <c r="D42" s="3" t="s">
-        <v>304</v>
+        <v>281</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>305</v>
+        <v>282</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="J42" s="3"/>
+        <v>283</v>
+      </c>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3" t="s">
+        <v>284</v>
+      </c>
       <c r="K42" s="3"/>
-    </row>
-    <row r="43" spans="1:11" ht="124.5" customHeight="1">
-      <c r="A43" s="9" t="s">
-        <v>307</v>
-      </c>
-      <c r="B43" s="3"/>
+      <c r="L42" s="3"/>
+      <c r="M42" s="3"/>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A43" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>286</v>
+      </c>
       <c r="C43" s="10"/>
       <c r="D43" s="3" t="s">
-        <v>308</v>
+        <v>287</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>309</v>
+        <v>288</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="I43" s="3"/>
-      <c r="J43" s="3" t="s">
-        <v>311</v>
+        <v>90</v>
+      </c>
+      <c r="I43" s="33" t="s">
+        <v>289</v>
+      </c>
+      <c r="J43" s="33" t="s">
+        <v>290</v>
       </c>
       <c r="K43" s="3"/>
-    </row>
-    <row r="44" spans="1:11" ht="115.5">
-      <c r="A44" s="20" t="s">
-        <v>312</v>
-      </c>
-      <c r="B44" s="10" t="s">
-        <v>313</v>
-      </c>
+      <c r="L43" s="3"/>
+      <c r="M43" s="3"/>
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="A44" s="9"/>
+      <c r="B44" s="3"/>
       <c r="C44" s="10"/>
       <c r="D44" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>183</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="F44" s="3"/>
       <c r="G44" s="3"/>
-      <c r="H44" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="I44" s="32" t="s">
-        <v>316</v>
-      </c>
-      <c r="J44" s="32" t="s">
-        <v>317</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11">
-      <c r="A45" s="9"/>
-      <c r="B45" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="33"/>
+      <c r="J44" s="33"/>
+      <c r="K44" s="3"/>
+      <c r="L44" s="3"/>
+      <c r="M44" s="3"/>
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="19" t="s">
+        <v>292</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>293</v>
+      </c>
       <c r="C45" s="10"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="3"/>
-      <c r="I45" s="32"/>
-      <c r="J45" s="32"/>
+      <c r="D45" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>298</v>
+      </c>
       <c r="K45" s="3"/>
-    </row>
-    <row r="46" spans="1:11" ht="37.5" customHeight="1">
-      <c r="A46" s="20" t="s">
-        <v>319</v>
-      </c>
-      <c r="B46" s="10" t="s">
-        <v>320</v>
-      </c>
+      <c r="L45" s="3"/>
+      <c r="M45" s="3"/>
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="B46" s="3"/>
       <c r="C46" s="10"/>
       <c r="D46" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" ht="59.25" customHeight="1">
+        <v>300</v>
+      </c>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
+      <c r="K46" s="3"/>
+      <c r="L46" s="3"/>
+      <c r="M46" s="3"/>
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="1:14" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
-        <v>327</v>
+        <v>301</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="3" t="s">
-        <v>328</v>
+        <v>302</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>329</v>
+        <v>303</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>330</v>
+        <v>304</v>
       </c>
       <c r="F47" s="3">
         <v>1</v>
       </c>
       <c r="G47" s="3"/>
       <c r="H47" s="3" t="s">
-        <v>310</v>
+        <v>283</v>
       </c>
       <c r="I47" s="3"/>
       <c r="J47" s="3"/>
       <c r="K47" s="3"/>
-    </row>
-    <row r="48" spans="1:11">
-      <c r="A48" s="20" t="s">
-        <v>331</v>
+      <c r="L47" s="3"/>
+      <c r="M47" s="3"/>
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A48" s="19" t="s">
+        <v>305</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>332</v>
+        <v>306</v>
       </c>
       <c r="C48" s="10"/>
       <c r="D48" s="3" t="s">
-        <v>333</v>
+        <v>307</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>334</v>
+        <v>308</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>335</v>
+        <v>309</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>336</v>
+        <v>310</v>
       </c>
       <c r="K48" s="3"/>
-    </row>
-    <row r="49" spans="1:11">
-      <c r="A49" s="20" t="s">
-        <v>337</v>
+      <c r="L48" s="3"/>
+      <c r="M48" s="3"/>
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A49" s="19" t="s">
+        <v>311</v>
       </c>
       <c r="B49" s="3"/>
       <c r="C49" s="3" t="s">
-        <v>338</v>
+        <v>312</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>339</v>
+        <v>313</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="G49" s="3"/>
       <c r="H49" s="3" t="s">
-        <v>274</v>
+        <v>247</v>
       </c>
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
       <c r="K49" s="3"/>
-    </row>
-    <row r="50" spans="1:11" ht="30">
-      <c r="A50" s="20" t="s">
-        <v>340</v>
-      </c>
+      <c r="L49" s="3"/>
+      <c r="M49" s="3"/>
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A50" s="19" t="s">
+        <v>314</v>
+      </c>
+      <c r="B50" s="3"/>
       <c r="C50" s="3" t="s">
-        <v>341</v>
+        <v>315</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>342</v>
+        <v>316</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="G50" s="3"/>
       <c r="H50" s="3" t="s">
-        <v>274</v>
+        <v>247</v>
       </c>
       <c r="I50" s="3"/>
       <c r="J50" s="3"/>
       <c r="K50" s="3"/>
-    </row>
-    <row r="51" spans="1:11">
-      <c r="A51" s="9" t="s">
-        <v>343</v>
-      </c>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3" t="s">
-        <v>344</v>
-      </c>
+      <c r="L50" s="3"/>
+      <c r="M50" s="3"/>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A51" s="19" t="s">
+        <v>317</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="C51" s="10"/>
       <c r="D51" s="3" t="s">
-        <v>345</v>
+        <v>319</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>320</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="G51" s="3"/>
       <c r="H51" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="I51" s="3"/>
-      <c r="J51" s="3"/>
-      <c r="K51" s="3"/>
-    </row>
-    <row r="52" spans="1:11" ht="45">
-      <c r="A52" s="20" t="s">
-        <v>347</v>
-      </c>
-      <c r="B52" s="10" t="s">
-        <v>348</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="J51" s="24" t="s">
+        <v>322</v>
+      </c>
+      <c r="K51" s="4"/>
+      <c r="L51" s="3"/>
+      <c r="M51" s="3"/>
+      <c r="N51" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A52" s="9"/>
+      <c r="B52" s="3"/>
       <c r="C52" s="10"/>
       <c r="D52" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>135</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="F52" s="3"/>
       <c r="G52" s="3"/>
-      <c r="H52" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="J52" s="25" t="s">
-        <v>352</v>
-      </c>
-      <c r="K52" s="4" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" ht="45">
+      <c r="H52" s="3"/>
+      <c r="I52" s="3"/>
+      <c r="J52" s="24"/>
+      <c r="K52" s="4"/>
+      <c r="L52" s="3"/>
+      <c r="M52" s="3"/>
+      <c r="N52" s="4"/>
+    </row>
+    <row r="53" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="9" t="s">
-        <v>354</v>
-      </c>
-      <c r="B53" s="3"/>
-      <c r="C53" s="38" t="s">
-        <v>355</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>356</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="C53" s="10"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
-      <c r="H53" s="3" t="s">
-        <v>357</v>
-      </c>
+      <c r="H53" s="3"/>
       <c r="I53" s="3"/>
-      <c r="J53" s="24"/>
-      <c r="K53" s="4"/>
-    </row>
-    <row r="54" spans="1:11" ht="45" customHeight="1">
-      <c r="A54" s="9" t="s">
-        <v>358</v>
-      </c>
-      <c r="B54" s="3"/>
-      <c r="C54" s="38" t="s">
-        <v>359</v>
-      </c>
-      <c r="D54" s="17" t="s">
-        <v>360</v>
+      <c r="J53" s="23"/>
+      <c r="K53" s="3"/>
+      <c r="L53" s="3"/>
+      <c r="M53" s="3"/>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="1:14" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="19" t="s">
+        <v>327</v>
+      </c>
+      <c r="B54" s="10"/>
+      <c r="C54" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>329</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="F54" s="3"/>
+        <v>330</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>160</v>
+      </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="I54" s="3"/>
-      <c r="J54" s="24"/>
-      <c r="K54" s="4"/>
-    </row>
-    <row r="55" spans="1:11" ht="30">
+        <v>90</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="J54" s="20" t="s">
+        <v>332</v>
+      </c>
+      <c r="K54" s="25" t="s">
+        <v>333</v>
+      </c>
+      <c r="L54" s="25"/>
+      <c r="M54" s="25"/>
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="9" t="s">
-        <v>362</v>
-      </c>
-      <c r="B55" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="C55" s="10"/>
+        <v>334</v>
+      </c>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3" t="s">
+        <v>335</v>
+      </c>
       <c r="D55" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="F55" s="3"/>
+        <v>336</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>160</v>
+      </c>
       <c r="G55" s="3"/>
-      <c r="H55" s="3"/>
+      <c r="H55" s="3" t="s">
+        <v>247</v>
+      </c>
       <c r="I55" s="3"/>
-      <c r="J55" s="24"/>
-      <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="1:11" ht="73.5" customHeight="1">
-      <c r="A56" s="20" t="s">
-        <v>365</v>
-      </c>
-      <c r="B56" s="10"/>
-      <c r="C56" s="3" t="s">
-        <v>366</v>
-      </c>
+      <c r="J55" s="3"/>
+      <c r="K55" s="25"/>
+      <c r="L55" s="17"/>
+      <c r="M55" s="17"/>
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="A56" s="19" t="s">
+        <v>338</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="C56" s="10"/>
       <c r="D56" s="3" t="s">
-        <v>364</v>
+        <v>340</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>367</v>
+        <v>341</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>183</v>
+        <v>109</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="I56" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="J56" s="21" t="s">
-        <v>369</v>
-      </c>
-      <c r="K56" s="3" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" ht="102.75" customHeight="1">
-      <c r="A57" s="9" t="s">
-        <v>371</v>
-      </c>
-      <c r="B57" s="3"/>
-      <c r="C57" s="3" t="s">
-        <v>372</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="I56" s="33" t="s">
+        <v>342</v>
+      </c>
+      <c r="J56" s="20" t="s">
+        <v>343</v>
+      </c>
+      <c r="K56" s="3"/>
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A57" s="19" t="s">
+        <v>344</v>
+      </c>
+      <c r="B57" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="C57" s="10"/>
       <c r="D57" s="3" t="s">
-        <v>373</v>
+        <v>346</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>374</v>
+        <v>347</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>183</v>
+        <v>348</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3" t="s">
-        <v>274</v>
+        <v>90</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J57" s="21"/>
+        <v>349</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>350</v>
+      </c>
       <c r="K57" s="3"/>
-    </row>
-    <row r="58" spans="1:11" ht="124.5" customHeight="1">
-      <c r="A58" s="9" t="s">
-        <v>375</v>
-      </c>
-      <c r="B58" s="3"/>
-      <c r="C58" s="3"/>
+      <c r="L57" s="3"/>
+      <c r="M57" s="3"/>
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="19" t="s">
+        <v>351</v>
+      </c>
+      <c r="B58" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="C58" s="27"/>
       <c r="D58" s="3" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="F58" s="3"/>
+        <v>288</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>160</v>
+      </c>
       <c r="G58" s="3"/>
       <c r="H58" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="I58" s="3"/>
-      <c r="J58" s="3"/>
+        <v>247</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>354</v>
+      </c>
       <c r="K58" s="3"/>
-    </row>
-    <row r="59" spans="1:11" ht="29.25">
-      <c r="A59" s="20" t="s">
-        <v>378</v>
-      </c>
-      <c r="B59" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="C59" s="10"/>
-      <c r="D59" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="G59" s="3"/>
-      <c r="H59" s="3"/>
-      <c r="I59" s="32" t="s">
-        <v>381</v>
-      </c>
-      <c r="J59" s="3"/>
-      <c r="K59" s="3"/>
-    </row>
-    <row r="60" spans="1:11" ht="72.75">
-      <c r="A60" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="B60" s="3"/>
-      <c r="C60" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="G60" s="3"/>
-      <c r="H60" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="I60" s="32"/>
-      <c r="J60" s="21" t="s">
-        <v>385</v>
-      </c>
-      <c r="K60" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11">
-      <c r="A61" s="9" t="s">
-        <v>387</v>
-      </c>
-      <c r="B61" s="3"/>
-      <c r="C61" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="F61" s="3"/>
-      <c r="G61" s="3"/>
-      <c r="H61" s="3"/>
-      <c r="I61" s="32"/>
-      <c r="J61" s="21"/>
-      <c r="K61" s="3"/>
-    </row>
-    <row r="62" spans="1:11" ht="75">
-      <c r="A62" s="9"/>
-      <c r="B62" s="3"/>
-      <c r="C62" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="D62" s="49" t="s">
-        <v>391</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="G62" s="3"/>
-      <c r="H62" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="I62" s="32"/>
-      <c r="J62" s="21"/>
-      <c r="K62" s="3"/>
-    </row>
-    <row r="63" spans="1:11" ht="30">
-      <c r="A63" s="20" t="s">
-        <v>393</v>
-      </c>
-      <c r="B63" s="10" t="s">
-        <v>394</v>
-      </c>
-      <c r="C63" s="10"/>
-      <c r="D63" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="G63" s="3"/>
-      <c r="H63" s="3"/>
-      <c r="I63" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="J63" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="K63" s="3"/>
-    </row>
-    <row r="64" spans="1:11" ht="30">
-      <c r="A64" s="9" t="s">
-        <v>399</v>
-      </c>
-      <c r="B64" s="3"/>
-      <c r="C64" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="G64" s="3"/>
-      <c r="H64" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="I64" s="3"/>
-      <c r="J64" s="3"/>
-      <c r="K64" s="3"/>
-    </row>
-    <row r="65" spans="1:11">
-      <c r="A65" s="9" t="s">
-        <v>401</v>
-      </c>
-      <c r="B65" s="3"/>
-      <c r="C65" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="F65" s="3"/>
-      <c r="G65" s="3"/>
-      <c r="H65" s="3"/>
-      <c r="I65" s="3"/>
-      <c r="J65" s="3"/>
-      <c r="K65" s="3"/>
-    </row>
-    <row r="66" spans="1:11" ht="27" customHeight="1">
-      <c r="A66" s="20" t="s">
-        <v>404</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="G66" s="3"/>
-      <c r="H66" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="K66" s="3"/>
-    </row>
-    <row r="67" spans="1:11" ht="27" customHeight="1">
-      <c r="A67" s="9" t="s">
-        <v>408</v>
-      </c>
-      <c r="C67" t="s">
-        <v>409</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="G67" s="3"/>
-      <c r="H67" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="I67" s="3"/>
-      <c r="J67" s="3"/>
-      <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="1:11" ht="30.75" customHeight="1">
-      <c r="A68" s="9"/>
-      <c r="D68" s="22"/>
-    </row>
-    <row r="69" spans="1:11">
-      <c r="A69" s="9"/>
-    </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="9"/>
-    </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="9"/>
-    </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="9"/>
-    </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="9"/>
-    </row>
-    <row r="88" spans="1:3">
-      <c r="B88" s="27"/>
-      <c r="C88" s="27"/>
-    </row>
-    <row r="89" spans="1:3" ht="15.75" thickBot="1">
-      <c r="B89" s="28"/>
-      <c r="C89" s="29"/>
-    </row>
-    <row r="90" spans="1:3" ht="15.75" thickTop="1">
-      <c r="B90" s="27"/>
-      <c r="C90" s="27"/>
+      <c r="L58" s="3"/>
+      <c r="M58" s="3"/>
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="1:14" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="B59" t="s">
+        <v>356</v>
+      </c>
+      <c r="D59" s="21" t="s">
+        <v>357</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="H59" t="s">
+        <v>359</v>
+      </c>
+      <c r="I59" t="s">
+        <v>360</v>
+      </c>
+      <c r="J59" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B63" s="28"/>
+      <c r="C63" s="28"/>
+    </row>
+    <row r="64" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B64" s="29"/>
+      <c r="C64" s="30"/>
+    </row>
+    <row r="65" spans="2:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B65" s="28"/>
+      <c r="C65" s="28"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="K52" r:id="rId1" xr:uid="{F83F3B55-B4C2-4802-934F-C9E3C14B805B}"/>
-    <hyperlink ref="K24" r:id="rId2" xr:uid="{B73C5555-EF90-4C17-AFEA-F4306780E8B3}"/>
-    <hyperlink ref="K21" r:id="rId3" xr:uid="{FEF2826C-4538-4BD0-84C3-18169970B566}"/>
-    <hyperlink ref="D62" r:id="rId4" display="https://referentiemodel.nhg.org/node/2514/publieksversie/published" xr:uid="{492B872A-3084-4D09-AB05-8A8C42E62B8A}"/>
+    <hyperlink ref="N51" r:id="rId1" xr:uid="{F83F3B55-B4C2-4802-934F-C9E3C14B805B}"/>
+    <hyperlink ref="N23" r:id="rId2" xr:uid="{B73C5555-EF90-4C17-AFEA-F4306780E8B3}"/>
+    <hyperlink ref="N20" r:id="rId3" xr:uid="{FEF2826C-4538-4BD0-84C3-18169970B566}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
-  <drawing r:id="rId6"/>
-  <legacyDrawing r:id="rId7"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
+  <drawing r:id="rId5"/>
+  <legacyDrawing r:id="rId6"/>
   <tableParts count="1">
-    <tablePart r:id="rId8"/>
+    <tablePart r:id="rId7"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{273AFAA3-99F7-4E93-9580-DCAE2B14D938}">
-  <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.140625" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" customWidth="1"/>
-    <col min="3" max="3" width="36.28515625" customWidth="1"/>
-    <col min="4" max="4" width="46.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" customWidth="1"/>
     <col min="5" max="5" width="16.7109375" customWidth="1"/>
     <col min="6" max="6" width="16.42578125" customWidth="1"/>
-    <col min="7" max="7" width="41.5703125" customWidth="1"/>
+    <col min="7" max="7" width="41.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="195.75" customHeight="1">
+    <row r="1" spans="1:7" ht="195.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>412</v>
+        <v>362</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>413</v>
+        <v>363</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>414</v>
+        <v>364</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>415</v>
+        <v>365</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>416</v>
+        <v>366</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>84</v>
-      </c>
-      <c r="B5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="71.25" customHeight="1">
-      <c r="A6" s="9" t="s">
-        <v>417</v>
-      </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="21" t="s">
-        <v>418</v>
-      </c>
-      <c r="D6" s="43" t="s">
-        <v>419</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-    </row>
-    <row r="7" spans="1:11" ht="71.25" customHeight="1">
-      <c r="A7" s="44" t="s">
-        <v>420</v>
-      </c>
-      <c r="B7" s="39" t="s">
-        <v>421</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="D7" s="50" t="s">
-        <v>423</v>
-      </c>
-      <c r="E7" s="45" t="s">
-        <v>424</v>
-      </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="39" t="s">
-        <v>425</v>
-      </c>
-      <c r="I7" s="39" t="s">
-        <v>426</v>
-      </c>
-      <c r="J7" s="39" t="s">
-        <v>427</v>
-      </c>
-      <c r="K7" s="3"/>
-    </row>
-    <row r="8" spans="1:11" ht="30">
-      <c r="A8" s="44" t="s">
-        <v>428</v>
-      </c>
-      <c r="B8" t="s">
-        <v>429</v>
-      </c>
-      <c r="D8" s="45" t="s">
-        <v>430</v>
-      </c>
-      <c r="E8" t="s">
-        <v>431</v>
-      </c>
-      <c r="F8" t="s">
-        <v>183</v>
-      </c>
-      <c r="H8" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="30">
-      <c r="A9" s="44" t="s">
-        <v>432</v>
-      </c>
-      <c r="B9" s="39" t="s">
-        <v>433</v>
-      </c>
-      <c r="C9" s="39" t="s">
-        <v>434</v>
-      </c>
-      <c r="D9" s="45" t="s">
-        <v>435</v>
-      </c>
-      <c r="E9" s="45" t="s">
-        <v>436</v>
-      </c>
-      <c r="F9" s="39" t="s">
-        <v>113</v>
-      </c>
-      <c r="G9" s="39"/>
-      <c r="H9" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="I9" s="39"/>
-      <c r="J9" s="39"/>
-      <c r="K9" s="40"/>
-    </row>
-    <row r="10" spans="1:11" ht="165">
-      <c r="A10" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="B10" s="41" t="s">
-        <v>438</v>
-      </c>
-      <c r="C10" s="41" t="s">
-        <v>439</v>
-      </c>
-      <c r="D10" s="47" t="s">
-        <v>440</v>
-      </c>
-      <c r="E10" s="47" t="s">
-        <v>441</v>
-      </c>
-      <c r="F10" s="41" t="s">
-        <v>183</v>
-      </c>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41" t="s">
-        <v>411</v>
-      </c>
-      <c r="I10" s="41"/>
-      <c r="J10" s="41"/>
-      <c r="K10" s="42" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="45">
-      <c r="A11" s="44" t="s">
-        <v>443</v>
-      </c>
-      <c r="B11" s="39" t="s">
-        <v>444</v>
-      </c>
-      <c r="C11" s="39" t="s">
-        <v>445</v>
-      </c>
-      <c r="D11" s="45" t="s">
-        <v>446</v>
-      </c>
-      <c r="E11" s="45"/>
-      <c r="F11" s="39" t="s">
-        <v>113</v>
-      </c>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="I11" s="39"/>
-      <c r="J11" s="39"/>
-      <c r="K11" s="40"/>
-    </row>
-    <row r="12" spans="1:11" ht="30">
-      <c r="A12" s="46" t="s">
-        <v>447</v>
-      </c>
-      <c r="B12" s="41" t="s">
-        <v>448</v>
-      </c>
-      <c r="C12" s="41" t="s">
-        <v>449</v>
-      </c>
-      <c r="D12" s="47" t="s">
-        <v>450</v>
-      </c>
-      <c r="E12" s="47"/>
-      <c r="F12" s="41" t="s">
-        <v>113</v>
-      </c>
-      <c r="G12" s="41"/>
-      <c r="H12" s="41" t="s">
-        <v>411</v>
-      </c>
-      <c r="I12" s="41"/>
-      <c r="J12" s="41"/>
-      <c r="K12" s="42" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="135">
-      <c r="A13" s="44" t="s">
-        <v>452</v>
-      </c>
-      <c r="B13" s="39" t="s">
-        <v>453</v>
-      </c>
-      <c r="C13" s="39" t="s">
-        <v>454</v>
-      </c>
-      <c r="D13" s="45" t="s">
-        <v>455</v>
-      </c>
-      <c r="E13" s="45" t="s">
-        <v>456</v>
-      </c>
-      <c r="F13" s="39" t="s">
-        <v>113</v>
-      </c>
-      <c r="G13" s="39"/>
-      <c r="H13" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="I13" s="39"/>
-      <c r="J13" s="39"/>
-      <c r="K13" s="40" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="60">
-      <c r="A14" s="46" t="s">
-        <v>458</v>
-      </c>
-      <c r="B14" s="41" t="s">
-        <v>459</v>
-      </c>
-      <c r="C14" s="41" t="s">
-        <v>460</v>
-      </c>
-      <c r="D14" s="47" t="s">
-        <v>461</v>
-      </c>
-      <c r="E14" s="47" t="s">
-        <v>462</v>
-      </c>
-      <c r="F14" s="41" t="s">
-        <v>113</v>
-      </c>
-      <c r="G14" s="41"/>
-      <c r="H14" s="41" t="s">
-        <v>411</v>
-      </c>
-      <c r="I14" s="41"/>
-      <c r="J14" s="41"/>
-      <c r="K14" s="42"/>
-    </row>
-    <row r="15" spans="1:11" ht="45">
-      <c r="A15" s="44" t="s">
-        <v>463</v>
-      </c>
-      <c r="B15" s="39" t="s">
-        <v>464</v>
-      </c>
-      <c r="C15" s="39" t="s">
-        <v>465</v>
-      </c>
-      <c r="D15" s="45" t="s">
-        <v>466</v>
-      </c>
-      <c r="E15" s="45" t="s">
-        <v>315</v>
-      </c>
-      <c r="F15" s="39" t="s">
-        <v>183</v>
-      </c>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="I15" s="39"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="40"/>
-    </row>
-    <row r="16" spans="1:11" ht="30">
-      <c r="A16" s="48" t="s">
-        <v>467</v>
-      </c>
-      <c r="B16" s="41" t="s">
-        <v>468</v>
-      </c>
-      <c r="C16" s="41" t="s">
-        <v>469</v>
-      </c>
-      <c r="D16" s="47" t="s">
-        <v>470</v>
-      </c>
-      <c r="E16" s="47"/>
-      <c r="F16" s="41" t="s">
-        <v>183</v>
-      </c>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41" t="s">
-        <v>411</v>
-      </c>
-      <c r="I16" s="41"/>
-      <c r="J16" s="41"/>
-      <c r="K16" s="42"/>
-    </row>
-    <row r="17" spans="1:11" ht="30">
-      <c r="A17" s="44" t="s">
-        <v>471</v>
-      </c>
-      <c r="B17" s="39" t="s">
-        <v>472</v>
-      </c>
-      <c r="C17" s="39" t="s">
-        <v>473</v>
-      </c>
-      <c r="D17" s="45" t="s">
-        <v>474</v>
-      </c>
-      <c r="E17" s="45" t="s">
-        <v>309</v>
-      </c>
-      <c r="F17" s="39" t="s">
-        <v>183</v>
-      </c>
-      <c r="G17" s="39"/>
-      <c r="H17" s="39" t="s">
-        <v>411</v>
-      </c>
-      <c r="I17" s="39"/>
-      <c r="J17" s="39"/>
-      <c r="K17" s="40"/>
-    </row>
-    <row r="18" spans="1:11" ht="89.45" customHeight="1">
-      <c r="A18" s="48" t="s">
-        <v>475</v>
-      </c>
-      <c r="B18" s="41" t="s">
-        <v>476</v>
-      </c>
-      <c r="C18" s="41" t="s">
-        <v>477</v>
-      </c>
-      <c r="D18" s="47" t="s">
-        <v>478</v>
-      </c>
-      <c r="E18" s="47"/>
-      <c r="F18" s="41" t="s">
-        <v>135</v>
-      </c>
-      <c r="G18" s="41"/>
-      <c r="H18" s="41" t="s">
-        <v>411</v>
-      </c>
-      <c r="I18" s="41"/>
-      <c r="J18" s="41"/>
-      <c r="K18" s="42"/>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" s="44" t="s">
-        <v>479</v>
-      </c>
-      <c r="B19" s="39" t="s">
-        <v>480</v>
-      </c>
-      <c r="C19" s="39" t="s">
-        <v>481</v>
-      </c>
-      <c r="D19" s="45"/>
-      <c r="E19" s="45"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="39"/>
-      <c r="H19" s="39"/>
-      <c r="I19" s="39"/>
-      <c r="J19" s="39"/>
-      <c r="K19" s="40"/>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" s="46" t="s">
-        <v>482</v>
-      </c>
-      <c r="B20" s="41" t="s">
-        <v>483</v>
-      </c>
-      <c r="C20" s="41" t="s">
-        <v>484</v>
-      </c>
-      <c r="D20" s="47"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="41"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="41"/>
-      <c r="I20" s="41"/>
-      <c r="J20" s="41"/>
-      <c r="K20" s="42"/>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" s="44" t="s">
-        <v>485</v>
-      </c>
-      <c r="B21" s="39" t="s">
-        <v>486</v>
-      </c>
-      <c r="C21" s="39" t="s">
-        <v>487</v>
-      </c>
-      <c r="D21" s="45"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="39"/>
-      <c r="J21" s="39"/>
-      <c r="K21" s="40"/>
-    </row>
-    <row r="22" spans="1:11" ht="210">
-      <c r="A22" s="51" t="s">
-        <v>347</v>
-      </c>
-      <c r="B22" s="52" t="s">
-        <v>348</v>
-      </c>
-      <c r="C22" s="52"/>
-      <c r="D22" s="45" t="s">
-        <v>349</v>
-      </c>
-      <c r="E22" s="45" t="s">
-        <v>488</v>
-      </c>
-      <c r="F22" s="45" t="s">
-        <v>135</v>
-      </c>
-      <c r="G22" s="45"/>
-      <c r="H22" s="45" t="s">
-        <v>114</v>
-      </c>
-      <c r="I22" s="45"/>
-      <c r="J22" s="53"/>
-      <c r="K22" s="54" t="s">
-        <v>489</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -6585,12 +5432,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2489EBC-5098-4697-9724-F190D24E1C3D}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" ht="111" customHeight="1"/>
-    <row r="2" spans="1:1">
+    <row r="1" spans="1:1" ht="111" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>490</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -6602,31 +5449,31 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0062C35-A590-498D-8635-16DE3DC0B82A}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.5703125" customWidth="1"/>
+    <col min="1" max="1" width="36.42578125" customWidth="1"/>
     <col min="2" max="2" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="B1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="30">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>491</v>
+        <v>368</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>493</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>
@@ -6638,72 +5485,72 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9E8E4E8-143C-4C64-99FB-1306F2338EFB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9E8E4E8-143C-4C64-99FB-1306F2338EFB}">
   <dimension ref="A2:J9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="27.7109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="27.5703125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="27.42578125" style="3" customWidth="1"/>
     <col min="4" max="4" width="60.140625" style="3" customWidth="1"/>
     <col min="5" max="5" width="47.7109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B2" s="15" t="s">
-        <v>494</v>
+        <v>371</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
       <c r="E2" s="12"/>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B3" s="16" t="s">
-        <v>495</v>
+        <v>372</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>496</v>
+        <v>373</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="156" customHeight="1">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="156" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="14" t="s">
-        <v>498</v>
+        <v>375</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>499</v>
+        <v>376</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>500</v>
+        <v>377</v>
       </c>
       <c r="E4" s="14"/>
     </row>
-    <row r="5" spans="1:10" ht="182.25" customHeight="1">
+    <row r="5" spans="1:10" ht="182.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
-        <v>501</v>
+        <v>378</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>306</v>
+        <v>279</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>502</v>
+        <v>379</v>
       </c>
       <c r="E5" s="14"/>
     </row>
-    <row r="6" spans="1:10" ht="45.75" customHeight="1">
-      <c r="A6" s="20"/>
+    <row r="6" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="19"/>
       <c r="B6" s="3" t="s">
-        <v>383</v>
+        <v>339</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>504</v>
+        <v>380</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>381</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
@@ -6711,50 +5558,58 @@
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" spans="1:10" ht="30">
+    <row r="7" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B7" s="14" t="s">
-        <v>505</v>
+        <v>382</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>503</v>
+        <v>380</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>506</v>
+        <v>383</v>
       </c>
       <c r="E7" s="14"/>
     </row>
-    <row r="8" spans="1:10" ht="30">
+    <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B8" s="14" t="s">
-        <v>507</v>
+        <v>384</v>
       </c>
       <c r="C8" s="14"/>
-      <c r="D8" s="34" t="s">
-        <v>508</v>
+      <c r="D8" s="35" t="s">
+        <v>385</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="90">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="90" x14ac:dyDescent="0.25">
       <c r="B9" s="14"/>
       <c r="C9" s="14" t="s">
-        <v>510</v>
+        <v>387</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>511</v>
-      </c>
-      <c r="E9" s="24"/>
+        <v>388</v>
+      </c>
+      <c r="E9" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="bb18a1b9-ddba-4244-9634-64732d0cb267">
@@ -6765,7 +5620,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D5656983173B1142A9B62A9C329F89A7" ma:contentTypeVersion="13" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="71caa5f225d89a4181f0614974a0635b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bb18a1b9-ddba-4244-9634-64732d0cb267" xmlns:ns3="06294a2e-6f87-4144-83b8-94a4d04d144a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d74eef483bec37fcdf125766e7bdb283" ns2:_="" ns3:_="">
     <xsd:import namespace="bb18a1b9-ddba-4244-9634-64732d0cb267"/>
@@ -6972,23 +5827,46 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E3A9028-3436-4B29-A420-9ED5B8A085B1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{148267B0-4CF5-48A7-B543-CDE45AF0A8FC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14B9AD58-A794-48C7-986D-80A9DB4B3205}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E3A9028-3436-4B29-A420-9ED5B8A085B1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="bb18a1b9-ddba-4244-9634-64732d0cb267"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="06294a2e-6f87-4144-83b8-94a4d04d144a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{148267B0-4CF5-48A7-B543-CDE45AF0A8FC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14B9AD58-A794-48C7-986D-80A9DB4B3205}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="bb18a1b9-ddba-4244-9634-64732d0cb267"/>
+    <ds:schemaRef ds:uri="06294a2e-6f87-4144-83b8-94a4d04d144a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/input/requirements/Condition.xlsx
+++ b/input/requirements/Condition.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edelman_nict1\IGs\GBB-IG\input\requirements\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/onnogieling/dev/GBB-IG/input/requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E15BA777-63BA-4A20-8B94-138FB720C249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ACC6E45-F058-3147-A954-25D8F093EA11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{71855D19-E937-4D4D-85D2-5BCEBB780255}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{71855D19-E937-4D4D-85D2-5BCEBB780255}"/>
   </bookViews>
   <sheets>
     <sheet name="Uitleg" sheetId="5" r:id="rId1"/>
@@ -3239,15 +3239,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F1013F7-63B2-4F83-92B0-1C8153859891}">
   <dimension ref="A1:C19"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="218.42578125" customWidth="1"/>
+    <col min="1" max="1" width="218.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3"/>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B18">
         <f>(510*132.5) + (160*132.5)</f>
         <v>88775</v>
@@ -3256,7 +3256,7 @@
         <v>5832</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19">
         <f>(542*132.5)</f>
         <v>71815</v>
@@ -3274,17 +3274,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CC1E3B3-D087-4A2B-920B-9BA971FAD64B}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
-    <col min="2" max="2" width="46.7109375" customWidth="1"/>
-    <col min="3" max="3" width="59.7109375" customWidth="1"/>
+    <col min="2" max="2" width="46.6640625" customWidth="1"/>
+    <col min="3" max="3" width="59.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="3"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -3295,7 +3295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -3306,7 +3306,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="96" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -3317,7 +3317,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="330" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="304" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -3328,7 +3328,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="64" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -3339,7 +3339,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -3350,7 +3350,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -3361,7 +3361,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="96" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -3372,7 +3372,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="135" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="128" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -3383,7 +3383,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -3394,7 +3394,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="315" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="256" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -3403,7 +3403,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -3425,16 +3425,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8AA88E1-0CFC-4A69-A682-35DA329C9688}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" customWidth="1"/>
-    <col min="2" max="2" width="51.28515625" customWidth="1"/>
-    <col min="3" max="3" width="67.28515625" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" customWidth="1"/>
+    <col min="2" max="2" width="51.33203125" customWidth="1"/>
+    <col min="3" max="3" width="67.33203125" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="58.140625" customWidth="1"/>
+    <col min="5" max="5" width="58.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>31</v>
       </c>
@@ -3451,7 +3451,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>36</v>
       </c>
@@ -3468,7 +3468,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>36</v>
       </c>
@@ -3485,7 +3485,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>36</v>
       </c>
@@ -3502,7 +3502,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>46</v>
       </c>
@@ -3517,7 +3517,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>46</v>
       </c>
@@ -3532,7 +3532,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>46</v>
       </c>
@@ -3547,7 +3547,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="48" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>55</v>
       </c>
@@ -3564,7 +3564,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="48" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>55</v>
       </c>
@@ -3581,7 +3581,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>55</v>
       </c>
@@ -3590,49 +3590,49 @@
       <c r="D10" s="3"/>
       <c r="E10" s="6"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="6"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="6"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="4"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="4"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="4"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
       <c r="E16" s="4"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -3659,25 +3659,25 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7034CDAF-2A08-4BE8-92C3-F4E7A6F24E1B}">
   <dimension ref="A1:O65"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" customWidth="1"/>
-    <col min="2" max="2" width="29.28515625" customWidth="1"/>
-    <col min="3" max="3" width="32.7109375" customWidth="1"/>
-    <col min="4" max="4" width="87.42578125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="11.5" customWidth="1"/>
+    <col min="2" max="2" width="29.33203125" customWidth="1"/>
+    <col min="3" max="3" width="32.6640625" customWidth="1"/>
+    <col min="4" max="4" width="87.5" style="3" customWidth="1"/>
     <col min="5" max="5" width="78" style="3" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" customWidth="1"/>
-    <col min="8" max="8" width="32.42578125" customWidth="1"/>
-    <col min="9" max="9" width="28.140625" customWidth="1"/>
-    <col min="10" max="10" width="51.28515625" customWidth="1"/>
-    <col min="11" max="11" width="38.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="38.42578125" customWidth="1"/>
-    <col min="14" max="14" width="33.28515625" customWidth="1"/>
+    <col min="6" max="6" width="18.6640625" customWidth="1"/>
+    <col min="7" max="7" width="11.5" customWidth="1"/>
+    <col min="8" max="8" width="32.5" customWidth="1"/>
+    <col min="9" max="9" width="28.1640625" customWidth="1"/>
+    <col min="10" max="10" width="51.33203125" customWidth="1"/>
+    <col min="11" max="11" width="38.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="38.5" customWidth="1"/>
+    <col min="14" max="14" width="33.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>62</v>
       </c>
@@ -3721,7 +3721,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="182.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="182.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="19" t="s">
         <v>80</v>
       </c>
@@ -3752,11 +3752,11 @@
       <c r="N3" s="19"/>
       <c r="O3" s="9"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="B4" s="8" t="s">
         <v>86</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -3779,12 +3779,11 @@
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
     </row>
-    <row r="5" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A5" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8" t="s">
+      <c r="B5" s="8" t="s">
         <v>92</v>
       </c>
       <c r="D5" s="3" t="s">
@@ -3807,12 +3806,11 @@
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
     </row>
-    <row r="6" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8" t="s">
+      <c r="B6" s="8" t="s">
         <v>86</v>
       </c>
       <c r="D6" s="3" t="s">
@@ -3835,12 +3833,11 @@
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
     </row>
-    <row r="7" spans="1:15" ht="105" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="80" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8" t="s">
+      <c r="B7" s="8" t="s">
         <v>100</v>
       </c>
       <c r="D7" s="3" t="s">
@@ -3863,7 +3860,7 @@
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
     </row>
-    <row r="8" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="32" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
         <v>103</v>
       </c>
@@ -3884,7 +3881,7 @@
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
     </row>
-    <row r="9" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="48" x14ac:dyDescent="0.2">
       <c r="A9" s="19" t="s">
         <v>106</v>
       </c>
@@ -3916,7 +3913,7 @@
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
     </row>
-    <row r="10" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" s="19" t="s">
         <v>114</v>
       </c>
@@ -3943,7 +3940,7 @@
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
     </row>
-    <row r="11" spans="1:15" ht="75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="64" x14ac:dyDescent="0.2">
       <c r="A11" s="19" t="s">
         <v>119</v>
       </c>
@@ -3976,7 +3973,7 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
     </row>
-    <row r="12" spans="1:15" ht="105" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="96" x14ac:dyDescent="0.2">
       <c r="A12" s="19" t="s">
         <v>127</v>
       </c>
@@ -4012,7 +4009,7 @@
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
     </row>
-    <row r="13" spans="1:15" ht="180.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" ht="180.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="19" t="s">
         <v>135</v>
       </c>
@@ -4048,7 +4045,7 @@
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="19" t="s">
         <v>142</v>
       </c>
@@ -4082,7 +4079,7 @@
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
     </row>
-    <row r="15" spans="1:15" ht="135" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" ht="135" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
         <v>147</v>
       </c>
@@ -4116,7 +4113,7 @@
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
     </row>
-    <row r="16" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
         <v>154</v>
       </c>
@@ -4134,7 +4131,7 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
     </row>
-    <row r="17" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="19" t="s">
         <v>156</v>
       </c>
@@ -4168,7 +4165,7 @@
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
     </row>
-    <row r="18" spans="1:14" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" ht="70.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="19" t="s">
         <v>163</v>
       </c>
@@ -4196,7 +4193,7 @@
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
         <v>168</v>
       </c>
@@ -4217,7 +4214,7 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
     </row>
-    <row r="20" spans="1:14" ht="101.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="101.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="19" t="s">
         <v>171</v>
       </c>
@@ -4255,7 +4252,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="108" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" ht="108" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="19" t="s">
         <v>179</v>
       </c>
@@ -4286,7 +4283,7 @@
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="19" t="s">
         <v>183</v>
       </c>
@@ -4304,7 +4301,7 @@
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
     </row>
-    <row r="23" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="64" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
         <v>185</v>
       </c>
@@ -4344,7 +4341,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="80" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
         <v>195</v>
       </c>
@@ -4372,7 +4369,7 @@
       <c r="M24" s="3"/>
       <c r="N24" s="5"/>
     </row>
-    <row r="25" spans="1:14" ht="149.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="149.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="s">
         <v>199</v>
       </c>
@@ -4400,7 +4397,7 @@
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
     </row>
-    <row r="26" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A26" s="19" t="s">
         <v>204</v>
       </c>
@@ -4434,7 +4431,7 @@
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="19" t="s">
         <v>210</v>
       </c>
@@ -4458,7 +4455,7 @@
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
     </row>
-    <row r="28" spans="1:14" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="19" t="s">
         <v>215</v>
       </c>
@@ -4482,7 +4479,7 @@
       <c r="I28" s="3"/>
       <c r="N28" s="3"/>
     </row>
-    <row r="29" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="19" t="s">
         <v>219</v>
       </c>
@@ -4510,7 +4507,7 @@
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
     </row>
-    <row r="30" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="19" t="s">
         <v>223</v>
       </c>
@@ -4538,7 +4535,7 @@
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
     </row>
-    <row r="31" spans="1:14" ht="219" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" ht="219" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="19" t="s">
         <v>228</v>
       </c>
@@ -4566,7 +4563,7 @@
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
     </row>
-    <row r="32" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="9" t="s">
         <v>233</v>
       </c>
@@ -4595,7 +4592,7 @@
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="19" t="s">
         <v>240</v>
       </c>
@@ -4618,7 +4615,7 @@
       </c>
       <c r="N33" s="3"/>
     </row>
-    <row r="34" spans="1:14" ht="162" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" ht="162" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="19" t="s">
         <v>243</v>
       </c>
@@ -4646,7 +4643,7 @@
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
     </row>
-    <row r="35" spans="1:14" ht="121.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" ht="121.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="9" t="s">
         <v>248</v>
       </c>
@@ -4674,7 +4671,7 @@
       <c r="M35" s="3"/>
       <c r="N35" s="3"/>
     </row>
-    <row r="36" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A36" s="9" t="s">
         <v>253</v>
       </c>
@@ -4701,7 +4698,7 @@
       <c r="M36" s="3"/>
       <c r="N36" s="3"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="19" t="s">
         <v>259</v>
       </c>
@@ -4729,7 +4726,7 @@
       <c r="M37" s="3"/>
       <c r="N37" s="3"/>
     </row>
-    <row r="38" spans="1:14" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" ht="66.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="19" t="s">
         <v>263</v>
       </c>
@@ -4757,7 +4754,7 @@
       <c r="M38" s="3"/>
       <c r="N38" s="3"/>
     </row>
-    <row r="39" spans="1:14" ht="178.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" ht="178.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="9" t="s">
         <v>267</v>
       </c>
@@ -4785,7 +4782,7 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
     </row>
-    <row r="40" spans="1:14" ht="135" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" ht="135" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="19" t="s">
         <v>271</v>
       </c>
@@ -4817,7 +4814,7 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
     </row>
-    <row r="41" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="9" t="s">
         <v>276</v>
       </c>
@@ -4845,7 +4842,7 @@
       <c r="M41" s="3"/>
       <c r="N41" s="3"/>
     </row>
-    <row r="42" spans="1:14" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" ht="98.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="9" t="s">
         <v>280</v>
       </c>
@@ -4873,7 +4870,7 @@
       <c r="M42" s="3"/>
       <c r="N42" s="3"/>
     </row>
-    <row r="43" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A43" s="19" t="s">
         <v>285</v>
       </c>
@@ -4905,7 +4902,7 @@
       <c r="M43" s="3"/>
       <c r="N43" s="3"/>
     </row>
-    <row r="44" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" ht="48" x14ac:dyDescent="0.2">
       <c r="A44" s="9"/>
       <c r="B44" s="3"/>
       <c r="C44" s="10"/>
@@ -4922,7 +4919,7 @@
       <c r="M44" s="3"/>
       <c r="N44" s="3"/>
     </row>
-    <row r="45" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="19" t="s">
         <v>292</v>
       </c>
@@ -4956,7 +4953,7 @@
       <c r="M45" s="3"/>
       <c r="N45" s="3"/>
     </row>
-    <row r="46" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="9" t="s">
         <v>299</v>
       </c>
@@ -4975,7 +4972,7 @@
       <c r="M46" s="3"/>
       <c r="N46" s="3"/>
     </row>
-    <row r="47" spans="1:14" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="9" t="s">
         <v>301</v>
       </c>
@@ -5003,7 +5000,7 @@
       <c r="M47" s="3"/>
       <c r="N47" s="3"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="19" t="s">
         <v>305</v>
       </c>
@@ -5035,7 +5032,7 @@
       <c r="M48" s="3"/>
       <c r="N48" s="3"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="19" t="s">
         <v>311</v>
       </c>
@@ -5060,7 +5057,7 @@
       <c r="M49" s="3"/>
       <c r="N49" s="3"/>
     </row>
-    <row r="50" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A50" s="19" t="s">
         <v>314</v>
       </c>
@@ -5085,7 +5082,7 @@
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
     </row>
-    <row r="51" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A51" s="19" t="s">
         <v>317</v>
       </c>
@@ -5119,7 +5116,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="52" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A52" s="9"/>
       <c r="B52" s="3"/>
       <c r="C52" s="10"/>
@@ -5136,7 +5133,7 @@
       <c r="M52" s="3"/>
       <c r="N52" s="4"/>
     </row>
-    <row r="53" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A53" s="9" t="s">
         <v>325</v>
       </c>
@@ -5154,7 +5151,7 @@
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
     </row>
-    <row r="54" spans="1:14" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="19" t="s">
         <v>327</v>
       </c>
@@ -5188,7 +5185,7 @@
       <c r="M54" s="25"/>
       <c r="N54" s="3"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="9" t="s">
         <v>334</v>
       </c>
@@ -5216,7 +5213,7 @@
       <c r="M55" s="17"/>
       <c r="N55" s="3"/>
     </row>
-    <row r="56" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A56" s="19" t="s">
         <v>338</v>
       </c>
@@ -5248,7 +5245,7 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
     </row>
-    <row r="57" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" ht="32" x14ac:dyDescent="0.2">
       <c r="A57" s="19" t="s">
         <v>344</v>
       </c>
@@ -5280,7 +5277,7 @@
       <c r="M57" s="3"/>
       <c r="N57" s="3"/>
     </row>
-    <row r="58" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="19" t="s">
         <v>351</v>
       </c>
@@ -5312,7 +5309,7 @@
       <c r="M58" s="3"/>
       <c r="N58" s="3"/>
     </row>
-    <row r="59" spans="1:14" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="9" t="s">
         <v>355</v>
       </c>
@@ -5335,15 +5332,15 @@
         <v>361</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B63" s="28"/>
       <c r="C63" s="28"/>
     </row>
-    <row r="64" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B64" s="29"/>
       <c r="C64" s="30"/>
     </row>
-    <row r="65" spans="2:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:3" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B65" s="28"/>
       <c r="C65" s="28"/>
     </row>
@@ -5367,17 +5364,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{273AFAA3-99F7-4E93-9580-DCAE2B14D938}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.140625" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" customWidth="1"/>
-    <col min="7" max="7" width="41.42578125" customWidth="1"/>
+    <col min="1" max="1" width="19.1640625" customWidth="1"/>
+    <col min="2" max="2" width="18.5" customWidth="1"/>
+    <col min="4" max="4" width="15.1640625" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="16.5" customWidth="1"/>
+    <col min="7" max="7" width="41.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="195.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="195.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>362</v>
       </c>
@@ -5400,7 +5397,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>364</v>
       </c>
@@ -5432,10 +5429,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2489EBC-5098-4697-9724-F190D24E1C3D}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1" ht="111" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" ht="111" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>367</v>
       </c>
@@ -5449,13 +5446,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0062C35-A590-498D-8635-16DE3DC0B82A}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.42578125" customWidth="1"/>
+    <col min="1" max="1" width="36.5" customWidth="1"/>
     <col min="2" max="2" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>100</v>
       </c>
@@ -5463,7 +5460,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>368</v>
       </c>
@@ -5471,7 +5468,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>370</v>
       </c>
@@ -5487,15 +5484,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9E8E4E8-143C-4C64-99FB-1306F2338EFB}">
   <dimension ref="A2:J9"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="27.7109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="27.42578125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="60.140625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="47.7109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="27.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="27.5" style="3" customWidth="1"/>
+    <col min="4" max="4" width="60.1640625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="47.6640625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="B2" s="15" t="s">
         <v>371</v>
       </c>
@@ -5503,7 +5500,7 @@
       <c r="D2" s="12"/>
       <c r="E2" s="12"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="B3" s="16" t="s">
         <v>372</v>
       </c>
@@ -5517,7 +5514,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="156" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="156" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="14" t="s">
         <v>375</v>
       </c>
@@ -5529,7 +5526,7 @@
       </c>
       <c r="E4" s="14"/>
     </row>
-    <row r="5" spans="1:10" ht="182.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="182.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="14" t="s">
         <v>378</v>
       </c>
@@ -5541,7 +5538,7 @@
       </c>
       <c r="E5" s="14"/>
     </row>
-    <row r="6" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="19"/>
       <c r="B6" s="3" t="s">
         <v>339</v>
@@ -5558,7 +5555,7 @@
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="B7" s="14" t="s">
         <v>382</v>
       </c>
@@ -5570,7 +5567,7 @@
       </c>
       <c r="E7" s="14"/>
     </row>
-    <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="B8" s="14" t="s">
         <v>384</v>
       </c>
@@ -5582,7 +5579,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="80" x14ac:dyDescent="0.2">
       <c r="B9" s="14"/>
       <c r="C9" s="14" t="s">
         <v>387</v>
@@ -5601,15 +5598,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="bb18a1b9-ddba-4244-9634-64732d0cb267">
@@ -5618,6 +5606,15 @@
     <TaxCatchAll xmlns="06294a2e-6f87-4144-83b8-94a4d04d144a" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5828,14 +5825,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{148267B0-4CF5-48A7-B543-CDE45AF0A8FC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E3A9028-3436-4B29-A420-9ED5B8A085B1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -5848,6 +5837,14 @@
     <ds:schemaRef ds:uri="06294a2e-6f87-4144-83b8-94a4d04d144a"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{148267B0-4CF5-48A7-B543-CDE45AF0A8FC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
